--- a/domain/tasks/20260311_202700_vd_masterdata_ingame_generation/vd_all/vd_all.xlsx
+++ b/domain/tasks/20260311_202700_vd_masterdata_ingame_generation/vd_all/vd_all.xlsx
@@ -7,16 +7,17 @@
   </bookViews>
   <sheets>
     <sheet name="ブロック基礎設計_vd_kai_normal_00001" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="MstInGame" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MstEnemyOutpost" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MstKomaLine" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="MstAutoPlayerSequence" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MstPage" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="MstEnemyStageParameter" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ブロック基礎設計_vd_osh_normal_00001" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MstInGame" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MstEnemyOutpost" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MstKomaLine" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MstAutoPlayerSequence" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MstPage" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MstEnemyStageParameter" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2052,206 +2053,1465 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M64"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="3.1640625" customWidth="1" min="1" max="1"/>
+    <col width="19.1640625" customWidth="1" min="2" max="2"/>
+    <col width="18.83203125" customWidth="1" min="3" max="10"/>
+    <col width="3.1640625" customWidth="1" min="11" max="13"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="30" t="inlineStr">
-        <is>
-          <t>ENABLE</t>
-        </is>
-      </c>
-      <c r="B1" s="30" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" s="30" t="inlineStr">
-        <is>
-          <t>mst_auto_player_sequence_id</t>
-        </is>
-      </c>
-      <c r="D1" s="30" t="inlineStr">
-        <is>
-          <t>mst_auto_player_sequence_set_id</t>
-        </is>
-      </c>
-      <c r="E1" s="30" t="inlineStr">
-        <is>
-          <t>bgm_asset_key</t>
-        </is>
-      </c>
-      <c r="F1" s="30" t="inlineStr">
-        <is>
-          <t>boss_bgm_asset_key</t>
-        </is>
-      </c>
-      <c r="G1" s="30" t="inlineStr">
-        <is>
-          <t>loop_background_asset_key</t>
-        </is>
-      </c>
-      <c r="H1" s="30" t="inlineStr">
-        <is>
-          <t>player_outpost_asset_key</t>
-        </is>
-      </c>
-      <c r="I1" s="30" t="inlineStr">
-        <is>
-          <t>mst_page_id</t>
-        </is>
-      </c>
-      <c r="J1" s="30" t="inlineStr">
-        <is>
-          <t>mst_enemy_outpost_id</t>
-        </is>
-      </c>
-      <c r="K1" s="30" t="inlineStr">
-        <is>
-          <t>mst_defense_target_id</t>
-        </is>
-      </c>
-      <c r="L1" s="30" t="inlineStr">
-        <is>
-          <t>boss_mst_enemy_stage_parameter_id</t>
-        </is>
-      </c>
-      <c r="M1" s="30" t="inlineStr">
-        <is>
-          <t>boss_count</t>
-        </is>
-      </c>
-      <c r="N1" s="30" t="inlineStr">
-        <is>
-          <t>normal_enemy_hp_coef</t>
-        </is>
-      </c>
-      <c r="O1" s="30" t="inlineStr">
-        <is>
-          <t>normal_enemy_attack_coef</t>
-        </is>
-      </c>
-      <c r="P1" s="30" t="inlineStr">
-        <is>
-          <t>normal_enemy_speed_coef</t>
-        </is>
-      </c>
-      <c r="Q1" s="30" t="inlineStr">
-        <is>
-          <t>boss_enemy_hp_coef</t>
-        </is>
-      </c>
-      <c r="R1" s="30" t="inlineStr">
-        <is>
-          <t>boss_enemy_attack_coef</t>
-        </is>
-      </c>
-      <c r="S1" s="30" t="inlineStr">
-        <is>
-          <t>boss_enemy_speed_coef</t>
-        </is>
-      </c>
-      <c r="T1" s="30" t="inlineStr">
-        <is>
-          <t>release_key</t>
-        </is>
-      </c>
-      <c r="U1" s="30" t="inlineStr">
-        <is>
-          <t>result_tips.ja</t>
-        </is>
-      </c>
-      <c r="V1" s="30" t="inlineStr">
-        <is>
-          <t>description.ja</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B2" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="C2" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="D2" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="E2" s="31" t="inlineStr">
-        <is>
-          <t>SSE_SBG_003_010</t>
-        </is>
-      </c>
-      <c r="F2" s="31" t="inlineStr"/>
-      <c r="G2" s="31" t="inlineStr"/>
-      <c r="H2" s="31" t="inlineStr"/>
-      <c r="I2" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="J2" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="K2" s="31" t="inlineStr"/>
-      <c r="L2" s="31" t="inlineStr"/>
-      <c r="M2" s="31" t="inlineStr"/>
-      <c r="N2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="S2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="T2" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-      <c r="U2" s="31" t="inlineStr"/>
-      <c r="V2" s="31" t="inlineStr"/>
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>ブロック基礎設計_vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="A2" s="6" t="n"/>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="13" customHeight="1">
+      <c r="A3" s="6" t="n"/>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>■要件テキスト</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="186" customHeight="1">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>ファントム（Colorless/Attack・HP5,000・ATK100・SPD34）が開幕250msに5体で序盤テンポを作り、その後【推しの子】Green属性キャラ4種（c_osh_00501→c_osh_00201→c_osh_00401→c_osh_00301の順）がHP10,000〜50,000で続く5波構成、合計21体。ファントムは`e_`キャラのため瞬時まとめ召喚、c_キャラは`summon_interval=500ms`で1体ずつ間隔を空けて召喚する。
+コマは3行固定。row1=2等分2コマ（0.50, 0.50）・row2=右広い3コマ（0.50, 0.25, 0.25）・row3=4等分4コマ（0.25×4）。コマアセット: osh_00001（back_ground_offset: -1.0）。
+UR対抗キャラ「B小町不動のセンター アイ」（chara_osh_00001）対抗。序盤ファントムで多属性対応を試しつつ、中盤以降はGreen属性対策コマが主軸となる設計。</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
+      <c r="H4" s="27" t="n"/>
+      <c r="I4" s="27" t="n"/>
+      <c r="J4" s="28" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="13" customHeight="1">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="13" customHeight="1">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>■基本情報</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>⇩ボスブロックのみに記載する</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>インゲームID</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>ブロック種別</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>敵ゲートHP</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>コマ行数</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>グループ切り替え</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>シーケンス行数</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>リリースキー</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>3行</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>なし（デフォルトグループのみ）</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>5行</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>202604010</v>
+      </c>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>※ノーマルブロックは3フロア固定で、ボスブロックは1フロア固定</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>■コマ効果</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>行</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>コマ数</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>コマアセット</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>コマ効果</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>レイアウト幅</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>行1</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>2コマ</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>0.5 / 0.5</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>行2</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>3コマ</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>0.5 / 0.25 / 0.25</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>行3</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>4コマ</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>0.25 / 0.25 / 0.25 / 0.25</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>コマ効果1</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>効果時間</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>効果数値</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>■登場敵パラメータ</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>敵ID</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>キャラ名</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>属性</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>ロール</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>攻撃</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>移動速度</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>役割</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Colorless（無属性）</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="F26" s="29" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="H26" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>雑魚（e_キャラ）</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00501_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>黒川あかね</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Green（緑属性）</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="F27" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G27" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="H27" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>雑魚（c_キャラ）</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="13" customHeight="1">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00201_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>星野 ルビー</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Green（緑属性）</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="F28" s="29" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G28" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="H28" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="26" t="inlineStr">
+        <is>
+          <t>雑魚（c_キャラ）</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="13" customHeight="1">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00401_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>有馬 かな</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Green（緑属性）</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="F29" s="29" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G29" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="H29" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="I29" s="26" t="inlineStr">
+        <is>
+          <t>雑魚（c_キャラ）</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="13" customHeight="1">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00301_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>MEMちょ</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>Green（緑属性）</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F30" s="29" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G30" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="H30" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="26" t="inlineStr">
+        <is>
+          <t>雑魚（c_キャラ）</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="13" customHeight="1">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+    </row>
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>■シーケンス構成</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+    </row>
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>行番号</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>トリガー種別</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>条件値（ms）</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>敵ID</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>キャラ名</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>体数</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="F40" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" s="26" t="inlineStr"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E41" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00501_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="F41" s="26" t="inlineStr">
+        <is>
+          <t>黒川あかね</t>
+        </is>
+      </c>
+      <c r="G41" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H41" s="26" t="inlineStr"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="D42" s="29" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00201_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="F42" s="26" t="inlineStr">
+        <is>
+          <t>星野 ルビー</t>
+        </is>
+      </c>
+      <c r="G42" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H42" s="26" t="inlineStr"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E43" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00401_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="F43" s="26" t="inlineStr">
+        <is>
+          <t>有馬 かな</t>
+        </is>
+      </c>
+      <c r="G43" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H43" s="26" t="inlineStr"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="D44" s="29" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00301_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="F44" s="26" t="inlineStr">
+        <is>
+          <t>MEMちょ</t>
+        </is>
+      </c>
+      <c r="G44" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" s="26" t="inlineStr"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+    </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="11" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
+    </row>
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="11" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
+    </row>
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="11" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="11" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n"/>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="11" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="11" t="n"/>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="11" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="11" t="n"/>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="15" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="11" t="n"/>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="11" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n"/>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="15" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="11" t="n"/>
+      <c r="G52" s="11" t="n"/>
+      <c r="H52" s="11" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n"/>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="11" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="11" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n"/>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="16" t="n"/>
+      <c r="B54" s="16" t="n"/>
+      <c r="C54" s="16" t="n"/>
+      <c r="D54" s="16" t="n"/>
+      <c r="E54" s="16" t="n"/>
+      <c r="F54" s="16" t="n"/>
+      <c r="G54" s="16" t="n"/>
+      <c r="H54" s="16" t="n"/>
+      <c r="I54" s="16" t="n"/>
+      <c r="J54" s="16" t="n"/>
+      <c r="K54" s="16" t="n"/>
+      <c r="L54" s="16" t="n"/>
+      <c r="M54" s="16" t="n"/>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="16" t="n"/>
+      <c r="B55" s="16" t="n"/>
+      <c r="C55" s="16" t="n"/>
+      <c r="D55" s="16" t="n"/>
+      <c r="E55" s="16" t="n"/>
+      <c r="F55" s="16" t="n"/>
+      <c r="G55" s="16" t="n"/>
+      <c r="H55" s="16" t="n"/>
+      <c r="I55" s="16" t="n"/>
+      <c r="J55" s="16" t="n"/>
+      <c r="K55" s="16" t="n"/>
+      <c r="L55" s="16" t="n"/>
+      <c r="M55" s="16" t="n"/>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="16" t="n"/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>■ステージ説明文</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="16" t="n"/>
+      <c r="F56" s="16" t="n"/>
+      <c r="G56" s="16" t="n"/>
+      <c r="H56" s="16" t="n"/>
+      <c r="I56" s="16" t="n"/>
+      <c r="J56" s="16" t="n"/>
+      <c r="K56" s="16" t="n"/>
+      <c r="L56" s="16" t="n"/>
+      <c r="M56" s="16" t="n"/>
+    </row>
+    <row r="57" ht="13" customHeight="1">
+      <c r="A57" s="16" t="n"/>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D57" s="27" t="n"/>
+      <c r="E57" s="27" t="n"/>
+      <c r="F57" s="27" t="n"/>
+      <c r="G57" s="28" t="n"/>
+      <c r="H57" s="16" t="n"/>
+      <c r="I57" s="16" t="n"/>
+      <c r="J57" s="16" t="n"/>
+      <c r="K57" s="16" t="n"/>
+      <c r="L57" s="16" t="n"/>
+      <c r="M57" s="16" t="n"/>
+    </row>
+    <row r="58" ht="13" customHeight="1">
+      <c r="A58" s="16" t="n"/>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>バトルヒント</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr"/>
+      <c r="D58" s="27" t="n"/>
+      <c r="E58" s="27" t="n"/>
+      <c r="F58" s="27" t="n"/>
+      <c r="G58" s="28" t="n"/>
+      <c r="H58" s="16" t="n"/>
+      <c r="I58" s="16" t="n"/>
+      <c r="J58" s="16" t="n"/>
+      <c r="K58" s="16" t="n"/>
+      <c r="L58" s="16" t="n"/>
+      <c r="M58" s="16" t="n"/>
+    </row>
+    <row r="59" ht="13" customHeight="1">
+      <c r="A59" s="16" t="n"/>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>ステージ説明文</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr"/>
+      <c r="D59" s="27" t="n"/>
+      <c r="E59" s="27" t="n"/>
+      <c r="F59" s="27" t="n"/>
+      <c r="G59" s="28" t="n"/>
+      <c r="H59" s="16" t="n"/>
+      <c r="I59" s="16" t="n"/>
+      <c r="J59" s="16" t="n"/>
+      <c r="K59" s="16" t="n"/>
+      <c r="L59" s="16" t="n"/>
+      <c r="M59" s="16" t="n"/>
+    </row>
+    <row r="60" ht="13" customHeight="1">
+      <c r="A60" s="16" t="n"/>
+      <c r="B60" s="16" t="n"/>
+      <c r="C60" s="16" t="n"/>
+      <c r="D60" s="16" t="n"/>
+      <c r="E60" s="16" t="n"/>
+      <c r="F60" s="16" t="n"/>
+      <c r="G60" s="16" t="n"/>
+      <c r="H60" s="16" t="n"/>
+      <c r="I60" s="16" t="n"/>
+      <c r="J60" s="16" t="n"/>
+      <c r="K60" s="16" t="n"/>
+      <c r="L60" s="16" t="n"/>
+      <c r="M60" s="16" t="n"/>
+    </row>
+    <row r="61" ht="13" customHeight="1">
+      <c r="A61" s="19" t="n"/>
+      <c r="B61" s="19" t="n"/>
+      <c r="C61" s="19" t="n"/>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="19" t="n"/>
+      <c r="G61" s="19" t="n"/>
+      <c r="H61" s="19" t="n"/>
+      <c r="I61" s="19" t="n"/>
+      <c r="J61" s="19" t="n"/>
+      <c r="K61" s="19" t="n"/>
+      <c r="L61" s="19" t="n"/>
+      <c r="M61" s="19" t="n"/>
+    </row>
+    <row r="62" ht="13" customHeight="1">
+      <c r="A62" s="19" t="n"/>
+      <c r="B62" s="19" t="n"/>
+      <c r="C62" s="19" t="n"/>
+      <c r="D62" s="19" t="n"/>
+      <c r="E62" s="19" t="n"/>
+      <c r="F62" s="19" t="n"/>
+      <c r="G62" s="19" t="n"/>
+      <c r="H62" s="19" t="n"/>
+      <c r="I62" s="19" t="n"/>
+      <c r="J62" s="19" t="n"/>
+      <c r="K62" s="19" t="n"/>
+      <c r="L62" s="19" t="n"/>
+      <c r="M62" s="19" t="n"/>
+    </row>
+    <row r="63" ht="13" customHeight="1">
+      <c r="A63" s="19" t="n"/>
+      <c r="B63" s="19" t="n"/>
+      <c r="C63" s="19" t="n"/>
+      <c r="D63" s="19" t="n"/>
+      <c r="E63" s="19" t="n"/>
+      <c r="F63" s="19" t="n"/>
+      <c r="G63" s="19" t="n"/>
+      <c r="H63" s="19" t="n"/>
+      <c r="I63" s="19" t="n"/>
+      <c r="J63" s="19" t="n"/>
+      <c r="K63" s="19" t="n"/>
+      <c r="L63" s="19" t="n"/>
+      <c r="M63" s="19" t="n"/>
+    </row>
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="19" t="n"/>
+      <c r="B64" s="19" t="n"/>
+      <c r="C64" s="19" t="n"/>
+      <c r="D64" s="19" t="n"/>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="19" t="n"/>
+      <c r="G64" s="19" t="n"/>
+      <c r="H64" s="19" t="n"/>
+      <c r="I64" s="19" t="n"/>
+      <c r="J64" s="19" t="n"/>
+      <c r="K64" s="19" t="n"/>
+      <c r="L64" s="19" t="n"/>
+      <c r="M64" s="19" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="4">
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="B4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -2261,7 +3521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2277,27 +3537,102 @@
       </c>
       <c r="C1" s="30" t="inlineStr">
         <is>
-          <t>hp</t>
+          <t>mst_auto_player_sequence_id</t>
         </is>
       </c>
       <c r="D1" s="30" t="inlineStr">
         <is>
-          <t>is_damage_invalidation</t>
+          <t>mst_auto_player_sequence_set_id</t>
         </is>
       </c>
       <c r="E1" s="30" t="inlineStr">
         <is>
-          <t>outpost_asset_key</t>
+          <t>bgm_asset_key</t>
         </is>
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>artwork_asset_key</t>
+          <t>boss_bgm_asset_key</t>
         </is>
       </c>
       <c r="G1" s="30" t="inlineStr">
         <is>
+          <t>loop_background_asset_key</t>
+        </is>
+      </c>
+      <c r="H1" s="30" t="inlineStr">
+        <is>
+          <t>player_outpost_asset_key</t>
+        </is>
+      </c>
+      <c r="I1" s="30" t="inlineStr">
+        <is>
+          <t>mst_page_id</t>
+        </is>
+      </c>
+      <c r="J1" s="30" t="inlineStr">
+        <is>
+          <t>mst_enemy_outpost_id</t>
+        </is>
+      </c>
+      <c r="K1" s="30" t="inlineStr">
+        <is>
+          <t>mst_defense_target_id</t>
+        </is>
+      </c>
+      <c r="L1" s="30" t="inlineStr">
+        <is>
+          <t>boss_mst_enemy_stage_parameter_id</t>
+        </is>
+      </c>
+      <c r="M1" s="30" t="inlineStr">
+        <is>
+          <t>boss_count</t>
+        </is>
+      </c>
+      <c r="N1" s="30" t="inlineStr">
+        <is>
+          <t>normal_enemy_hp_coef</t>
+        </is>
+      </c>
+      <c r="O1" s="30" t="inlineStr">
+        <is>
+          <t>normal_enemy_attack_coef</t>
+        </is>
+      </c>
+      <c r="P1" s="30" t="inlineStr">
+        <is>
+          <t>normal_enemy_speed_coef</t>
+        </is>
+      </c>
+      <c r="Q1" s="30" t="inlineStr">
+        <is>
+          <t>boss_enemy_hp_coef</t>
+        </is>
+      </c>
+      <c r="R1" s="30" t="inlineStr">
+        <is>
+          <t>boss_enemy_attack_coef</t>
+        </is>
+      </c>
+      <c r="S1" s="30" t="inlineStr">
+        <is>
+          <t>boss_enemy_speed_coef</t>
+        </is>
+      </c>
+      <c r="T1" s="30" t="inlineStr">
+        <is>
           <t>release_key</t>
+        </is>
+      </c>
+      <c r="U1" s="30" t="inlineStr">
+        <is>
+          <t>result_tips.ja</t>
+        </is>
+      </c>
+      <c r="V1" s="30" t="inlineStr">
+        <is>
+          <t>description.ja</t>
         </is>
       </c>
     </row>
@@ -2314,17 +3649,136 @@
       </c>
       <c r="C2" s="31" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D2" s="31" t="inlineStr"/>
-      <c r="E2" s="31" t="inlineStr"/>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D2" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="E2" s="31" t="inlineStr">
+        <is>
+          <t>SSE_SBG_003_010</t>
+        </is>
+      </c>
       <c r="F2" s="31" t="inlineStr"/>
-      <c r="G2" s="31" t="inlineStr">
+      <c r="G2" s="31" t="inlineStr"/>
+      <c r="H2" s="31" t="inlineStr"/>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="J2" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="K2" s="31" t="inlineStr"/>
+      <c r="L2" s="31" t="inlineStr"/>
+      <c r="M2" s="31" t="inlineStr"/>
+      <c r="N2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="S2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="T2" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
       </c>
+      <c r="U2" s="31" t="inlineStr"/>
+      <c r="V2" s="31" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr"/>
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>SSE_SBG_003_010</t>
+        </is>
+      </c>
+      <c r="F3" s="31" t="inlineStr"/>
+      <c r="G3" s="31" t="inlineStr"/>
+      <c r="H3" s="31" t="inlineStr"/>
+      <c r="I3" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="J3" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="K3" s="31" t="inlineStr"/>
+      <c r="L3" s="31" t="inlineStr"/>
+      <c r="M3" s="31" t="inlineStr"/>
+      <c r="N3" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O3" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P3" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q3" s="31" t="inlineStr"/>
+      <c r="R3" s="31" t="inlineStr"/>
+      <c r="S3" s="31" t="inlineStr"/>
+      <c r="T3" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+      <c r="U3" s="31" t="inlineStr"/>
+      <c r="V3" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2337,7 +3791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2353,205 +3807,25 @@
       </c>
       <c r="C1" s="30" t="inlineStr">
         <is>
-          <t>mst_page_id</t>
+          <t>hp</t>
         </is>
       </c>
       <c r="D1" s="30" t="inlineStr">
         <is>
-          <t>row</t>
+          <t>is_damage_invalidation</t>
         </is>
       </c>
       <c r="E1" s="30" t="inlineStr">
         <is>
-          <t>height</t>
+          <t>outpost_asset_key</t>
         </is>
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>koma_line_layout_asset_key</t>
+          <t>artwork_asset_key</t>
         </is>
       </c>
       <c r="G1" s="30" t="inlineStr">
-        <is>
-          <t>koma1_asset_key</t>
-        </is>
-      </c>
-      <c r="H1" s="30" t="inlineStr">
-        <is>
-          <t>koma1_width</t>
-        </is>
-      </c>
-      <c r="I1" s="30" t="inlineStr">
-        <is>
-          <t>koma1_back_ground_offset</t>
-        </is>
-      </c>
-      <c r="J1" s="30" t="inlineStr">
-        <is>
-          <t>koma1_effect_type</t>
-        </is>
-      </c>
-      <c r="K1" s="30" t="inlineStr">
-        <is>
-          <t>koma1_effect_parameter1</t>
-        </is>
-      </c>
-      <c r="L1" s="30" t="inlineStr">
-        <is>
-          <t>koma1_effect_parameter2</t>
-        </is>
-      </c>
-      <c r="M1" s="30" t="inlineStr">
-        <is>
-          <t>koma1_effect_target_side</t>
-        </is>
-      </c>
-      <c r="N1" s="30" t="inlineStr">
-        <is>
-          <t>koma1_effect_target_colors</t>
-        </is>
-      </c>
-      <c r="O1" s="30" t="inlineStr">
-        <is>
-          <t>koma1_effect_target_roles</t>
-        </is>
-      </c>
-      <c r="P1" s="30" t="inlineStr">
-        <is>
-          <t>koma2_asset_key</t>
-        </is>
-      </c>
-      <c r="Q1" s="30" t="inlineStr">
-        <is>
-          <t>koma2_width</t>
-        </is>
-      </c>
-      <c r="R1" s="30" t="inlineStr">
-        <is>
-          <t>koma2_back_ground_offset</t>
-        </is>
-      </c>
-      <c r="S1" s="30" t="inlineStr">
-        <is>
-          <t>koma2_effect_type</t>
-        </is>
-      </c>
-      <c r="T1" s="30" t="inlineStr">
-        <is>
-          <t>koma2_effect_parameter1</t>
-        </is>
-      </c>
-      <c r="U1" s="30" t="inlineStr">
-        <is>
-          <t>koma2_effect_parameter2</t>
-        </is>
-      </c>
-      <c r="V1" s="30" t="inlineStr">
-        <is>
-          <t>koma2_effect_target_side</t>
-        </is>
-      </c>
-      <c r="W1" s="30" t="inlineStr">
-        <is>
-          <t>koma2_effect_target_colors</t>
-        </is>
-      </c>
-      <c r="X1" s="30" t="inlineStr">
-        <is>
-          <t>koma2_effect_target_roles</t>
-        </is>
-      </c>
-      <c r="Y1" s="30" t="inlineStr">
-        <is>
-          <t>koma3_asset_key</t>
-        </is>
-      </c>
-      <c r="Z1" s="30" t="inlineStr">
-        <is>
-          <t>koma3_width</t>
-        </is>
-      </c>
-      <c r="AA1" s="30" t="inlineStr">
-        <is>
-          <t>koma3_back_ground_offset</t>
-        </is>
-      </c>
-      <c r="AB1" s="30" t="inlineStr">
-        <is>
-          <t>koma3_effect_type</t>
-        </is>
-      </c>
-      <c r="AC1" s="30" t="inlineStr">
-        <is>
-          <t>koma3_effect_parameter1</t>
-        </is>
-      </c>
-      <c r="AD1" s="30" t="inlineStr">
-        <is>
-          <t>koma3_effect_parameter2</t>
-        </is>
-      </c>
-      <c r="AE1" s="30" t="inlineStr">
-        <is>
-          <t>koma3_effect_target_side</t>
-        </is>
-      </c>
-      <c r="AF1" s="30" t="inlineStr">
-        <is>
-          <t>koma3_effect_target_colors</t>
-        </is>
-      </c>
-      <c r="AG1" s="30" t="inlineStr">
-        <is>
-          <t>koma3_effect_target_roles</t>
-        </is>
-      </c>
-      <c r="AH1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_asset_key</t>
-        </is>
-      </c>
-      <c r="AI1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_width</t>
-        </is>
-      </c>
-      <c r="AJ1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_back_ground_offset</t>
-        </is>
-      </c>
-      <c r="AK1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_effect_type</t>
-        </is>
-      </c>
-      <c r="AL1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_effect_parameter1</t>
-        </is>
-      </c>
-      <c r="AM1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_effect_parameter2</t>
-        </is>
-      </c>
-      <c r="AN1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_effect_target_side</t>
-        </is>
-      </c>
-      <c r="AO1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_effect_target_colors</t>
-        </is>
-      </c>
-      <c r="AP1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_effect_target_roles</t>
-        </is>
-      </c>
-      <c r="AQ1" s="30" t="inlineStr">
         <is>
           <t>release_key</t>
         </is>
@@ -2565,186 +3839,18 @@
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001_1</t>
+          <t>vd_kai_normal_00001</t>
         </is>
       </c>
       <c r="C2" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="D2" s="31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" s="31" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="F2" s="31" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D2" s="31" t="inlineStr"/>
+      <c r="E2" s="31" t="inlineStr"/>
+      <c r="F2" s="31" t="inlineStr"/>
       <c r="G2" s="31" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
-      <c r="H2" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="I2" s="31" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J2" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="N2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="O2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="P2" s="31" t="inlineStr"/>
-      <c r="Q2" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="R2" s="31" t="inlineStr"/>
-      <c r="S2" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="W2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="X2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="Y2" s="31" t="inlineStr"/>
-      <c r="Z2" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AA2" s="31" t="inlineStr"/>
-      <c r="AB2" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AC2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AF2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AG2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AH2" s="31" t="inlineStr"/>
-      <c r="AI2" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AJ2" s="31" t="inlineStr"/>
-      <c r="AK2" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AL2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AO2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AP2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AQ2" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -2758,367 +3864,18 @@
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001_2</t>
+          <t>vd_osh_normal_00001</t>
         </is>
       </c>
       <c r="C3" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="D3" s="31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E3" s="31" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="F3" s="31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="inlineStr"/>
+      <c r="E3" s="31" t="inlineStr"/>
+      <c r="F3" s="31" t="inlineStr"/>
       <c r="G3" s="31" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
-      <c r="H3" s="31" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I3" s="31" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="N3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="O3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="P3" s="31" t="inlineStr"/>
-      <c r="Q3" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="R3" s="31" t="inlineStr"/>
-      <c r="S3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="W3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="X3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="Y3" s="31" t="inlineStr"/>
-      <c r="Z3" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AA3" s="31" t="inlineStr"/>
-      <c r="AB3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AC3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AF3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AG3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AH3" s="31" t="inlineStr"/>
-      <c r="AI3" s="31" t="inlineStr"/>
-      <c r="AJ3" s="31" t="inlineStr"/>
-      <c r="AK3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AL3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AO3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AP3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AQ3" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001_3</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="F4" s="31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
-      <c r="H4" s="31" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I4" s="31" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J4" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="N4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="O4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="P4" s="31" t="inlineStr"/>
-      <c r="Q4" s="31" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="R4" s="31" t="inlineStr"/>
-      <c r="S4" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="W4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="X4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="Y4" s="31" t="inlineStr"/>
-      <c r="Z4" s="31" t="inlineStr"/>
-      <c r="AA4" s="31" t="inlineStr"/>
-      <c r="AB4" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AC4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AF4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AG4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AH4" s="31" t="inlineStr"/>
-      <c r="AI4" s="31" t="inlineStr"/>
-      <c r="AJ4" s="31" t="inlineStr"/>
-      <c r="AK4" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AL4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AO4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AP4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AQ4" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -3135,7 +3892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3151,165 +3908,205 @@
       </c>
       <c r="C1" s="30" t="inlineStr">
         <is>
-          <t>sequence_set_id</t>
+          <t>mst_page_id</t>
         </is>
       </c>
       <c r="D1" s="30" t="inlineStr">
         <is>
-          <t>sequence_group_id</t>
+          <t>row</t>
         </is>
       </c>
       <c r="E1" s="30" t="inlineStr">
         <is>
-          <t>sequence_element_id</t>
+          <t>height</t>
         </is>
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>priority_sequence_element_id</t>
+          <t>koma_line_layout_asset_key</t>
         </is>
       </c>
       <c r="G1" s="30" t="inlineStr">
         <is>
-          <t>condition_type</t>
+          <t>koma1_asset_key</t>
         </is>
       </c>
       <c r="H1" s="30" t="inlineStr">
         <is>
-          <t>condition_value</t>
+          <t>koma1_width</t>
         </is>
       </c>
       <c r="I1" s="30" t="inlineStr">
         <is>
-          <t>action_type</t>
+          <t>koma1_back_ground_offset</t>
         </is>
       </c>
       <c r="J1" s="30" t="inlineStr">
         <is>
-          <t>action_value</t>
+          <t>koma1_effect_type</t>
         </is>
       </c>
       <c r="K1" s="30" t="inlineStr">
         <is>
-          <t>action_value2</t>
+          <t>koma1_effect_parameter1</t>
         </is>
       </c>
       <c r="L1" s="30" t="inlineStr">
         <is>
-          <t>summon_count</t>
+          <t>koma1_effect_parameter2</t>
         </is>
       </c>
       <c r="M1" s="30" t="inlineStr">
         <is>
-          <t>summon_interval</t>
+          <t>koma1_effect_target_side</t>
         </is>
       </c>
       <c r="N1" s="30" t="inlineStr">
         <is>
-          <t>summon_animation_type</t>
+          <t>koma1_effect_target_colors</t>
         </is>
       </c>
       <c r="O1" s="30" t="inlineStr">
         <is>
-          <t>summon_position</t>
+          <t>koma1_effect_target_roles</t>
         </is>
       </c>
       <c r="P1" s="30" t="inlineStr">
         <is>
-          <t>move_start_condition_type</t>
+          <t>koma2_asset_key</t>
         </is>
       </c>
       <c r="Q1" s="30" t="inlineStr">
         <is>
-          <t>move_start_condition_value</t>
+          <t>koma2_width</t>
         </is>
       </c>
       <c r="R1" s="30" t="inlineStr">
         <is>
-          <t>move_stop_condition_type</t>
+          <t>koma2_back_ground_offset</t>
         </is>
       </c>
       <c r="S1" s="30" t="inlineStr">
         <is>
-          <t>move_stop_condition_value</t>
+          <t>koma2_effect_type</t>
         </is>
       </c>
       <c r="T1" s="30" t="inlineStr">
         <is>
-          <t>move_restart_condition_type</t>
+          <t>koma2_effect_parameter1</t>
         </is>
       </c>
       <c r="U1" s="30" t="inlineStr">
         <is>
-          <t>move_restart_condition_value</t>
+          <t>koma2_effect_parameter2</t>
         </is>
       </c>
       <c r="V1" s="30" t="inlineStr">
         <is>
-          <t>move_loop_count</t>
+          <t>koma2_effect_target_side</t>
         </is>
       </c>
       <c r="W1" s="30" t="inlineStr">
         <is>
-          <t>is_summon_unit_outpost_damage_invalidation</t>
+          <t>koma2_effect_target_colors</t>
         </is>
       </c>
       <c r="X1" s="30" t="inlineStr">
         <is>
-          <t>last_boss_trigger</t>
+          <t>koma2_effect_target_roles</t>
         </is>
       </c>
       <c r="Y1" s="30" t="inlineStr">
         <is>
-          <t>aura_type</t>
+          <t>koma3_asset_key</t>
         </is>
       </c>
       <c r="Z1" s="30" t="inlineStr">
         <is>
-          <t>death_type</t>
+          <t>koma3_width</t>
         </is>
       </c>
       <c r="AA1" s="30" t="inlineStr">
         <is>
-          <t>enemy_hp_coef</t>
+          <t>koma3_back_ground_offset</t>
         </is>
       </c>
       <c r="AB1" s="30" t="inlineStr">
         <is>
-          <t>enemy_attack_coef</t>
+          <t>koma3_effect_type</t>
         </is>
       </c>
       <c r="AC1" s="30" t="inlineStr">
         <is>
-          <t>enemy_speed_coef</t>
+          <t>koma3_effect_parameter1</t>
         </is>
       </c>
       <c r="AD1" s="30" t="inlineStr">
         <is>
-          <t>override_drop_battle_point</t>
+          <t>koma3_effect_parameter2</t>
         </is>
       </c>
       <c r="AE1" s="30" t="inlineStr">
         <is>
-          <t>defeated_score</t>
+          <t>koma3_effect_target_side</t>
         </is>
       </c>
       <c r="AF1" s="30" t="inlineStr">
         <is>
-          <t>action_delay</t>
+          <t>koma3_effect_target_colors</t>
         </is>
       </c>
       <c r="AG1" s="30" t="inlineStr">
         <is>
-          <t>deactivation_condition_type</t>
+          <t>koma3_effect_target_roles</t>
         </is>
       </c>
       <c r="AH1" s="30" t="inlineStr">
         <is>
-          <t>deactivation_condition_value</t>
+          <t>koma4_asset_key</t>
         </is>
       </c>
       <c r="AI1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_width</t>
+        </is>
+      </c>
+      <c r="AJ1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_back_ground_offset</t>
+        </is>
+      </c>
+      <c r="AK1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_effect_type</t>
+        </is>
+      </c>
+      <c r="AL1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_effect_parameter1</t>
+        </is>
+      </c>
+      <c r="AM1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_effect_parameter2</t>
+        </is>
+      </c>
+      <c r="AN1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_effect_target_side</t>
+        </is>
+      </c>
+      <c r="AO1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_effect_target_colors</t>
+        </is>
+      </c>
+      <c r="AP1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_effect_target_roles</t>
+        </is>
+      </c>
+      <c r="AQ1" s="30" t="inlineStr">
         <is>
           <t>release_key</t>
         </is>
@@ -3331,107 +4128,179 @@
           <t>vd_kai_normal_00001</t>
         </is>
       </c>
-      <c r="D2" s="31" t="inlineStr"/>
+      <c r="D2" s="31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E2" s="31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F2" s="31" t="inlineStr"/>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="F2" s="31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="G2" s="31" t="inlineStr">
         <is>
-          <t>ElapsedTime</t>
+          <t>kai_00001</t>
         </is>
       </c>
       <c r="H2" s="31" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I2" s="31" t="inlineStr">
         <is>
-          <t>SummonEnemy</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" s="31" t="inlineStr">
         <is>
-          <t>e_glo_00001_vd_Normal_Colorless</t>
-        </is>
-      </c>
-      <c r="K2" s="31" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L2" s="31" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M2" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
       <c r="N2" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O2" s="31" t="inlineStr"/>
-      <c r="P2" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q2" s="31" t="inlineStr"/>
-      <c r="R2" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S2" s="31" t="inlineStr"/>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="P2" s="31" t="inlineStr"/>
+      <c r="Q2" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="R2" s="31" t="inlineStr"/>
+      <c r="S2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="T2" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U2" s="31" t="inlineStr"/>
-      <c r="V2" s="31" t="inlineStr"/>
-      <c r="W2" s="31" t="inlineStr"/>
-      <c r="X2" s="31" t="inlineStr"/>
-      <c r="Y2" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Y2" s="31" t="inlineStr"/>
       <c r="Z2" s="31" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA2" s="31" t="inlineStr"/>
       <c r="AB2" s="31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AC2" s="31" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD2" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF2" s="31" t="inlineStr"/>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
       <c r="AG2" s="31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>All</t>
         </is>
       </c>
       <c r="AH2" s="31" t="inlineStr"/>
       <c r="AI2" s="31" t="inlineStr">
         <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AJ2" s="31" t="inlineStr"/>
+      <c r="AK2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AO2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AP2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AQ2" s="31" t="inlineStr">
+        <is>
           <t>202604010</t>
         </is>
       </c>
@@ -3452,106 +4321,174 @@
           <t>vd_kai_normal_00001</t>
         </is>
       </c>
-      <c r="D3" s="31" t="inlineStr"/>
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="E3" s="31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F3" s="31" t="inlineStr"/>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="F3" s="31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="G3" s="31" t="inlineStr">
         <is>
-          <t>ElapsedTime</t>
+          <t>kai_00001</t>
         </is>
       </c>
       <c r="H3" s="31" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I3" s="31" t="inlineStr">
         <is>
-          <t>SummonEnemy</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" s="31" t="inlineStr">
         <is>
-          <t>e_kai_00101_vd_Normal_Yellow</t>
-        </is>
-      </c>
-      <c r="K3" s="31" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L3" s="31" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M3" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
       <c r="N3" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O3" s="31" t="inlineStr"/>
-      <c r="P3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q3" s="31" t="inlineStr"/>
-      <c r="R3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S3" s="31" t="inlineStr"/>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="P3" s="31" t="inlineStr"/>
+      <c r="Q3" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="R3" s="31" t="inlineStr"/>
+      <c r="S3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="T3" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U3" s="31" t="inlineStr"/>
-      <c r="V3" s="31" t="inlineStr"/>
-      <c r="W3" s="31" t="inlineStr"/>
-      <c r="X3" s="31" t="inlineStr"/>
-      <c r="Y3" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Y3" s="31" t="inlineStr"/>
       <c r="Z3" s="31" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA3" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA3" s="31" t="inlineStr"/>
       <c r="AB3" s="31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AC3" s="31" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD3" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AG3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AH3" s="31" t="inlineStr"/>
+      <c r="AI3" s="31" t="inlineStr"/>
+      <c r="AJ3" s="31" t="inlineStr"/>
+      <c r="AK3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL3" s="31" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AF3" s="31" t="inlineStr"/>
-      <c r="AG3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AH3" s="31" t="inlineStr"/>
-      <c r="AI3" s="31" t="inlineStr">
+      <c r="AM3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AO3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AP3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AQ3" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -3573,106 +4510,170 @@
           <t>vd_kai_normal_00001</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr"/>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E4" s="31" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="31" t="inlineStr"/>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="G4" s="31" t="inlineStr">
         <is>
-          <t>ElapsedTime</t>
+          <t>kai_00001</t>
         </is>
       </c>
       <c r="H4" s="31" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I4" s="31" t="inlineStr">
         <is>
-          <t>SummonEnemy</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J4" s="31" t="inlineStr">
         <is>
-          <t>e_glo_00001_vd_Normal_Colorless</t>
-        </is>
-      </c>
-      <c r="K4" s="31" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L4" s="31" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M4" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
       <c r="N4" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O4" s="31" t="inlineStr"/>
-      <c r="P4" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q4" s="31" t="inlineStr"/>
-      <c r="R4" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S4" s="31" t="inlineStr"/>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="P4" s="31" t="inlineStr"/>
+      <c r="Q4" s="31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="R4" s="31" t="inlineStr"/>
+      <c r="S4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="T4" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U4" s="31" t="inlineStr"/>
-      <c r="V4" s="31" t="inlineStr"/>
-      <c r="W4" s="31" t="inlineStr"/>
-      <c r="X4" s="31" t="inlineStr"/>
-      <c r="Y4" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="Z4" s="31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA4" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Y4" s="31" t="inlineStr"/>
+      <c r="Z4" s="31" t="inlineStr"/>
+      <c r="AA4" s="31" t="inlineStr"/>
       <c r="AB4" s="31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AC4" s="31" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD4" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AG4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AH4" s="31" t="inlineStr"/>
+      <c r="AI4" s="31" t="inlineStr"/>
+      <c r="AJ4" s="31" t="inlineStr"/>
+      <c r="AK4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL4" s="31" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AF4" s="31" t="inlineStr"/>
-      <c r="AG4" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AH4" s="31" t="inlineStr"/>
-      <c r="AI4" s="31" t="inlineStr">
+      <c r="AM4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AO4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AP4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AQ4" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -3686,114 +4687,130 @@
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001_4</t>
+          <t>vd_osh_normal_00001_1</t>
         </is>
       </c>
       <c r="C5" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr"/>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E5" s="31" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="inlineStr"/>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="G5" s="31" t="inlineStr">
         <is>
-          <t>ElapsedTime</t>
+          <t>osh_00001</t>
         </is>
       </c>
       <c r="H5" s="31" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I5" s="31" t="inlineStr">
         <is>
-          <t>SummonEnemy</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" s="31" t="inlineStr">
         <is>
-          <t>e_kai_00101_vd_Normal_Yellow</t>
-        </is>
-      </c>
-      <c r="K5" s="31" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L5" s="31" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M5" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
       <c r="N5" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O5" s="31" t="inlineStr"/>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O5" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
       <c r="P5" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q5" s="31" t="inlineStr"/>
-      <c r="R5" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S5" s="31" t="inlineStr"/>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="Q5" s="31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="R5" s="31" t="inlineStr"/>
+      <c r="S5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="T5" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U5" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="V5" s="31" t="inlineStr"/>
       <c r="W5" s="31" t="inlineStr"/>
       <c r="X5" s="31" t="inlineStr"/>
-      <c r="Y5" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="Z5" s="31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA5" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
+      <c r="Y5" s="31" t="inlineStr"/>
+      <c r="Z5" s="31" t="inlineStr"/>
+      <c r="AA5" s="31" t="inlineStr"/>
       <c r="AB5" s="31" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AC5" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC5" s="31" t="inlineStr"/>
       <c r="AD5" s="31" t="inlineStr"/>
-      <c r="AE5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AE5" s="31" t="inlineStr"/>
       <c r="AF5" s="31" t="inlineStr"/>
-      <c r="AG5" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="AG5" s="31" t="inlineStr"/>
       <c r="AH5" s="31" t="inlineStr"/>
-      <c r="AI5" s="31" t="inlineStr">
+      <c r="AI5" s="31" t="inlineStr"/>
+      <c r="AJ5" s="31" t="inlineStr"/>
+      <c r="AK5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL5" s="31" t="inlineStr"/>
+      <c r="AM5" s="31" t="inlineStr"/>
+      <c r="AN5" s="31" t="inlineStr"/>
+      <c r="AO5" s="31" t="inlineStr"/>
+      <c r="AP5" s="31" t="inlineStr"/>
+      <c r="AQ5" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -3807,114 +4824,315 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001_5</t>
+          <t>vd_osh_normal_00001_2</t>
         </is>
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr"/>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="E6" s="31" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F6" s="31" t="inlineStr"/>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="G6" s="31" t="inlineStr">
         <is>
-          <t>ElapsedTime</t>
+          <t>osh_00001</t>
         </is>
       </c>
       <c r="H6" s="31" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I6" s="31" t="inlineStr">
         <is>
-          <t>SummonEnemy</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" s="31" t="inlineStr">
         <is>
-          <t>e_kai_00101_vd_Normal_Yellow</t>
-        </is>
-      </c>
-      <c r="K6" s="31" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L6" s="31" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M6" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
       <c r="N6" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O6" s="31" t="inlineStr"/>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O6" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
       <c r="P6" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q6" s="31" t="inlineStr"/>
-      <c r="R6" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S6" s="31" t="inlineStr"/>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="Q6" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="R6" s="31" t="inlineStr"/>
+      <c r="S6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="T6" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U6" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="V6" s="31" t="inlineStr"/>
       <c r="W6" s="31" t="inlineStr"/>
       <c r="X6" s="31" t="inlineStr"/>
       <c r="Y6" s="31" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>osh_00001</t>
         </is>
       </c>
       <c r="Z6" s="31" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA6" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA6" s="31" t="inlineStr"/>
       <c r="AB6" s="31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AC6" s="31" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD6" s="31" t="inlineStr"/>
-      <c r="AE6" s="31" t="inlineStr">
-        <is>
           <t>0</t>
         </is>
       </c>
+      <c r="AD6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE6" s="31" t="inlineStr"/>
       <c r="AF6" s="31" t="inlineStr"/>
-      <c r="AG6" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="AG6" s="31" t="inlineStr"/>
       <c r="AH6" s="31" t="inlineStr"/>
-      <c r="AI6" s="31" t="inlineStr">
+      <c r="AI6" s="31" t="inlineStr"/>
+      <c r="AJ6" s="31" t="inlineStr"/>
+      <c r="AK6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL6" s="31" t="inlineStr"/>
+      <c r="AM6" s="31" t="inlineStr"/>
+      <c r="AN6" s="31" t="inlineStr"/>
+      <c r="AO6" s="31" t="inlineStr"/>
+      <c r="AP6" s="31" t="inlineStr"/>
+      <c r="AQ6" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_3</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="H7" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="N7" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O7" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="P7" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="Q7" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="R7" s="31" t="inlineStr"/>
+      <c r="S7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V7" s="31" t="inlineStr"/>
+      <c r="W7" s="31" t="inlineStr"/>
+      <c r="X7" s="31" t="inlineStr"/>
+      <c r="Y7" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="Z7" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA7" s="31" t="inlineStr"/>
+      <c r="AB7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" s="31" t="inlineStr"/>
+      <c r="AF7" s="31" t="inlineStr"/>
+      <c r="AG7" s="31" t="inlineStr"/>
+      <c r="AH7" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="AI7" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AJ7" s="31" t="inlineStr"/>
+      <c r="AK7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN7" s="31" t="inlineStr"/>
+      <c r="AO7" s="31" t="inlineStr"/>
+      <c r="AP7" s="31" t="inlineStr"/>
+      <c r="AQ7" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -3931,7 +5149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3947,6 +5165,166 @@
       </c>
       <c r="C1" s="30" t="inlineStr">
         <is>
+          <t>sequence_set_id</t>
+        </is>
+      </c>
+      <c r="D1" s="30" t="inlineStr">
+        <is>
+          <t>sequence_group_id</t>
+        </is>
+      </c>
+      <c r="E1" s="30" t="inlineStr">
+        <is>
+          <t>sequence_element_id</t>
+        </is>
+      </c>
+      <c r="F1" s="30" t="inlineStr">
+        <is>
+          <t>priority_sequence_element_id</t>
+        </is>
+      </c>
+      <c r="G1" s="30" t="inlineStr">
+        <is>
+          <t>condition_type</t>
+        </is>
+      </c>
+      <c r="H1" s="30" t="inlineStr">
+        <is>
+          <t>condition_value</t>
+        </is>
+      </c>
+      <c r="I1" s="30" t="inlineStr">
+        <is>
+          <t>action_type</t>
+        </is>
+      </c>
+      <c r="J1" s="30" t="inlineStr">
+        <is>
+          <t>action_value</t>
+        </is>
+      </c>
+      <c r="K1" s="30" t="inlineStr">
+        <is>
+          <t>action_value2</t>
+        </is>
+      </c>
+      <c r="L1" s="30" t="inlineStr">
+        <is>
+          <t>summon_count</t>
+        </is>
+      </c>
+      <c r="M1" s="30" t="inlineStr">
+        <is>
+          <t>summon_interval</t>
+        </is>
+      </c>
+      <c r="N1" s="30" t="inlineStr">
+        <is>
+          <t>summon_animation_type</t>
+        </is>
+      </c>
+      <c r="O1" s="30" t="inlineStr">
+        <is>
+          <t>summon_position</t>
+        </is>
+      </c>
+      <c r="P1" s="30" t="inlineStr">
+        <is>
+          <t>move_start_condition_type</t>
+        </is>
+      </c>
+      <c r="Q1" s="30" t="inlineStr">
+        <is>
+          <t>move_start_condition_value</t>
+        </is>
+      </c>
+      <c r="R1" s="30" t="inlineStr">
+        <is>
+          <t>move_stop_condition_type</t>
+        </is>
+      </c>
+      <c r="S1" s="30" t="inlineStr">
+        <is>
+          <t>move_stop_condition_value</t>
+        </is>
+      </c>
+      <c r="T1" s="30" t="inlineStr">
+        <is>
+          <t>move_restart_condition_type</t>
+        </is>
+      </c>
+      <c r="U1" s="30" t="inlineStr">
+        <is>
+          <t>move_restart_condition_value</t>
+        </is>
+      </c>
+      <c r="V1" s="30" t="inlineStr">
+        <is>
+          <t>move_loop_count</t>
+        </is>
+      </c>
+      <c r="W1" s="30" t="inlineStr">
+        <is>
+          <t>is_summon_unit_outpost_damage_invalidation</t>
+        </is>
+      </c>
+      <c r="X1" s="30" t="inlineStr">
+        <is>
+          <t>last_boss_trigger</t>
+        </is>
+      </c>
+      <c r="Y1" s="30" t="inlineStr">
+        <is>
+          <t>aura_type</t>
+        </is>
+      </c>
+      <c r="Z1" s="30" t="inlineStr">
+        <is>
+          <t>death_type</t>
+        </is>
+      </c>
+      <c r="AA1" s="30" t="inlineStr">
+        <is>
+          <t>enemy_hp_coef</t>
+        </is>
+      </c>
+      <c r="AB1" s="30" t="inlineStr">
+        <is>
+          <t>enemy_attack_coef</t>
+        </is>
+      </c>
+      <c r="AC1" s="30" t="inlineStr">
+        <is>
+          <t>enemy_speed_coef</t>
+        </is>
+      </c>
+      <c r="AD1" s="30" t="inlineStr">
+        <is>
+          <t>override_drop_battle_point</t>
+        </is>
+      </c>
+      <c r="AE1" s="30" t="inlineStr">
+        <is>
+          <t>defeated_score</t>
+        </is>
+      </c>
+      <c r="AF1" s="30" t="inlineStr">
+        <is>
+          <t>action_delay</t>
+        </is>
+      </c>
+      <c r="AG1" s="30" t="inlineStr">
+        <is>
+          <t>deactivation_condition_type</t>
+        </is>
+      </c>
+      <c r="AH1" s="30" t="inlineStr">
+        <is>
+          <t>deactivation_condition_value</t>
+        </is>
+      </c>
+      <c r="AI1" s="30" t="inlineStr">
+        <is>
           <t>release_key</t>
         </is>
       </c>
@@ -3959,10 +5337,1203 @@
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
+          <t>vd_kai_normal_00001_1</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
           <t>vd_kai_normal_00001</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr"/>
+      <c r="E2" s="31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" s="31" t="inlineStr"/>
+      <c r="G2" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H2" s="31" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J2" s="31" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K2" s="31" t="inlineStr"/>
+      <c r="L2" s="31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M2" s="31" t="inlineStr"/>
+      <c r="N2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O2" s="31" t="inlineStr"/>
+      <c r="P2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q2" s="31" t="inlineStr"/>
+      <c r="R2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S2" s="31" t="inlineStr"/>
+      <c r="T2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U2" s="31" t="inlineStr"/>
+      <c r="V2" s="31" t="inlineStr"/>
+      <c r="W2" s="31" t="inlineStr"/>
+      <c r="X2" s="31" t="inlineStr"/>
+      <c r="Y2" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z2" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD2" s="31" t="inlineStr"/>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr"/>
+      <c r="AG2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH2" s="31" t="inlineStr"/>
+      <c r="AI2" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001_2</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="inlineStr"/>
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" s="31" t="inlineStr"/>
+      <c r="G3" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H3" s="31" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="I3" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J3" s="31" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="K3" s="31" t="inlineStr"/>
+      <c r="L3" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M3" s="31" t="inlineStr"/>
+      <c r="N3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O3" s="31" t="inlineStr"/>
+      <c r="P3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q3" s="31" t="inlineStr"/>
+      <c r="R3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S3" s="31" t="inlineStr"/>
+      <c r="T3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U3" s="31" t="inlineStr"/>
+      <c r="V3" s="31" t="inlineStr"/>
+      <c r="W3" s="31" t="inlineStr"/>
+      <c r="X3" s="31" t="inlineStr"/>
+      <c r="Y3" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z3" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA3" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB3" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC3" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD3" s="31" t="inlineStr"/>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr"/>
+      <c r="AG3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH3" s="31" t="inlineStr"/>
+      <c r="AI3" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001_3</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr"/>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr"/>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H4" s="31" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J4" s="31" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K4" s="31" t="inlineStr"/>
+      <c r="L4" s="31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="31" t="inlineStr"/>
+      <c r="N4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O4" s="31" t="inlineStr"/>
+      <c r="P4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q4" s="31" t="inlineStr"/>
+      <c r="R4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S4" s="31" t="inlineStr"/>
+      <c r="T4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U4" s="31" t="inlineStr"/>
+      <c r="V4" s="31" t="inlineStr"/>
+      <c r="W4" s="31" t="inlineStr"/>
+      <c r="X4" s="31" t="inlineStr"/>
+      <c r="Y4" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z4" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD4" s="31" t="inlineStr"/>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="inlineStr"/>
+      <c r="AG4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH4" s="31" t="inlineStr"/>
+      <c r="AI4" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001_4</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr"/>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr"/>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J5" s="31" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="inlineStr"/>
+      <c r="L5" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M5" s="31" t="inlineStr"/>
+      <c r="N5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O5" s="31" t="inlineStr"/>
+      <c r="P5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q5" s="31" t="inlineStr"/>
+      <c r="R5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S5" s="31" t="inlineStr"/>
+      <c r="T5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U5" s="31" t="inlineStr"/>
+      <c r="V5" s="31" t="inlineStr"/>
+      <c r="W5" s="31" t="inlineStr"/>
+      <c r="X5" s="31" t="inlineStr"/>
+      <c r="Y5" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z5" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA5" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB5" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD5" s="31" t="inlineStr"/>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="inlineStr"/>
+      <c r="AG5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH5" s="31" t="inlineStr"/>
+      <c r="AI5" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001_5</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr"/>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F6" s="31" t="inlineStr"/>
+      <c r="G6" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H6" s="31" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J6" s="31" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="K6" s="31" t="inlineStr"/>
+      <c r="L6" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M6" s="31" t="inlineStr"/>
+      <c r="N6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O6" s="31" t="inlineStr"/>
+      <c r="P6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q6" s="31" t="inlineStr"/>
+      <c r="R6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S6" s="31" t="inlineStr"/>
+      <c r="T6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U6" s="31" t="inlineStr"/>
+      <c r="V6" s="31" t="inlineStr"/>
+      <c r="W6" s="31" t="inlineStr"/>
+      <c r="X6" s="31" t="inlineStr"/>
+      <c r="Y6" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z6" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA6" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB6" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC6" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD6" s="31" t="inlineStr"/>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr"/>
+      <c r="AG6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH6" s="31" t="inlineStr"/>
+      <c r="AI6" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_1</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr"/>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_1</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr"/>
+      <c r="G7" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H7" s="31" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K7" s="31" t="inlineStr"/>
+      <c r="L7" s="31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O7" s="31" t="inlineStr"/>
+      <c r="P7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q7" s="31" t="inlineStr"/>
+      <c r="R7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S7" s="31" t="inlineStr"/>
+      <c r="T7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U7" s="31" t="inlineStr"/>
+      <c r="V7" s="31" t="inlineStr"/>
+      <c r="W7" s="31" t="inlineStr"/>
+      <c r="X7" s="31" t="inlineStr"/>
+      <c r="Y7" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z7" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA7" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB7" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC7" s="31" t="inlineStr"/>
+      <c r="AD7" s="31" t="inlineStr"/>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr"/>
+      <c r="AG7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH7" s="31" t="inlineStr"/>
+      <c r="AI7" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_2</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr"/>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_2</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr"/>
+      <c r="G8" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H8" s="31" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J8" s="31" t="inlineStr">
+        <is>
+          <t>c_osh_00501_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="K8" s="31" t="inlineStr"/>
+      <c r="L8" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M8" s="31" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="N8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O8" s="31" t="inlineStr"/>
+      <c r="P8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q8" s="31" t="inlineStr"/>
+      <c r="R8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S8" s="31" t="inlineStr"/>
+      <c r="T8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U8" s="31" t="inlineStr"/>
+      <c r="V8" s="31" t="inlineStr"/>
+      <c r="W8" s="31" t="inlineStr"/>
+      <c r="X8" s="31" t="inlineStr"/>
+      <c r="Y8" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z8" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA8" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB8" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC8" s="31" t="inlineStr"/>
+      <c r="AD8" s="31" t="inlineStr"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr"/>
+      <c r="AG8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH8" s="31" t="inlineStr"/>
+      <c r="AI8" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_3</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr"/>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_3</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr"/>
+      <c r="G9" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H9" s="31" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="I9" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>c_osh_00201_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="K9" s="31" t="inlineStr"/>
+      <c r="L9" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M9" s="31" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="N9" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O9" s="31" t="inlineStr"/>
+      <c r="P9" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q9" s="31" t="inlineStr"/>
+      <c r="R9" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S9" s="31" t="inlineStr"/>
+      <c r="T9" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U9" s="31" t="inlineStr"/>
+      <c r="V9" s="31" t="inlineStr"/>
+      <c r="W9" s="31" t="inlineStr"/>
+      <c r="X9" s="31" t="inlineStr"/>
+      <c r="Y9" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z9" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA9" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB9" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="31" t="inlineStr"/>
+      <c r="AD9" s="31" t="inlineStr"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr"/>
+      <c r="AG9" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH9" s="31" t="inlineStr"/>
+      <c r="AI9" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_4</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr"/>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_4</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr"/>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>13000</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J10" s="31" t="inlineStr">
+        <is>
+          <t>c_osh_00401_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="K10" s="31" t="inlineStr"/>
+      <c r="L10" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="31" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="N10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O10" s="31" t="inlineStr"/>
+      <c r="P10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q10" s="31" t="inlineStr"/>
+      <c r="R10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S10" s="31" t="inlineStr"/>
+      <c r="T10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U10" s="31" t="inlineStr"/>
+      <c r="V10" s="31" t="inlineStr"/>
+      <c r="W10" s="31" t="inlineStr"/>
+      <c r="X10" s="31" t="inlineStr"/>
+      <c r="Y10" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z10" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA10" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB10" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="31" t="inlineStr"/>
+      <c r="AD10" s="31" t="inlineStr"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr"/>
+      <c r="AG10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH10" s="31" t="inlineStr"/>
+      <c r="AI10" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_5</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr"/>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_5</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr"/>
+      <c r="G11" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H11" s="31" t="inlineStr">
+        <is>
+          <t>18000</t>
+        </is>
+      </c>
+      <c r="I11" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>c_osh_00301_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="K11" s="31" t="inlineStr"/>
+      <c r="L11" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M11" s="31" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="N11" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O11" s="31" t="inlineStr"/>
+      <c r="P11" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q11" s="31" t="inlineStr"/>
+      <c r="R11" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S11" s="31" t="inlineStr"/>
+      <c r="T11" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U11" s="31" t="inlineStr"/>
+      <c r="V11" s="31" t="inlineStr"/>
+      <c r="W11" s="31" t="inlineStr"/>
+      <c r="X11" s="31" t="inlineStr"/>
+      <c r="Y11" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z11" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA11" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB11" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="31" t="inlineStr"/>
+      <c r="AD11" s="31" t="inlineStr"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr"/>
+      <c r="AG11" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH11" s="31" t="inlineStr"/>
+      <c r="AI11" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -3979,6 +6550,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>ENABLE</t>
+        </is>
+      </c>
+      <c r="B1" s="30" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="30" t="inlineStr">
+        <is>
+          <t>release_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:S48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/domain/tasks/20260311_202700_vd_masterdata_ingame_generation/vd_all/vd_all.xlsx
+++ b/domain/tasks/20260311_202700_vd_masterdata_ingame_generation/vd_all/vd_all.xlsx
@@ -1333,7 +1333,7 @@
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
-          <t>雑魚（共通）</t>
+          <t>雑魚（e_キャラ）</t>
         </is>
       </c>
       <c r="J27" s="2" t="n"/>
@@ -3044,7 +3044,11 @@
       <c r="G40" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="26" t="inlineStr"/>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>開幕5体・序盤テンポ</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
@@ -3077,7 +3081,11 @@
       <c r="G41" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H41" s="26" t="inlineStr"/>
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>500ms間隔×4体</t>
+        </is>
+      </c>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
@@ -3110,7 +3118,11 @@
       <c r="G42" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H42" s="26" t="inlineStr"/>
+      <c r="H42" s="26" t="inlineStr">
+        <is>
+          <t>500ms間隔×4体</t>
+        </is>
+      </c>
       <c r="I42" s="2" t="n"/>
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
@@ -3143,7 +3155,11 @@
       <c r="G43" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H43" s="26" t="inlineStr"/>
+      <c r="H43" s="26" t="inlineStr">
+        <is>
+          <t>500ms間隔×4体</t>
+        </is>
+      </c>
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
@@ -3176,7 +3192,11 @@
       <c r="G44" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H44" s="26" t="inlineStr"/>
+      <c r="H44" s="26" t="inlineStr">
+        <is>
+          <t>500ms間隔×4体</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="n"/>
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
@@ -3521,7 +3541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3647,11 +3667,7 @@
           <t>vd_kai_normal_00001</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
+      <c r="C2" s="31" t="inlineStr"/>
       <c r="D2" s="31" t="inlineStr">
         <is>
           <t>vd_kai_normal_00001</t>
@@ -3675,9 +3691,17 @@
           <t>vd_kai_normal_00001</t>
         </is>
       </c>
-      <c r="K2" s="31" t="inlineStr"/>
+      <c r="K2" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
       <c r="L2" s="31" t="inlineStr"/>
-      <c r="M2" s="31" t="inlineStr"/>
+      <c r="M2" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
       <c r="N2" s="31" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -3716,69 +3740,89 @@
       <c r="U2" s="31" t="inlineStr"/>
       <c r="V2" s="31" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>vd_osh_normal_00001</t>
         </is>
       </c>
-      <c r="C3" s="31" t="inlineStr"/>
-      <c r="D3" s="31" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr"/>
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>vd_osh_normal_00001</t>
         </is>
       </c>
-      <c r="E3" s="31" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>SSE_SBG_003_010</t>
         </is>
       </c>
-      <c r="F3" s="31" t="inlineStr"/>
-      <c r="G3" s="31" t="inlineStr"/>
-      <c r="H3" s="31" t="inlineStr"/>
-      <c r="I3" s="31" t="inlineStr">
+      <c r="F4" s="31" t="inlineStr"/>
+      <c r="G4" s="31" t="inlineStr"/>
+      <c r="H4" s="31" t="inlineStr"/>
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t>vd_osh_normal_00001</t>
         </is>
       </c>
-      <c r="J3" s="31" t="inlineStr">
+      <c r="J4" s="31" t="inlineStr">
         <is>
           <t>vd_osh_normal_00001</t>
         </is>
       </c>
-      <c r="K3" s="31" t="inlineStr"/>
-      <c r="L3" s="31" t="inlineStr"/>
-      <c r="M3" s="31" t="inlineStr"/>
-      <c r="N3" s="31" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="L4" s="31" t="inlineStr"/>
+      <c r="M4" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="N4" s="31" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="O3" s="31" t="inlineStr">
+      <c r="O4" s="31" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="P3" s="31" t="inlineStr">
+      <c r="P4" s="31" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="Q3" s="31" t="inlineStr"/>
-      <c r="R3" s="31" t="inlineStr"/>
-      <c r="S3" s="31" t="inlineStr"/>
-      <c r="T3" s="31" t="inlineStr">
+      <c r="Q4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="S4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="T4" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
       </c>
-      <c r="U3" s="31" t="inlineStr"/>
-      <c r="V3" s="31" t="inlineStr"/>
+      <c r="U4" s="31" t="inlineStr"/>
+      <c r="V4" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3791,7 +3835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3847,7 +3891,11 @@
           <t>100</t>
         </is>
       </c>
-      <c r="D2" s="31" t="inlineStr"/>
+      <c r="D2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="E2" s="31" t="inlineStr"/>
       <c r="F2" s="31" t="inlineStr"/>
       <c r="G2" s="31" t="inlineStr">
@@ -3856,26 +3904,30 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>vd_osh_normal_00001</t>
         </is>
       </c>
-      <c r="C3" s="31" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D3" s="31" t="inlineStr"/>
-      <c r="E3" s="31" t="inlineStr"/>
-      <c r="F3" s="31" t="inlineStr"/>
-      <c r="G3" s="31" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr"/>
+      <c r="F4" s="31" t="inlineStr"/>
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -3892,7 +3944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4188,7 +4240,11 @@
           <t>All</t>
         </is>
       </c>
-      <c r="P2" s="31" t="inlineStr"/>
+      <c r="P2" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
       <c r="Q2" s="31" t="inlineStr">
         <is>
           <t>0.25</t>
@@ -4200,16 +4256,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="T2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T2" s="31" t="inlineStr"/>
+      <c r="U2" s="31" t="inlineStr"/>
       <c r="V2" s="31" t="inlineStr">
         <is>
           <t>All</t>
@@ -4225,7 +4273,11 @@
           <t>All</t>
         </is>
       </c>
-      <c r="Y2" s="31" t="inlineStr"/>
+      <c r="Y2" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
       <c r="Z2" s="31" t="inlineStr">
         <is>
           <t>0.25</t>
@@ -4237,32 +4289,16 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AC2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AF2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AG2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AH2" s="31" t="inlineStr"/>
+      <c r="AC2" s="31" t="inlineStr"/>
+      <c r="AD2" s="31" t="inlineStr"/>
+      <c r="AE2" s="31" t="inlineStr"/>
+      <c r="AF2" s="31" t="inlineStr"/>
+      <c r="AG2" s="31" t="inlineStr"/>
+      <c r="AH2" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
       <c r="AI2" s="31" t="inlineStr">
         <is>
           <t>0.25</t>
@@ -4274,31 +4310,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AO2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AP2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
+      <c r="AL2" s="31" t="inlineStr"/>
+      <c r="AM2" s="31" t="inlineStr"/>
+      <c r="AN2" s="31" t="inlineStr"/>
+      <c r="AO2" s="31" t="inlineStr"/>
+      <c r="AP2" s="31" t="inlineStr"/>
       <c r="AQ2" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
@@ -4381,7 +4397,11 @@
           <t>All</t>
         </is>
       </c>
-      <c r="P3" s="31" t="inlineStr"/>
+      <c r="P3" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
       <c r="Q3" s="31" t="inlineStr">
         <is>
           <t>0.25</t>
@@ -4393,16 +4413,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="T3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T3" s="31" t="inlineStr"/>
+      <c r="U3" s="31" t="inlineStr"/>
       <c r="V3" s="31" t="inlineStr">
         <is>
           <t>All</t>
@@ -4418,7 +4430,11 @@
           <t>All</t>
         </is>
       </c>
-      <c r="Y3" s="31" t="inlineStr"/>
+      <c r="Y3" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
       <c r="Z3" s="31" t="inlineStr">
         <is>
           <t>0.25</t>
@@ -4430,31 +4446,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AC3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AF3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AG3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
+      <c r="AC3" s="31" t="inlineStr"/>
+      <c r="AD3" s="31" t="inlineStr"/>
+      <c r="AE3" s="31" t="inlineStr"/>
+      <c r="AF3" s="31" t="inlineStr"/>
+      <c r="AG3" s="31" t="inlineStr"/>
       <c r="AH3" s="31" t="inlineStr"/>
       <c r="AI3" s="31" t="inlineStr"/>
       <c r="AJ3" s="31" t="inlineStr"/>
@@ -4463,31 +4459,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AO3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AP3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
+      <c r="AL3" s="31" t="inlineStr"/>
+      <c r="AM3" s="31" t="inlineStr"/>
+      <c r="AN3" s="31" t="inlineStr"/>
+      <c r="AO3" s="31" t="inlineStr"/>
+      <c r="AP3" s="31" t="inlineStr"/>
       <c r="AQ3" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
@@ -4570,7 +4546,11 @@
           <t>All</t>
         </is>
       </c>
-      <c r="P4" s="31" t="inlineStr"/>
+      <c r="P4" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
       <c r="Q4" s="31" t="inlineStr">
         <is>
           <t>0.5</t>
@@ -4582,16 +4562,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="T4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T4" s="31" t="inlineStr"/>
+      <c r="U4" s="31" t="inlineStr"/>
       <c r="V4" s="31" t="inlineStr">
         <is>
           <t>All</t>
@@ -4615,31 +4587,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AC4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AF4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AG4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
+      <c r="AC4" s="31" t="inlineStr"/>
+      <c r="AD4" s="31" t="inlineStr"/>
+      <c r="AE4" s="31" t="inlineStr"/>
+      <c r="AF4" s="31" t="inlineStr"/>
+      <c r="AG4" s="31" t="inlineStr"/>
       <c r="AH4" s="31" t="inlineStr"/>
       <c r="AI4" s="31" t="inlineStr"/>
       <c r="AJ4" s="31" t="inlineStr"/>
@@ -4648,169 +4600,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AO4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AP4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
+      <c r="AL4" s="31" t="inlineStr"/>
+      <c r="AM4" s="31" t="inlineStr"/>
+      <c r="AN4" s="31" t="inlineStr"/>
+      <c r="AO4" s="31" t="inlineStr"/>
+      <c r="AP4" s="31" t="inlineStr"/>
       <c r="AQ4" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001_1</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G5" s="31" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="H5" s="31" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I5" s="31" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J5" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="N5" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="O5" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="P5" s="31" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="Q5" s="31" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="R5" s="31" t="inlineStr"/>
-      <c r="S5" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V5" s="31" t="inlineStr"/>
-      <c r="W5" s="31" t="inlineStr"/>
-      <c r="X5" s="31" t="inlineStr"/>
-      <c r="Y5" s="31" t="inlineStr"/>
-      <c r="Z5" s="31" t="inlineStr"/>
-      <c r="AA5" s="31" t="inlineStr"/>
-      <c r="AB5" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AC5" s="31" t="inlineStr"/>
-      <c r="AD5" s="31" t="inlineStr"/>
-      <c r="AE5" s="31" t="inlineStr"/>
-      <c r="AF5" s="31" t="inlineStr"/>
-      <c r="AG5" s="31" t="inlineStr"/>
-      <c r="AH5" s="31" t="inlineStr"/>
-      <c r="AI5" s="31" t="inlineStr"/>
-      <c r="AJ5" s="31" t="inlineStr"/>
-      <c r="AK5" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AL5" s="31" t="inlineStr"/>
-      <c r="AM5" s="31" t="inlineStr"/>
-      <c r="AN5" s="31" t="inlineStr"/>
-      <c r="AO5" s="31" t="inlineStr"/>
-      <c r="AP5" s="31" t="inlineStr"/>
-      <c r="AQ5" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -4824,7 +4619,7 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>vd_osh_normal_00001_2</t>
+          <t>vd_osh_normal_00001_1</t>
         </is>
       </c>
       <c r="C6" s="31" t="inlineStr">
@@ -4834,7 +4629,7 @@
       </c>
       <c r="D6" s="31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" s="31" t="inlineStr">
@@ -4844,7 +4639,7 @@
       </c>
       <c r="F6" s="31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G6" s="31" t="inlineStr">
@@ -4899,7 +4694,7 @@
       </c>
       <c r="Q6" s="31" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="R6" s="31" t="inlineStr"/>
@@ -4908,45 +4703,33 @@
           <t>None</t>
         </is>
       </c>
-      <c r="T6" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U6" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V6" s="31" t="inlineStr"/>
-      <c r="W6" s="31" t="inlineStr"/>
-      <c r="X6" s="31" t="inlineStr"/>
-      <c r="Y6" s="31" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="Z6" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
+      <c r="T6" s="31" t="inlineStr"/>
+      <c r="U6" s="31" t="inlineStr"/>
+      <c r="V6" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W6" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X6" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Y6" s="31" t="inlineStr"/>
+      <c r="Z6" s="31" t="inlineStr"/>
       <c r="AA6" s="31" t="inlineStr"/>
       <c r="AB6" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AC6" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD6" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AC6" s="31" t="inlineStr"/>
+      <c r="AD6" s="31" t="inlineStr"/>
       <c r="AE6" s="31" t="inlineStr"/>
       <c r="AF6" s="31" t="inlineStr"/>
       <c r="AG6" s="31" t="inlineStr"/>
@@ -4977,7 +4760,7 @@
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
-          <t>vd_osh_normal_00001_3</t>
+          <t>vd_osh_normal_00001_2</t>
         </is>
       </c>
       <c r="C7" s="31" t="inlineStr">
@@ -4987,17 +4770,17 @@
       </c>
       <c r="D7" s="31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F7" s="31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G7" s="31" t="inlineStr">
@@ -5007,7 +4790,7 @@
       </c>
       <c r="H7" s="31" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I7" s="31" t="inlineStr">
@@ -5061,19 +4844,23 @@
           <t>None</t>
         </is>
       </c>
-      <c r="T7" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U7" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V7" s="31" t="inlineStr"/>
-      <c r="W7" s="31" t="inlineStr"/>
-      <c r="X7" s="31" t="inlineStr"/>
+      <c r="T7" s="31" t="inlineStr"/>
+      <c r="U7" s="31" t="inlineStr"/>
+      <c r="V7" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W7" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X7" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
       <c r="Y7" s="31" t="inlineStr">
         <is>
           <t>osh_00001</t>
@@ -5090,49 +4877,218 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AC7" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD7" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE7" s="31" t="inlineStr"/>
-      <c r="AF7" s="31" t="inlineStr"/>
-      <c r="AG7" s="31" t="inlineStr"/>
-      <c r="AH7" s="31" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="AI7" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
+      <c r="AC7" s="31" t="inlineStr"/>
+      <c r="AD7" s="31" t="inlineStr"/>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AG7" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AH7" s="31" t="inlineStr"/>
+      <c r="AI7" s="31" t="inlineStr"/>
       <c r="AJ7" s="31" t="inlineStr"/>
       <c r="AK7" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AL7" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM7" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AL7" s="31" t="inlineStr"/>
+      <c r="AM7" s="31" t="inlineStr"/>
       <c r="AN7" s="31" t="inlineStr"/>
       <c r="AO7" s="31" t="inlineStr"/>
       <c r="AP7" s="31" t="inlineStr"/>
       <c r="AQ7" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_3</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G8" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="H8" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="N8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="P8" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="Q8" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="R8" s="31" t="inlineStr"/>
+      <c r="S8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T8" s="31" t="inlineStr"/>
+      <c r="U8" s="31" t="inlineStr"/>
+      <c r="V8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Y8" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="Z8" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA8" s="31" t="inlineStr"/>
+      <c r="AB8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC8" s="31" t="inlineStr"/>
+      <c r="AD8" s="31" t="inlineStr"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AG8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AH8" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="AI8" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AJ8" s="31" t="inlineStr"/>
+      <c r="AK8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL8" s="31" t="inlineStr"/>
+      <c r="AM8" s="31" t="inlineStr"/>
+      <c r="AN8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AO8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AP8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="AQ8" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -5149,7 +5105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5351,7 +5307,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F2" s="31" t="inlineStr"/>
+      <c r="F2" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
       <c r="G2" s="31" t="inlineStr">
         <is>
           <t>ElapsedTime</t>
@@ -5378,34 +5338,66 @@
           <t>5</t>
         </is>
       </c>
-      <c r="M2" s="31" t="inlineStr"/>
+      <c r="M2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N2" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O2" s="31" t="inlineStr"/>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="P2" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q2" s="31" t="inlineStr"/>
+      <c r="Q2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R2" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="S2" s="31" t="inlineStr"/>
+      <c r="S2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="T2" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="U2" s="31" t="inlineStr"/>
-      <c r="V2" s="31" t="inlineStr"/>
-      <c r="W2" s="31" t="inlineStr"/>
-      <c r="X2" s="31" t="inlineStr"/>
+      <c r="U2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Y2" s="31" t="inlineStr">
         <is>
           <t>Default</t>
@@ -5437,7 +5429,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AF2" s="31" t="inlineStr"/>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AG2" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -5472,7 +5468,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="F3" s="31" t="inlineStr"/>
+      <c r="F3" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
       <c r="G3" s="31" t="inlineStr">
         <is>
           <t>ElapsedTime</t>
@@ -5499,34 +5499,66 @@
           <t>4</t>
         </is>
       </c>
-      <c r="M3" s="31" t="inlineStr"/>
+      <c r="M3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N3" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O3" s="31" t="inlineStr"/>
+      <c r="O3" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="P3" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q3" s="31" t="inlineStr"/>
+      <c r="Q3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R3" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="S3" s="31" t="inlineStr"/>
+      <c r="S3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="T3" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="U3" s="31" t="inlineStr"/>
-      <c r="V3" s="31" t="inlineStr"/>
-      <c r="W3" s="31" t="inlineStr"/>
-      <c r="X3" s="31" t="inlineStr"/>
+      <c r="U3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Y3" s="31" t="inlineStr">
         <is>
           <t>Default</t>
@@ -5558,7 +5590,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AF3" s="31" t="inlineStr"/>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AG3" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -5593,7 +5629,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="31" t="inlineStr"/>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
       <c r="G4" s="31" t="inlineStr">
         <is>
           <t>ElapsedTime</t>
@@ -5620,34 +5660,66 @@
           <t>5</t>
         </is>
       </c>
-      <c r="M4" s="31" t="inlineStr"/>
+      <c r="M4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N4" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O4" s="31" t="inlineStr"/>
+      <c r="O4" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="P4" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q4" s="31" t="inlineStr"/>
+      <c r="Q4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R4" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="S4" s="31" t="inlineStr"/>
+      <c r="S4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="T4" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="U4" s="31" t="inlineStr"/>
-      <c r="V4" s="31" t="inlineStr"/>
-      <c r="W4" s="31" t="inlineStr"/>
-      <c r="X4" s="31" t="inlineStr"/>
+      <c r="U4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Y4" s="31" t="inlineStr">
         <is>
           <t>Default</t>
@@ -5679,7 +5751,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AF4" s="31" t="inlineStr"/>
+      <c r="AF4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AG4" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -5714,7 +5790,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F5" s="31" t="inlineStr"/>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
       <c r="G5" s="31" t="inlineStr">
         <is>
           <t>ElapsedTime</t>
@@ -5741,34 +5821,66 @@
           <t>4</t>
         </is>
       </c>
-      <c r="M5" s="31" t="inlineStr"/>
+      <c r="M5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N5" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O5" s="31" t="inlineStr"/>
+      <c r="O5" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="P5" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q5" s="31" t="inlineStr"/>
+      <c r="Q5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R5" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="S5" s="31" t="inlineStr"/>
+      <c r="S5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="T5" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="U5" s="31" t="inlineStr"/>
-      <c r="V5" s="31" t="inlineStr"/>
-      <c r="W5" s="31" t="inlineStr"/>
-      <c r="X5" s="31" t="inlineStr"/>
+      <c r="U5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Y5" s="31" t="inlineStr">
         <is>
           <t>Default</t>
@@ -5800,7 +5912,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AF5" s="31" t="inlineStr"/>
+      <c r="AF5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AG5" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -5835,7 +5951,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F6" s="31" t="inlineStr"/>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
       <c r="G6" s="31" t="inlineStr">
         <is>
           <t>ElapsedTime</t>
@@ -5862,34 +5982,66 @@
           <t>4</t>
         </is>
       </c>
-      <c r="M6" s="31" t="inlineStr"/>
+      <c r="M6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N6" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O6" s="31" t="inlineStr"/>
+      <c r="O6" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="P6" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q6" s="31" t="inlineStr"/>
+      <c r="Q6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R6" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="S6" s="31" t="inlineStr"/>
+      <c r="S6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="T6" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="U6" s="31" t="inlineStr"/>
-      <c r="V6" s="31" t="inlineStr"/>
-      <c r="W6" s="31" t="inlineStr"/>
-      <c r="X6" s="31" t="inlineStr"/>
+      <c r="U6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Y6" s="31" t="inlineStr">
         <is>
           <t>Default</t>
@@ -5921,7 +6073,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AF6" s="31" t="inlineStr"/>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AG6" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -5934,127 +6090,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001_1</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="D7" s="31" t="inlineStr"/>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001_1</t>
-        </is>
-      </c>
-      <c r="F7" s="31" t="inlineStr"/>
-      <c r="G7" s="31" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="H7" s="31" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="I7" s="31" t="inlineStr">
-        <is>
-          <t>SummonEnemy</t>
-        </is>
-      </c>
-      <c r="J7" s="31" t="inlineStr">
-        <is>
-          <t>e_glo_00001_vd_Normal_Colorless</t>
-        </is>
-      </c>
-      <c r="K7" s="31" t="inlineStr"/>
-      <c r="L7" s="31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M7" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O7" s="31" t="inlineStr"/>
-      <c r="P7" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q7" s="31" t="inlineStr"/>
-      <c r="R7" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S7" s="31" t="inlineStr"/>
-      <c r="T7" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U7" s="31" t="inlineStr"/>
-      <c r="V7" s="31" t="inlineStr"/>
-      <c r="W7" s="31" t="inlineStr"/>
-      <c r="X7" s="31" t="inlineStr"/>
-      <c r="Y7" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="Z7" s="31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA7" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AB7" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AC7" s="31" t="inlineStr"/>
-      <c r="AD7" s="31" t="inlineStr"/>
-      <c r="AE7" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF7" s="31" t="inlineStr"/>
-      <c r="AG7" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AH7" s="31" t="inlineStr"/>
-      <c r="AI7" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
         <is>
@@ -6063,7 +6098,7 @@
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>vd_osh_normal_00001_2</t>
+          <t>vd_osh_normal_00001_1</t>
         </is>
       </c>
       <c r="C8" s="31" t="inlineStr">
@@ -6074,7 +6109,7 @@
       <c r="D8" s="31" t="inlineStr"/>
       <c r="E8" s="31" t="inlineStr">
         <is>
-          <t>vd_osh_normal_00001_2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" s="31" t="inlineStr"/>
@@ -6085,7 +6120,7 @@
       </c>
       <c r="H8" s="31" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>250</t>
         </is>
       </c>
       <c r="I8" s="31" t="inlineStr">
@@ -6095,18 +6130,18 @@
       </c>
       <c r="J8" s="31" t="inlineStr">
         <is>
-          <t>c_osh_00501_vd_Normal_Green</t>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
         </is>
       </c>
       <c r="K8" s="31" t="inlineStr"/>
       <c r="L8" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M8" s="31" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N8" s="31" t="inlineStr">
@@ -6114,28 +6149,56 @@
           <t>None</t>
         </is>
       </c>
-      <c r="O8" s="31" t="inlineStr"/>
+      <c r="O8" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="P8" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q8" s="31" t="inlineStr"/>
+      <c r="Q8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R8" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="S8" s="31" t="inlineStr"/>
+      <c r="S8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="T8" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="U8" s="31" t="inlineStr"/>
-      <c r="V8" s="31" t="inlineStr"/>
-      <c r="W8" s="31" t="inlineStr"/>
-      <c r="X8" s="31" t="inlineStr"/>
+      <c r="U8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Y8" s="31" t="inlineStr">
         <is>
           <t>Default</t>
@@ -6156,14 +6219,22 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="AC8" s="31" t="inlineStr"/>
+      <c r="AC8" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="AD8" s="31" t="inlineStr"/>
       <c r="AE8" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AF8" s="31" t="inlineStr"/>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AG8" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -6184,7 +6255,7 @@
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>vd_osh_normal_00001_3</t>
+          <t>vd_osh_normal_00001_2</t>
         </is>
       </c>
       <c r="C9" s="31" t="inlineStr">
@@ -6195,7 +6266,7 @@
       <c r="D9" s="31" t="inlineStr"/>
       <c r="E9" s="31" t="inlineStr">
         <is>
-          <t>vd_osh_normal_00001_3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" s="31" t="inlineStr"/>
@@ -6206,7 +6277,7 @@
       </c>
       <c r="H9" s="31" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="I9" s="31" t="inlineStr">
@@ -6216,7 +6287,7 @@
       </c>
       <c r="J9" s="31" t="inlineStr">
         <is>
-          <t>c_osh_00201_vd_Normal_Green</t>
+          <t>c_osh_00501_vd_Normal_Green</t>
         </is>
       </c>
       <c r="K9" s="31" t="inlineStr"/>
@@ -6235,28 +6306,56 @@
           <t>None</t>
         </is>
       </c>
-      <c r="O9" s="31" t="inlineStr"/>
+      <c r="O9" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="P9" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q9" s="31" t="inlineStr"/>
+      <c r="Q9" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R9" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="S9" s="31" t="inlineStr"/>
+      <c r="S9" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="T9" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="U9" s="31" t="inlineStr"/>
-      <c r="V9" s="31" t="inlineStr"/>
-      <c r="W9" s="31" t="inlineStr"/>
-      <c r="X9" s="31" t="inlineStr"/>
+      <c r="U9" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V9" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Y9" s="31" t="inlineStr">
         <is>
           <t>Default</t>
@@ -6277,14 +6376,22 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="AC9" s="31" t="inlineStr"/>
+      <c r="AC9" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="AD9" s="31" t="inlineStr"/>
       <c r="AE9" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AF9" s="31" t="inlineStr"/>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AG9" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -6305,7 +6412,7 @@
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>vd_osh_normal_00001_4</t>
+          <t>vd_osh_normal_00001_3</t>
         </is>
       </c>
       <c r="C10" s="31" t="inlineStr">
@@ -6316,7 +6423,7 @@
       <c r="D10" s="31" t="inlineStr"/>
       <c r="E10" s="31" t="inlineStr">
         <is>
-          <t>vd_osh_normal_00001_4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F10" s="31" t="inlineStr"/>
@@ -6327,7 +6434,7 @@
       </c>
       <c r="H10" s="31" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="I10" s="31" t="inlineStr">
@@ -6337,7 +6444,7 @@
       </c>
       <c r="J10" s="31" t="inlineStr">
         <is>
-          <t>c_osh_00401_vd_Normal_Green</t>
+          <t>c_osh_00201_vd_Normal_Green</t>
         </is>
       </c>
       <c r="K10" s="31" t="inlineStr"/>
@@ -6356,28 +6463,56 @@
           <t>None</t>
         </is>
       </c>
-      <c r="O10" s="31" t="inlineStr"/>
+      <c r="O10" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="P10" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q10" s="31" t="inlineStr"/>
+      <c r="Q10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R10" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="S10" s="31" t="inlineStr"/>
+      <c r="S10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="T10" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="U10" s="31" t="inlineStr"/>
-      <c r="V10" s="31" t="inlineStr"/>
-      <c r="W10" s="31" t="inlineStr"/>
-      <c r="X10" s="31" t="inlineStr"/>
+      <c r="U10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Y10" s="31" t="inlineStr">
         <is>
           <t>Default</t>
@@ -6398,14 +6533,22 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="AC10" s="31" t="inlineStr"/>
+      <c r="AC10" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="AD10" s="31" t="inlineStr"/>
       <c r="AE10" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AF10" s="31" t="inlineStr"/>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AG10" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -6426,7 +6569,7 @@
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>vd_osh_normal_00001_5</t>
+          <t>vd_osh_normal_00001_4</t>
         </is>
       </c>
       <c r="C11" s="31" t="inlineStr">
@@ -6437,7 +6580,7 @@
       <c r="D11" s="31" t="inlineStr"/>
       <c r="E11" s="31" t="inlineStr">
         <is>
-          <t>vd_osh_normal_00001_5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F11" s="31" t="inlineStr"/>
@@ -6448,7 +6591,7 @@
       </c>
       <c r="H11" s="31" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="I11" s="31" t="inlineStr">
@@ -6458,7 +6601,7 @@
       </c>
       <c r="J11" s="31" t="inlineStr">
         <is>
-          <t>c_osh_00301_vd_Normal_Green</t>
+          <t>c_osh_00401_vd_Normal_Green</t>
         </is>
       </c>
       <c r="K11" s="31" t="inlineStr"/>
@@ -6477,28 +6620,56 @@
           <t>None</t>
         </is>
       </c>
-      <c r="O11" s="31" t="inlineStr"/>
+      <c r="O11" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="P11" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q11" s="31" t="inlineStr"/>
+      <c r="Q11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R11" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="S11" s="31" t="inlineStr"/>
+      <c r="S11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="T11" s="31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="U11" s="31" t="inlineStr"/>
-      <c r="V11" s="31" t="inlineStr"/>
-      <c r="W11" s="31" t="inlineStr"/>
-      <c r="X11" s="31" t="inlineStr"/>
+      <c r="U11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Y11" s="31" t="inlineStr">
         <is>
           <t>Default</t>
@@ -6519,14 +6690,22 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="AC11" s="31" t="inlineStr"/>
+      <c r="AC11" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="AD11" s="31" t="inlineStr"/>
       <c r="AE11" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AF11" s="31" t="inlineStr"/>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AG11" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -6534,6 +6713,163 @@
       </c>
       <c r="AH11" s="31" t="inlineStr"/>
       <c r="AI11" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_5</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr"/>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr"/>
+      <c r="G12" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H12" s="31" t="inlineStr">
+        <is>
+          <t>18000</t>
+        </is>
+      </c>
+      <c r="I12" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J12" s="31" t="inlineStr">
+        <is>
+          <t>c_osh_00301_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="K12" s="31" t="inlineStr"/>
+      <c r="L12" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M12" s="31" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="N12" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O12" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P12" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R12" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y12" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z12" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA12" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB12" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD12" s="31" t="inlineStr"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG12" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH12" s="31" t="inlineStr"/>
+      <c r="AI12" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -6550,7 +6886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6587,18 +6923,18 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>vd_osh_normal_00001</t>
         </is>
       </c>
-      <c r="C3" s="31" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>

--- a/domain/tasks/20260311_202700_vd_masterdata_ingame_generation/vd_all/vd_all.xlsx
+++ b/domain/tasks/20260311_202700_vd_masterdata_ingame_generation/vd_all/vd_all.xlsx
@@ -7,17 +7,16 @@
   </bookViews>
   <sheets>
     <sheet name="ブロック基礎設計_vd_kai_normal_00001" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ブロック基礎設計_vd_osh_normal_00001" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MstInGame" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MstEnemyOutpost" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="MstKomaLine" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MstAutoPlayerSequence" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="MstPage" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MstEnemyStageParameter" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MstInGame" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MstEnemyOutpost" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MstKomaLine" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MstAutoPlayerSequence" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MstPage" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MstEnemyStageParameter" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
-    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2053,1485 +2052,234 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3.1640625" customWidth="1" min="1" max="1"/>
-    <col width="19.1640625" customWidth="1" min="2" max="2"/>
-    <col width="18.83203125" customWidth="1" min="3" max="10"/>
-    <col width="3.1640625" customWidth="1" min="11" max="13"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>ブロック基礎設計_vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="n"/>
-      <c r="D1" s="5" t="n"/>
-      <c r="E1" s="5" t="n"/>
-      <c r="F1" s="5" t="n"/>
-      <c r="G1" s="5" t="n"/>
-      <c r="H1" s="5" t="n"/>
-      <c r="I1" s="5" t="n"/>
-      <c r="J1" s="5" t="n"/>
-    </row>
-    <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="6" t="n"/>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="6" t="n"/>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="6" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="6" t="n"/>
-      <c r="J2" s="6" t="n"/>
-      <c r="K2" s="6" t="n"/>
-      <c r="L2" s="6" t="n"/>
-      <c r="M2" s="6" t="n"/>
-    </row>
-    <row r="3" ht="13" customHeight="1">
-      <c r="A3" s="6" t="n"/>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>■要件テキスト</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-      <c r="I3" s="6" t="n"/>
-      <c r="J3" s="6" t="n"/>
-      <c r="K3" s="6" t="n"/>
-      <c r="L3" s="6" t="n"/>
-      <c r="M3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="186" customHeight="1">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>ファントム（Colorless/Attack・HP5,000・ATK100・SPD34）が開幕250msに5体で序盤テンポを作り、その後【推しの子】Green属性キャラ4種（c_osh_00501→c_osh_00201→c_osh_00401→c_osh_00301の順）がHP10,000〜50,000で続く5波構成、合計21体。ファントムは`e_`キャラのため瞬時まとめ召喚、c_キャラは`summon_interval=500ms`で1体ずつ間隔を空けて召喚する。
-コマは3行固定。row1=2等分2コマ（0.50, 0.50）・row2=右広い3コマ（0.50, 0.25, 0.25）・row3=4等分4コマ（0.25×4）。コマアセット: osh_00001（back_ground_offset: -1.0）。
-UR対抗キャラ「B小町不動のセンター アイ」（chara_osh_00001）対抗。序盤ファントムで多属性対応を試しつつ、中盤以降はGreen属性対策コマが主軸となる設計。</t>
-        </is>
-      </c>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="27" t="n"/>
-      <c r="J4" s="28" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>■基本情報</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>⇩ボスブロックのみに記載する</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
-    </row>
-    <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>インゲームID</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>ブロック種別</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>敵ゲートHP</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>コマ行数</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>グループ切り替え</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
-        <is>
-          <t>シーケンス行数</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>リリースキー</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="26" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="E9" s="26" t="inlineStr">
-        <is>
-          <t>3行</t>
-        </is>
-      </c>
-      <c r="F9" s="26" t="inlineStr">
-        <is>
-          <t>なし（デフォルトグループのみ）</t>
-        </is>
-      </c>
-      <c r="G9" s="26" t="inlineStr">
-        <is>
-          <t>5行</t>
-        </is>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>202604010</v>
-      </c>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-    </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>※ノーマルブロックは3フロア固定で、ボスブロックは1フロア固定</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-    </row>
-    <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-    </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>■コマ効果</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-    </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>行</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>コマ数</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>コマアセット</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>コマ効果</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>レイアウト幅</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-    </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>行1</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>2コマ</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="E14" s="26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F14" s="26" t="inlineStr">
-        <is>
-          <t>0.5 / 0.5</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
-    </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>行2</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>3コマ</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="E15" s="26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F15" s="26" t="inlineStr">
-        <is>
-          <t>0.5 / 0.25 / 0.25</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
-    </row>
-    <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>行3</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>4コマ</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F16" s="26" t="inlineStr">
-        <is>
-          <t>0.25 / 0.25 / 0.25 / 0.25</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-    </row>
-    <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-    </row>
-    <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>コマ効果1</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>効果時間</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>効果数値</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-    </row>
-    <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
-    </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-    </row>
-    <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
-    </row>
-    <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
-    </row>
-    <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
-    </row>
-    <row r="24" ht="13" customHeight="1">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>■登場敵パラメータ</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="n"/>
-    </row>
-    <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>敵ID</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>キャラ名</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>属性</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>ロール</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>攻撃</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>移動速度</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>役割</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="n"/>
-      <c r="M25" s="2" t="n"/>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="26" t="inlineStr">
-        <is>
-          <t>e_glo_00001_vd_Normal_Colorless</t>
-        </is>
-      </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>ファントム</t>
-        </is>
-      </c>
-      <c r="D26" s="26" t="inlineStr">
-        <is>
-          <t>Colorless（無属性）</t>
-        </is>
-      </c>
-      <c r="E26" s="26" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="F26" s="29" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G26" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="H26" s="26" t="n">
-        <v>34</v>
-      </c>
-      <c r="I26" s="26" t="inlineStr">
-        <is>
-          <t>雑魚（e_キャラ）</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="26" t="inlineStr">
-        <is>
-          <t>c_osh_00501_vd_Normal_Green</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>黒川あかね</t>
-        </is>
-      </c>
-      <c r="D27" s="26" t="inlineStr">
-        <is>
-          <t>Green（緑属性）</t>
-        </is>
-      </c>
-      <c r="E27" s="26" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="F27" s="29" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G27" s="26" t="n">
-        <v>300</v>
-      </c>
-      <c r="H27" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="26" t="inlineStr">
-        <is>
-          <t>雑魚（c_キャラ）</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="n"/>
-      <c r="M27" s="2" t="n"/>
-    </row>
-    <row r="28" ht="13" customHeight="1">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>c_osh_00201_vd_Normal_Green</t>
-        </is>
-      </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>星野 ルビー</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="inlineStr">
-        <is>
-          <t>Green（緑属性）</t>
-        </is>
-      </c>
-      <c r="E28" s="26" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="F28" s="29" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G28" s="26" t="n">
-        <v>300</v>
-      </c>
-      <c r="H28" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="26" t="inlineStr">
-        <is>
-          <t>雑魚（c_キャラ）</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
-    </row>
-    <row r="29" ht="13" customHeight="1">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>c_osh_00401_vd_Normal_Green</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>有馬 かな</t>
-        </is>
-      </c>
-      <c r="D29" s="26" t="inlineStr">
-        <is>
-          <t>Green（緑属性）</t>
-        </is>
-      </c>
-      <c r="E29" s="26" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="F29" s="29" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G29" s="26" t="n">
-        <v>300</v>
-      </c>
-      <c r="H29" s="26" t="n">
-        <v>32</v>
-      </c>
-      <c r="I29" s="26" t="inlineStr">
-        <is>
-          <t>雑魚（c_キャラ）</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
-    </row>
-    <row r="30" ht="13" customHeight="1">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="26" t="inlineStr">
-        <is>
-          <t>c_osh_00301_vd_Normal_Green</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>MEMちょ</t>
-        </is>
-      </c>
-      <c r="D30" s="26" t="inlineStr">
-        <is>
-          <t>Green（緑属性）</t>
-        </is>
-      </c>
-      <c r="E30" s="26" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="F30" s="29" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G30" s="26" t="n">
-        <v>300</v>
-      </c>
-      <c r="H30" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="26" t="inlineStr">
-        <is>
-          <t>雑魚（c_キャラ）</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
-    </row>
-    <row r="31" ht="13" customHeight="1">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
-    </row>
-    <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
-    </row>
-    <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
-    </row>
-    <row r="34" ht="13" customHeight="1">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="11" t="n"/>
-      <c r="I34" s="9" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-    </row>
-    <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
-    </row>
-    <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
-    </row>
-    <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
-    </row>
-    <row r="38" ht="13" customHeight="1">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>■シーケンス構成</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
-    </row>
-    <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>行番号</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>トリガー種別</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>条件値（ms）</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>敵ID</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>キャラ名</t>
-        </is>
-      </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>体数</t>
-        </is>
-      </c>
-      <c r="H39" s="1" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="26" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="D40" s="26" t="n">
-        <v>250</v>
-      </c>
-      <c r="E40" s="26" t="inlineStr">
-        <is>
-          <t>e_glo_00001_vd_Normal_Colorless</t>
-        </is>
-      </c>
-      <c r="F40" s="26" t="inlineStr">
-        <is>
-          <t>ファントム</t>
-        </is>
-      </c>
-      <c r="G40" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="H40" s="26" t="inlineStr">
-        <is>
-          <t>開幕5体・序盤テンポ</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="D41" s="26" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E41" s="26" t="inlineStr">
-        <is>
-          <t>c_osh_00501_vd_Normal_Green</t>
-        </is>
-      </c>
-      <c r="F41" s="26" t="inlineStr">
-        <is>
-          <t>黒川あかね</t>
-        </is>
-      </c>
-      <c r="G41" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="H41" s="26" t="inlineStr">
-        <is>
-          <t>500ms間隔×4体</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n"/>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="D42" s="29" t="n">
-        <v>8000</v>
-      </c>
-      <c r="E42" s="26" t="inlineStr">
-        <is>
-          <t>c_osh_00201_vd_Normal_Green</t>
-        </is>
-      </c>
-      <c r="F42" s="26" t="inlineStr">
-        <is>
-          <t>星野 ルビー</t>
-        </is>
-      </c>
-      <c r="G42" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="H42" s="26" t="inlineStr">
-        <is>
-          <t>500ms間隔×4体</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="n"/>
-      <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n"/>
-    </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="D43" s="29" t="n">
-        <v>13000</v>
-      </c>
-      <c r="E43" s="26" t="inlineStr">
-        <is>
-          <t>c_osh_00401_vd_Normal_Green</t>
-        </is>
-      </c>
-      <c r="F43" s="26" t="inlineStr">
-        <is>
-          <t>有馬 かな</t>
-        </is>
-      </c>
-      <c r="G43" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="H43" s="26" t="inlineStr">
-        <is>
-          <t>500ms間隔×4体</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="n"/>
-      <c r="M43" s="2" t="n"/>
-    </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="D44" s="29" t="n">
-        <v>18000</v>
-      </c>
-      <c r="E44" s="26" t="inlineStr">
-        <is>
-          <t>c_osh_00301_vd_Normal_Green</t>
-        </is>
-      </c>
-      <c r="F44" s="26" t="inlineStr">
-        <is>
-          <t>MEMちょ</t>
-        </is>
-      </c>
-      <c r="G44" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="H44" s="26" t="inlineStr">
-        <is>
-          <t>500ms間隔×4体</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
-    </row>
-    <row r="45" ht="13" customHeight="1">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="11" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n"/>
-    </row>
-    <row r="46" ht="13" customHeight="1">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="11" t="n"/>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="12" t="n"/>
-      <c r="F46" s="11" t="n"/>
-      <c r="G46" s="11" t="n"/>
-      <c r="H46" s="11" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="13" customHeight="1">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="11" t="n"/>
-      <c r="D47" s="11" t="n"/>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="11" t="n"/>
-      <c r="G47" s="11" t="n"/>
-      <c r="H47" s="11" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="n"/>
-    </row>
-    <row r="48" ht="13" customHeight="1">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="11" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="12" t="n"/>
-      <c r="F48" s="11" t="n"/>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="11" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n"/>
-      <c r="L48" s="2" t="n"/>
-      <c r="M48" s="2" t="n"/>
-    </row>
-    <row r="49" ht="13" customHeight="1">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="11" t="n"/>
-      <c r="C49" s="11" t="n"/>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="12" t="n"/>
-      <c r="F49" s="11" t="n"/>
-      <c r="G49" s="11" t="n"/>
-      <c r="H49" s="11" t="n"/>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="n"/>
-      <c r="L49" s="2" t="n"/>
-      <c r="M49" s="2" t="n"/>
-    </row>
-    <row r="50" ht="13" customHeight="1">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="11" t="n"/>
-      <c r="C50" s="11" t="n"/>
-      <c r="D50" s="11" t="n"/>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="11" t="n"/>
-      <c r="G50" s="11" t="n"/>
-      <c r="H50" s="11" t="n"/>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="2" t="n"/>
-      <c r="K50" s="2" t="n"/>
-      <c r="L50" s="2" t="n"/>
-      <c r="M50" s="2" t="n"/>
-    </row>
-    <row r="51" ht="13" customHeight="1">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="11" t="n"/>
-      <c r="C51" s="11" t="n"/>
-      <c r="D51" s="15" t="n"/>
-      <c r="E51" s="12" t="n"/>
-      <c r="F51" s="11" t="n"/>
-      <c r="G51" s="11" t="n"/>
-      <c r="H51" s="11" t="n"/>
-      <c r="I51" s="2" t="n"/>
-      <c r="J51" s="2" t="n"/>
-      <c r="K51" s="2" t="n"/>
-      <c r="L51" s="2" t="n"/>
-      <c r="M51" s="2" t="n"/>
-    </row>
-    <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="2" t="n"/>
-      <c r="B52" s="11" t="n"/>
-      <c r="C52" s="11" t="n"/>
-      <c r="D52" s="15" t="n"/>
-      <c r="E52" s="12" t="n"/>
-      <c r="F52" s="11" t="n"/>
-      <c r="G52" s="11" t="n"/>
-      <c r="H52" s="11" t="n"/>
-      <c r="I52" s="2" t="n"/>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="n"/>
-      <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n"/>
-    </row>
-    <row r="53" ht="13" customHeight="1">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="11" t="n"/>
-      <c r="C53" s="11" t="n"/>
-      <c r="D53" s="15" t="n"/>
-      <c r="E53" s="12" t="n"/>
-      <c r="F53" s="11" t="n"/>
-      <c r="G53" s="11" t="n"/>
-      <c r="H53" s="11" t="n"/>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="n"/>
-      <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="n"/>
-    </row>
-    <row r="54" ht="13" customHeight="1">
-      <c r="A54" s="16" t="n"/>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="16" t="n"/>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
-      <c r="G54" s="16" t="n"/>
-      <c r="H54" s="16" t="n"/>
-      <c r="I54" s="16" t="n"/>
-      <c r="J54" s="16" t="n"/>
-      <c r="K54" s="16" t="n"/>
-      <c r="L54" s="16" t="n"/>
-      <c r="M54" s="16" t="n"/>
-    </row>
-    <row r="55" ht="13" customHeight="1">
-      <c r="A55" s="16" t="n"/>
-      <c r="B55" s="16" t="n"/>
-      <c r="C55" s="16" t="n"/>
-      <c r="D55" s="16" t="n"/>
-      <c r="E55" s="16" t="n"/>
-      <c r="F55" s="16" t="n"/>
-      <c r="G55" s="16" t="n"/>
-      <c r="H55" s="16" t="n"/>
-      <c r="I55" s="16" t="n"/>
-      <c r="J55" s="16" t="n"/>
-      <c r="K55" s="16" t="n"/>
-      <c r="L55" s="16" t="n"/>
-      <c r="M55" s="16" t="n"/>
-    </row>
-    <row r="56" ht="13" customHeight="1">
-      <c r="A56" s="16" t="n"/>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>■ステージ説明文</t>
-        </is>
-      </c>
-      <c r="C56" s="16" t="n"/>
-      <c r="D56" s="16" t="n"/>
-      <c r="E56" s="16" t="n"/>
-      <c r="F56" s="16" t="n"/>
-      <c r="G56" s="16" t="n"/>
-      <c r="H56" s="16" t="n"/>
-      <c r="I56" s="16" t="n"/>
-      <c r="J56" s="16" t="n"/>
-      <c r="K56" s="16" t="n"/>
-      <c r="L56" s="16" t="n"/>
-      <c r="M56" s="16" t="n"/>
-    </row>
-    <row r="57" ht="13" customHeight="1">
-      <c r="A57" s="16" t="n"/>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D57" s="27" t="n"/>
-      <c r="E57" s="27" t="n"/>
-      <c r="F57" s="27" t="n"/>
-      <c r="G57" s="28" t="n"/>
-      <c r="H57" s="16" t="n"/>
-      <c r="I57" s="16" t="n"/>
-      <c r="J57" s="16" t="n"/>
-      <c r="K57" s="16" t="n"/>
-      <c r="L57" s="16" t="n"/>
-      <c r="M57" s="16" t="n"/>
-    </row>
-    <row r="58" ht="13" customHeight="1">
-      <c r="A58" s="16" t="n"/>
-      <c r="B58" s="18" t="inlineStr">
-        <is>
-          <t>バトルヒント</t>
-        </is>
-      </c>
-      <c r="C58" s="26" t="inlineStr"/>
-      <c r="D58" s="27" t="n"/>
-      <c r="E58" s="27" t="n"/>
-      <c r="F58" s="27" t="n"/>
-      <c r="G58" s="28" t="n"/>
-      <c r="H58" s="16" t="n"/>
-      <c r="I58" s="16" t="n"/>
-      <c r="J58" s="16" t="n"/>
-      <c r="K58" s="16" t="n"/>
-      <c r="L58" s="16" t="n"/>
-      <c r="M58" s="16" t="n"/>
-    </row>
-    <row r="59" ht="13" customHeight="1">
-      <c r="A59" s="16" t="n"/>
-      <c r="B59" s="18" t="inlineStr">
-        <is>
-          <t>ステージ説明文</t>
-        </is>
-      </c>
-      <c r="C59" s="26" t="inlineStr"/>
-      <c r="D59" s="27" t="n"/>
-      <c r="E59" s="27" t="n"/>
-      <c r="F59" s="27" t="n"/>
-      <c r="G59" s="28" t="n"/>
-      <c r="H59" s="16" t="n"/>
-      <c r="I59" s="16" t="n"/>
-      <c r="J59" s="16" t="n"/>
-      <c r="K59" s="16" t="n"/>
-      <c r="L59" s="16" t="n"/>
-      <c r="M59" s="16" t="n"/>
-    </row>
-    <row r="60" ht="13" customHeight="1">
-      <c r="A60" s="16" t="n"/>
-      <c r="B60" s="16" t="n"/>
-      <c r="C60" s="16" t="n"/>
-      <c r="D60" s="16" t="n"/>
-      <c r="E60" s="16" t="n"/>
-      <c r="F60" s="16" t="n"/>
-      <c r="G60" s="16" t="n"/>
-      <c r="H60" s="16" t="n"/>
-      <c r="I60" s="16" t="n"/>
-      <c r="J60" s="16" t="n"/>
-      <c r="K60" s="16" t="n"/>
-      <c r="L60" s="16" t="n"/>
-      <c r="M60" s="16" t="n"/>
-    </row>
-    <row r="61" ht="13" customHeight="1">
-      <c r="A61" s="19" t="n"/>
-      <c r="B61" s="19" t="n"/>
-      <c r="C61" s="19" t="n"/>
-      <c r="D61" s="19" t="n"/>
-      <c r="E61" s="19" t="n"/>
-      <c r="F61" s="19" t="n"/>
-      <c r="G61" s="19" t="n"/>
-      <c r="H61" s="19" t="n"/>
-      <c r="I61" s="19" t="n"/>
-      <c r="J61" s="19" t="n"/>
-      <c r="K61" s="19" t="n"/>
-      <c r="L61" s="19" t="n"/>
-      <c r="M61" s="19" t="n"/>
-    </row>
-    <row r="62" ht="13" customHeight="1">
-      <c r="A62" s="19" t="n"/>
-      <c r="B62" s="19" t="n"/>
-      <c r="C62" s="19" t="n"/>
-      <c r="D62" s="19" t="n"/>
-      <c r="E62" s="19" t="n"/>
-      <c r="F62" s="19" t="n"/>
-      <c r="G62" s="19" t="n"/>
-      <c r="H62" s="19" t="n"/>
-      <c r="I62" s="19" t="n"/>
-      <c r="J62" s="19" t="n"/>
-      <c r="K62" s="19" t="n"/>
-      <c r="L62" s="19" t="n"/>
-      <c r="M62" s="19" t="n"/>
-    </row>
-    <row r="63" ht="13" customHeight="1">
-      <c r="A63" s="19" t="n"/>
-      <c r="B63" s="19" t="n"/>
-      <c r="C63" s="19" t="n"/>
-      <c r="D63" s="19" t="n"/>
-      <c r="E63" s="19" t="n"/>
-      <c r="F63" s="19" t="n"/>
-      <c r="G63" s="19" t="n"/>
-      <c r="H63" s="19" t="n"/>
-      <c r="I63" s="19" t="n"/>
-      <c r="J63" s="19" t="n"/>
-      <c r="K63" s="19" t="n"/>
-      <c r="L63" s="19" t="n"/>
-      <c r="M63" s="19" t="n"/>
-    </row>
-    <row r="64" ht="13" customHeight="1">
-      <c r="A64" s="19" t="n"/>
-      <c r="B64" s="19" t="n"/>
-      <c r="C64" s="19" t="n"/>
-      <c r="D64" s="19" t="n"/>
-      <c r="E64" s="19" t="n"/>
-      <c r="F64" s="19" t="n"/>
-      <c r="G64" s="19" t="n"/>
-      <c r="H64" s="19" t="n"/>
-      <c r="I64" s="19" t="n"/>
-      <c r="J64" s="19" t="n"/>
-      <c r="K64" s="19" t="n"/>
-      <c r="L64" s="19" t="n"/>
-      <c r="M64" s="19" t="n"/>
+    <row r="1">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>ENABLE</t>
+        </is>
+      </c>
+      <c r="B1" s="30" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="30" t="inlineStr">
+        <is>
+          <t>mst_auto_player_sequence_id</t>
+        </is>
+      </c>
+      <c r="D1" s="30" t="inlineStr">
+        <is>
+          <t>mst_auto_player_sequence_set_id</t>
+        </is>
+      </c>
+      <c r="E1" s="30" t="inlineStr">
+        <is>
+          <t>bgm_asset_key</t>
+        </is>
+      </c>
+      <c r="F1" s="30" t="inlineStr">
+        <is>
+          <t>boss_bgm_asset_key</t>
+        </is>
+      </c>
+      <c r="G1" s="30" t="inlineStr">
+        <is>
+          <t>loop_background_asset_key</t>
+        </is>
+      </c>
+      <c r="H1" s="30" t="inlineStr">
+        <is>
+          <t>player_outpost_asset_key</t>
+        </is>
+      </c>
+      <c r="I1" s="30" t="inlineStr">
+        <is>
+          <t>mst_page_id</t>
+        </is>
+      </c>
+      <c r="J1" s="30" t="inlineStr">
+        <is>
+          <t>mst_enemy_outpost_id</t>
+        </is>
+      </c>
+      <c r="K1" s="30" t="inlineStr">
+        <is>
+          <t>mst_defense_target_id</t>
+        </is>
+      </c>
+      <c r="L1" s="30" t="inlineStr">
+        <is>
+          <t>boss_mst_enemy_stage_parameter_id</t>
+        </is>
+      </c>
+      <c r="M1" s="30" t="inlineStr">
+        <is>
+          <t>boss_count</t>
+        </is>
+      </c>
+      <c r="N1" s="30" t="inlineStr">
+        <is>
+          <t>normal_enemy_hp_coef</t>
+        </is>
+      </c>
+      <c r="O1" s="30" t="inlineStr">
+        <is>
+          <t>normal_enemy_attack_coef</t>
+        </is>
+      </c>
+      <c r="P1" s="30" t="inlineStr">
+        <is>
+          <t>normal_enemy_speed_coef</t>
+        </is>
+      </c>
+      <c r="Q1" s="30" t="inlineStr">
+        <is>
+          <t>boss_enemy_hp_coef</t>
+        </is>
+      </c>
+      <c r="R1" s="30" t="inlineStr">
+        <is>
+          <t>boss_enemy_attack_coef</t>
+        </is>
+      </c>
+      <c r="S1" s="30" t="inlineStr">
+        <is>
+          <t>boss_enemy_speed_coef</t>
+        </is>
+      </c>
+      <c r="T1" s="30" t="inlineStr">
+        <is>
+          <t>release_key</t>
+        </is>
+      </c>
+      <c r="U1" s="30" t="inlineStr">
+        <is>
+          <t>result_tips.ja</t>
+        </is>
+      </c>
+      <c r="V1" s="30" t="inlineStr">
+        <is>
+          <t>description.ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="inlineStr"/>
+      <c r="D2" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="E2" s="31" t="inlineStr">
+        <is>
+          <t>SSE_SBG_003_010</t>
+        </is>
+      </c>
+      <c r="F2" s="31" t="inlineStr"/>
+      <c r="G2" s="31" t="inlineStr"/>
+      <c r="H2" s="31" t="inlineStr"/>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="J2" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="K2" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="L2" s="31" t="inlineStr"/>
+      <c r="M2" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="N2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="S2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="T2" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+      <c r="U2" s="31" t="inlineStr"/>
+      <c r="V2" s="31" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="B4:J4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -3541,8 +2289,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="30" t="inlineStr">
@@ -3557,102 +2314,27 @@
       </c>
       <c r="C1" s="30" t="inlineStr">
         <is>
-          <t>mst_auto_player_sequence_id</t>
+          <t>hp</t>
         </is>
       </c>
       <c r="D1" s="30" t="inlineStr">
         <is>
-          <t>mst_auto_player_sequence_set_id</t>
+          <t>is_damage_invalidation</t>
         </is>
       </c>
       <c r="E1" s="30" t="inlineStr">
         <is>
-          <t>bgm_asset_key</t>
+          <t>outpost_asset_key</t>
         </is>
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>boss_bgm_asset_key</t>
+          <t>artwork_asset_key</t>
         </is>
       </c>
       <c r="G1" s="30" t="inlineStr">
         <is>
-          <t>loop_background_asset_key</t>
-        </is>
-      </c>
-      <c r="H1" s="30" t="inlineStr">
-        <is>
-          <t>player_outpost_asset_key</t>
-        </is>
-      </c>
-      <c r="I1" s="30" t="inlineStr">
-        <is>
-          <t>mst_page_id</t>
-        </is>
-      </c>
-      <c r="J1" s="30" t="inlineStr">
-        <is>
-          <t>mst_enemy_outpost_id</t>
-        </is>
-      </c>
-      <c r="K1" s="30" t="inlineStr">
-        <is>
-          <t>mst_defense_target_id</t>
-        </is>
-      </c>
-      <c r="L1" s="30" t="inlineStr">
-        <is>
-          <t>boss_mst_enemy_stage_parameter_id</t>
-        </is>
-      </c>
-      <c r="M1" s="30" t="inlineStr">
-        <is>
-          <t>boss_count</t>
-        </is>
-      </c>
-      <c r="N1" s="30" t="inlineStr">
-        <is>
-          <t>normal_enemy_hp_coef</t>
-        </is>
-      </c>
-      <c r="O1" s="30" t="inlineStr">
-        <is>
-          <t>normal_enemy_attack_coef</t>
-        </is>
-      </c>
-      <c r="P1" s="30" t="inlineStr">
-        <is>
-          <t>normal_enemy_speed_coef</t>
-        </is>
-      </c>
-      <c r="Q1" s="30" t="inlineStr">
-        <is>
-          <t>boss_enemy_hp_coef</t>
-        </is>
-      </c>
-      <c r="R1" s="30" t="inlineStr">
-        <is>
-          <t>boss_enemy_attack_coef</t>
-        </is>
-      </c>
-      <c r="S1" s="30" t="inlineStr">
-        <is>
-          <t>boss_enemy_speed_coef</t>
-        </is>
-      </c>
-      <c r="T1" s="30" t="inlineStr">
-        <is>
           <t>release_key</t>
-        </is>
-      </c>
-      <c r="U1" s="30" t="inlineStr">
-        <is>
-          <t>result_tips.ja</t>
-        </is>
-      </c>
-      <c r="V1" s="30" t="inlineStr">
-        <is>
-          <t>description.ja</t>
         </is>
       </c>
     </row>
@@ -3667,162 +2349,23 @@
           <t>vd_kai_normal_00001</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr"/>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="D2" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="E2" s="31" t="inlineStr">
-        <is>
-          <t>SSE_SBG_003_010</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" s="31" t="inlineStr"/>
       <c r="F2" s="31" t="inlineStr"/>
-      <c r="G2" s="31" t="inlineStr"/>
-      <c r="H2" s="31" t="inlineStr"/>
-      <c r="I2" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="J2" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="K2" s="31" t="inlineStr">
-        <is>
-          <t>__NULL__</t>
-        </is>
-      </c>
-      <c r="L2" s="31" t="inlineStr"/>
-      <c r="M2" s="31" t="inlineStr">
-        <is>
-          <t>__NULL__</t>
-        </is>
-      </c>
-      <c r="N2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="S2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="T2" s="31" t="inlineStr">
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
       </c>
-      <c r="U2" s="31" t="inlineStr"/>
-      <c r="V2" s="31" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr"/>
-      <c r="D4" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t>SSE_SBG_003_010</t>
-        </is>
-      </c>
-      <c r="F4" s="31" t="inlineStr"/>
-      <c r="G4" s="31" t="inlineStr"/>
-      <c r="H4" s="31" t="inlineStr"/>
-      <c r="I4" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="J4" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="K4" s="31" t="inlineStr">
-        <is>
-          <t>__NULL__</t>
-        </is>
-      </c>
-      <c r="L4" s="31" t="inlineStr"/>
-      <c r="M4" s="31" t="inlineStr">
-        <is>
-          <t>__NULL__</t>
-        </is>
-      </c>
-      <c r="N4" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O4" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P4" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q4" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R4" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="S4" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="T4" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-      <c r="U4" s="31" t="inlineStr"/>
-      <c r="V4" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3835,8 +2378,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="25" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="28" customWidth="1" min="23" max="23"/>
+    <col width="27" customWidth="1" min="24" max="24"/>
+    <col width="17" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="28" max="28"/>
+    <col width="25" customWidth="1" min="29" max="29"/>
+    <col width="25" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="26" customWidth="1" min="36" max="36"/>
+    <col width="19" customWidth="1" min="37" max="37"/>
+    <col width="25" customWidth="1" min="38" max="38"/>
+    <col width="25" customWidth="1" min="39" max="39"/>
+    <col width="26" customWidth="1" min="40" max="40"/>
+    <col width="28" customWidth="1" min="41" max="41"/>
+    <col width="27" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="30" t="inlineStr">
@@ -3851,25 +2439,205 @@
       </c>
       <c r="C1" s="30" t="inlineStr">
         <is>
-          <t>hp</t>
+          <t>mst_page_id</t>
         </is>
       </c>
       <c r="D1" s="30" t="inlineStr">
         <is>
-          <t>is_damage_invalidation</t>
+          <t>row</t>
         </is>
       </c>
       <c r="E1" s="30" t="inlineStr">
         <is>
-          <t>outpost_asset_key</t>
+          <t>height</t>
         </is>
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>artwork_asset_key</t>
+          <t>koma_line_layout_asset_key</t>
         </is>
       </c>
       <c r="G1" s="30" t="inlineStr">
+        <is>
+          <t>koma1_asset_key</t>
+        </is>
+      </c>
+      <c r="H1" s="30" t="inlineStr">
+        <is>
+          <t>koma1_width</t>
+        </is>
+      </c>
+      <c r="I1" s="30" t="inlineStr">
+        <is>
+          <t>koma1_back_ground_offset</t>
+        </is>
+      </c>
+      <c r="J1" s="30" t="inlineStr">
+        <is>
+          <t>koma1_effect_type</t>
+        </is>
+      </c>
+      <c r="K1" s="30" t="inlineStr">
+        <is>
+          <t>koma1_effect_parameter1</t>
+        </is>
+      </c>
+      <c r="L1" s="30" t="inlineStr">
+        <is>
+          <t>koma1_effect_parameter2</t>
+        </is>
+      </c>
+      <c r="M1" s="30" t="inlineStr">
+        <is>
+          <t>koma1_effect_target_side</t>
+        </is>
+      </c>
+      <c r="N1" s="30" t="inlineStr">
+        <is>
+          <t>koma1_effect_target_colors</t>
+        </is>
+      </c>
+      <c r="O1" s="30" t="inlineStr">
+        <is>
+          <t>koma1_effect_target_roles</t>
+        </is>
+      </c>
+      <c r="P1" s="30" t="inlineStr">
+        <is>
+          <t>koma2_asset_key</t>
+        </is>
+      </c>
+      <c r="Q1" s="30" t="inlineStr">
+        <is>
+          <t>koma2_width</t>
+        </is>
+      </c>
+      <c r="R1" s="30" t="inlineStr">
+        <is>
+          <t>koma2_back_ground_offset</t>
+        </is>
+      </c>
+      <c r="S1" s="30" t="inlineStr">
+        <is>
+          <t>koma2_effect_type</t>
+        </is>
+      </c>
+      <c r="T1" s="30" t="inlineStr">
+        <is>
+          <t>koma2_effect_parameter1</t>
+        </is>
+      </c>
+      <c r="U1" s="30" t="inlineStr">
+        <is>
+          <t>koma2_effect_parameter2</t>
+        </is>
+      </c>
+      <c r="V1" s="30" t="inlineStr">
+        <is>
+          <t>koma2_effect_target_side</t>
+        </is>
+      </c>
+      <c r="W1" s="30" t="inlineStr">
+        <is>
+          <t>koma2_effect_target_colors</t>
+        </is>
+      </c>
+      <c r="X1" s="30" t="inlineStr">
+        <is>
+          <t>koma2_effect_target_roles</t>
+        </is>
+      </c>
+      <c r="Y1" s="30" t="inlineStr">
+        <is>
+          <t>koma3_asset_key</t>
+        </is>
+      </c>
+      <c r="Z1" s="30" t="inlineStr">
+        <is>
+          <t>koma3_width</t>
+        </is>
+      </c>
+      <c r="AA1" s="30" t="inlineStr">
+        <is>
+          <t>koma3_back_ground_offset</t>
+        </is>
+      </c>
+      <c r="AB1" s="30" t="inlineStr">
+        <is>
+          <t>koma3_effect_type</t>
+        </is>
+      </c>
+      <c r="AC1" s="30" t="inlineStr">
+        <is>
+          <t>koma3_effect_parameter1</t>
+        </is>
+      </c>
+      <c r="AD1" s="30" t="inlineStr">
+        <is>
+          <t>koma3_effect_parameter2</t>
+        </is>
+      </c>
+      <c r="AE1" s="30" t="inlineStr">
+        <is>
+          <t>koma3_effect_target_side</t>
+        </is>
+      </c>
+      <c r="AF1" s="30" t="inlineStr">
+        <is>
+          <t>koma3_effect_target_colors</t>
+        </is>
+      </c>
+      <c r="AG1" s="30" t="inlineStr">
+        <is>
+          <t>koma3_effect_target_roles</t>
+        </is>
+      </c>
+      <c r="AH1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_asset_key</t>
+        </is>
+      </c>
+      <c r="AI1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_width</t>
+        </is>
+      </c>
+      <c r="AJ1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_back_ground_offset</t>
+        </is>
+      </c>
+      <c r="AK1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_effect_type</t>
+        </is>
+      </c>
+      <c r="AL1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_effect_parameter1</t>
+        </is>
+      </c>
+      <c r="AM1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_effect_parameter2</t>
+        </is>
+      </c>
+      <c r="AN1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_effect_target_side</t>
+        </is>
+      </c>
+      <c r="AO1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_effect_target_colors</t>
+        </is>
+      </c>
+      <c r="AP1" s="30" t="inlineStr">
+        <is>
+          <t>koma4_effect_target_roles</t>
+        </is>
+      </c>
+      <c r="AQ1" s="30" t="inlineStr">
         <is>
           <t>release_key</t>
         </is>
@@ -3883,22 +2651,299 @@
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
+          <t>vd_kai_normal_00001_1</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
           <t>vd_kai_normal_00001</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="D2" s="31" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" s="31" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="F2" s="31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G2" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="H2" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K2" s="31" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E2" s="31" t="inlineStr"/>
-      <c r="F2" s="31" t="inlineStr"/>
-      <c r="G2" s="31" t="inlineStr">
+      <c r="L2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="N2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="P2" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="Q2" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="R2" s="31" t="inlineStr"/>
+      <c r="S2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T2" s="31" t="inlineStr"/>
+      <c r="U2" s="31" t="inlineStr"/>
+      <c r="V2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X2" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Y2" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="Z2" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA2" s="31" t="inlineStr"/>
+      <c r="AB2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC2" s="31" t="inlineStr"/>
+      <c r="AD2" s="31" t="inlineStr"/>
+      <c r="AE2" s="31" t="inlineStr"/>
+      <c r="AF2" s="31" t="inlineStr"/>
+      <c r="AG2" s="31" t="inlineStr"/>
+      <c r="AH2" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="AI2" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AJ2" s="31" t="inlineStr"/>
+      <c r="AK2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL2" s="31" t="inlineStr"/>
+      <c r="AM2" s="31" t="inlineStr"/>
+      <c r="AN2" s="31" t="inlineStr"/>
+      <c r="AO2" s="31" t="inlineStr"/>
+      <c r="AP2" s="31" t="inlineStr"/>
+      <c r="AQ2" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001_2</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="F3" s="31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G3" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="H3" s="31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I3" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="N3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="P3" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="Q3" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="R3" s="31" t="inlineStr"/>
+      <c r="S3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T3" s="31" t="inlineStr"/>
+      <c r="U3" s="31" t="inlineStr"/>
+      <c r="V3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X3" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Y3" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="Z3" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA3" s="31" t="inlineStr"/>
+      <c r="AB3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC3" s="31" t="inlineStr"/>
+      <c r="AD3" s="31" t="inlineStr"/>
+      <c r="AE3" s="31" t="inlineStr"/>
+      <c r="AF3" s="31" t="inlineStr"/>
+      <c r="AG3" s="31" t="inlineStr"/>
+      <c r="AH3" s="31" t="inlineStr"/>
+      <c r="AI3" s="31" t="inlineStr"/>
+      <c r="AJ3" s="31" t="inlineStr"/>
+      <c r="AK3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL3" s="31" t="inlineStr"/>
+      <c r="AM3" s="31" t="inlineStr"/>
+      <c r="AN3" s="31" t="inlineStr"/>
+      <c r="AO3" s="31" t="inlineStr"/>
+      <c r="AP3" s="31" t="inlineStr"/>
+      <c r="AQ3" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -3912,22 +2957,134 @@
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
-          <t>vd_osh_normal_00001</t>
+          <t>vd_kai_normal_00001_3</t>
         </is>
       </c>
       <c r="C4" s="31" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>vd_kai_normal_00001</t>
         </is>
       </c>
       <c r="D4" s="31" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="H4" s="31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K4" s="31" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr"/>
-      <c r="F4" s="31" t="inlineStr"/>
-      <c r="G4" s="31" t="inlineStr">
+      <c r="L4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="N4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="P4" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="Q4" s="31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="R4" s="31" t="inlineStr"/>
+      <c r="S4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T4" s="31" t="inlineStr"/>
+      <c r="U4" s="31" t="inlineStr"/>
+      <c r="V4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X4" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Y4" s="31" t="inlineStr"/>
+      <c r="Z4" s="31" t="inlineStr"/>
+      <c r="AA4" s="31" t="inlineStr"/>
+      <c r="AB4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC4" s="31" t="inlineStr"/>
+      <c r="AD4" s="31" t="inlineStr"/>
+      <c r="AE4" s="31" t="inlineStr"/>
+      <c r="AF4" s="31" t="inlineStr"/>
+      <c r="AG4" s="31" t="inlineStr"/>
+      <c r="AH4" s="31" t="inlineStr"/>
+      <c r="AI4" s="31" t="inlineStr"/>
+      <c r="AJ4" s="31" t="inlineStr"/>
+      <c r="AK4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL4" s="31" t="inlineStr"/>
+      <c r="AM4" s="31" t="inlineStr"/>
+      <c r="AN4" s="31" t="inlineStr"/>
+      <c r="AO4" s="31" t="inlineStr"/>
+      <c r="AP4" s="31" t="inlineStr"/>
+      <c r="AQ4" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -3944,8 +3101,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="19" max="19"/>
+    <col width="29" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="22" max="22"/>
+    <col width="44" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="28" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="30" t="inlineStr">
@@ -3960,205 +3154,165 @@
       </c>
       <c r="C1" s="30" t="inlineStr">
         <is>
-          <t>mst_page_id</t>
+          <t>sequence_set_id</t>
         </is>
       </c>
       <c r="D1" s="30" t="inlineStr">
         <is>
-          <t>row</t>
+          <t>sequence_group_id</t>
         </is>
       </c>
       <c r="E1" s="30" t="inlineStr">
         <is>
-          <t>height</t>
+          <t>sequence_element_id</t>
         </is>
       </c>
       <c r="F1" s="30" t="inlineStr">
         <is>
-          <t>koma_line_layout_asset_key</t>
+          <t>priority_sequence_element_id</t>
         </is>
       </c>
       <c r="G1" s="30" t="inlineStr">
         <is>
-          <t>koma1_asset_key</t>
+          <t>condition_type</t>
         </is>
       </c>
       <c r="H1" s="30" t="inlineStr">
         <is>
-          <t>koma1_width</t>
+          <t>condition_value</t>
         </is>
       </c>
       <c r="I1" s="30" t="inlineStr">
         <is>
-          <t>koma1_back_ground_offset</t>
+          <t>action_type</t>
         </is>
       </c>
       <c r="J1" s="30" t="inlineStr">
         <is>
-          <t>koma1_effect_type</t>
+          <t>action_value</t>
         </is>
       </c>
       <c r="K1" s="30" t="inlineStr">
         <is>
-          <t>koma1_effect_parameter1</t>
+          <t>action_value2</t>
         </is>
       </c>
       <c r="L1" s="30" t="inlineStr">
         <is>
-          <t>koma1_effect_parameter2</t>
+          <t>summon_count</t>
         </is>
       </c>
       <c r="M1" s="30" t="inlineStr">
         <is>
-          <t>koma1_effect_target_side</t>
+          <t>summon_interval</t>
         </is>
       </c>
       <c r="N1" s="30" t="inlineStr">
         <is>
-          <t>koma1_effect_target_colors</t>
+          <t>summon_animation_type</t>
         </is>
       </c>
       <c r="O1" s="30" t="inlineStr">
         <is>
-          <t>koma1_effect_target_roles</t>
+          <t>summon_position</t>
         </is>
       </c>
       <c r="P1" s="30" t="inlineStr">
         <is>
-          <t>koma2_asset_key</t>
+          <t>move_start_condition_type</t>
         </is>
       </c>
       <c r="Q1" s="30" t="inlineStr">
         <is>
-          <t>koma2_width</t>
+          <t>move_start_condition_value</t>
         </is>
       </c>
       <c r="R1" s="30" t="inlineStr">
         <is>
-          <t>koma2_back_ground_offset</t>
+          <t>move_stop_condition_type</t>
         </is>
       </c>
       <c r="S1" s="30" t="inlineStr">
         <is>
-          <t>koma2_effect_type</t>
+          <t>move_stop_condition_value</t>
         </is>
       </c>
       <c r="T1" s="30" t="inlineStr">
         <is>
-          <t>koma2_effect_parameter1</t>
+          <t>move_restart_condition_type</t>
         </is>
       </c>
       <c r="U1" s="30" t="inlineStr">
         <is>
-          <t>koma2_effect_parameter2</t>
+          <t>move_restart_condition_value</t>
         </is>
       </c>
       <c r="V1" s="30" t="inlineStr">
         <is>
-          <t>koma2_effect_target_side</t>
+          <t>move_loop_count</t>
         </is>
       </c>
       <c r="W1" s="30" t="inlineStr">
         <is>
-          <t>koma2_effect_target_colors</t>
+          <t>is_summon_unit_outpost_damage_invalidation</t>
         </is>
       </c>
       <c r="X1" s="30" t="inlineStr">
         <is>
-          <t>koma2_effect_target_roles</t>
+          <t>last_boss_trigger</t>
         </is>
       </c>
       <c r="Y1" s="30" t="inlineStr">
         <is>
-          <t>koma3_asset_key</t>
+          <t>aura_type</t>
         </is>
       </c>
       <c r="Z1" s="30" t="inlineStr">
         <is>
-          <t>koma3_width</t>
+          <t>death_type</t>
         </is>
       </c>
       <c r="AA1" s="30" t="inlineStr">
         <is>
-          <t>koma3_back_ground_offset</t>
+          <t>enemy_hp_coef</t>
         </is>
       </c>
       <c r="AB1" s="30" t="inlineStr">
         <is>
-          <t>koma3_effect_type</t>
+          <t>enemy_attack_coef</t>
         </is>
       </c>
       <c r="AC1" s="30" t="inlineStr">
         <is>
-          <t>koma3_effect_parameter1</t>
+          <t>enemy_speed_coef</t>
         </is>
       </c>
       <c r="AD1" s="30" t="inlineStr">
         <is>
-          <t>koma3_effect_parameter2</t>
+          <t>override_drop_battle_point</t>
         </is>
       </c>
       <c r="AE1" s="30" t="inlineStr">
         <is>
-          <t>koma3_effect_target_side</t>
+          <t>defeated_score</t>
         </is>
       </c>
       <c r="AF1" s="30" t="inlineStr">
         <is>
-          <t>koma3_effect_target_colors</t>
+          <t>action_delay</t>
         </is>
       </c>
       <c r="AG1" s="30" t="inlineStr">
         <is>
-          <t>koma3_effect_target_roles</t>
+          <t>deactivation_condition_type</t>
         </is>
       </c>
       <c r="AH1" s="30" t="inlineStr">
         <is>
-          <t>koma4_asset_key</t>
+          <t>deactivation_condition_value</t>
         </is>
       </c>
       <c r="AI1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_width</t>
-        </is>
-      </c>
-      <c r="AJ1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_back_ground_offset</t>
-        </is>
-      </c>
-      <c r="AK1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_effect_type</t>
-        </is>
-      </c>
-      <c r="AL1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_effect_parameter1</t>
-        </is>
-      </c>
-      <c r="AM1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_effect_parameter2</t>
-        </is>
-      </c>
-      <c r="AN1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_effect_target_side</t>
-        </is>
-      </c>
-      <c r="AO1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_effect_target_colors</t>
-        </is>
-      </c>
-      <c r="AP1" s="30" t="inlineStr">
-        <is>
-          <t>koma4_effect_target_roles</t>
-        </is>
-      </c>
-      <c r="AQ1" s="30" t="inlineStr">
         <is>
           <t>release_key</t>
         </is>
@@ -4180,142 +3334,146 @@
           <t>vd_kai_normal_00001</t>
         </is>
       </c>
-      <c r="D2" s="31" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr"/>
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E2" s="31" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
       <c r="F2" s="31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>__NULL__</t>
         </is>
       </c>
       <c r="G2" s="31" t="inlineStr">
         <is>
-          <t>kai_00001</t>
+          <t>ElapsedTime</t>
         </is>
       </c>
       <c r="H2" s="31" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>250</t>
         </is>
       </c>
       <c r="I2" s="31" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>SummonEnemy</t>
         </is>
       </c>
       <c r="J2" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K2" s="31" t="inlineStr">
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K2" s="31" t="inlineStr"/>
+      <c r="L2" s="31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M2" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L2" s="31" t="inlineStr">
+      <c r="N2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q2" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="N2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="O2" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="P2" s="31" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
-      <c r="Q2" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="R2" s="31" t="inlineStr"/>
+      <c r="R2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="S2" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T2" s="31" t="inlineStr"/>
-      <c r="U2" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="V2" s="31" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W2" s="31" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X2" s="31" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y2" s="31" t="inlineStr">
         <is>
-          <t>kai_00001</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="Z2" s="31" t="inlineStr">
         <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AA2" s="31" t="inlineStr"/>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="AB2" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AC2" s="31" t="inlineStr"/>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC2" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="AD2" s="31" t="inlineStr"/>
-      <c r="AE2" s="31" t="inlineStr"/>
-      <c r="AF2" s="31" t="inlineStr"/>
-      <c r="AG2" s="31" t="inlineStr"/>
-      <c r="AH2" s="31" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH2" s="31" t="inlineStr"/>
       <c r="AI2" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AJ2" s="31" t="inlineStr"/>
-      <c r="AK2" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AL2" s="31" t="inlineStr"/>
-      <c r="AM2" s="31" t="inlineStr"/>
-      <c r="AN2" s="31" t="inlineStr"/>
-      <c r="AO2" s="31" t="inlineStr"/>
-      <c r="AP2" s="31" t="inlineStr"/>
-      <c r="AQ2" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -4337,134 +3495,146 @@
           <t>vd_kai_normal_00001</t>
         </is>
       </c>
-      <c r="D3" s="31" t="inlineStr">
+      <c r="D3" s="31" t="inlineStr"/>
+      <c r="E3" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E3" s="31" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
       <c r="F3" s="31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>__NULL__</t>
         </is>
       </c>
       <c r="G3" s="31" t="inlineStr">
         <is>
-          <t>kai_00001</t>
+          <t>ElapsedTime</t>
         </is>
       </c>
       <c r="H3" s="31" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="I3" s="31" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>SummonEnemy</t>
         </is>
       </c>
       <c r="J3" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K3" s="31" t="inlineStr">
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="K3" s="31" t="inlineStr"/>
+      <c r="L3" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M3" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L3" s="31" t="inlineStr">
+      <c r="N3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O3" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q3" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="N3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="O3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="P3" s="31" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
-      <c r="Q3" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="R3" s="31" t="inlineStr"/>
+      <c r="R3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="S3" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T3" s="31" t="inlineStr"/>
-      <c r="U3" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="V3" s="31" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" s="31" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X3" s="31" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y3" s="31" t="inlineStr">
         <is>
-          <t>kai_00001</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="Z3" s="31" t="inlineStr">
         <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AA3" s="31" t="inlineStr"/>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA3" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="AB3" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AC3" s="31" t="inlineStr"/>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC3" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="AD3" s="31" t="inlineStr"/>
-      <c r="AE3" s="31" t="inlineStr"/>
-      <c r="AF3" s="31" t="inlineStr"/>
-      <c r="AG3" s="31" t="inlineStr"/>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AH3" s="31" t="inlineStr"/>
-      <c r="AI3" s="31" t="inlineStr"/>
-      <c r="AJ3" s="31" t="inlineStr"/>
-      <c r="AK3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AL3" s="31" t="inlineStr"/>
-      <c r="AM3" s="31" t="inlineStr"/>
-      <c r="AN3" s="31" t="inlineStr"/>
-      <c r="AO3" s="31" t="inlineStr"/>
-      <c r="AP3" s="31" t="inlineStr"/>
-      <c r="AQ3" s="31" t="inlineStr">
+      <c r="AI3" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -4486,126 +3656,307 @@
           <t>vd_kai_normal_00001</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr"/>
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
       <c r="F4" s="31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>__NULL__</t>
         </is>
       </c>
       <c r="G4" s="31" t="inlineStr">
         <is>
-          <t>kai_00001</t>
+          <t>ElapsedTime</t>
         </is>
       </c>
       <c r="H4" s="31" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="I4" s="31" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>SummonEnemy</t>
         </is>
       </c>
       <c r="J4" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K4" s="31" t="inlineStr">
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K4" s="31" t="inlineStr"/>
+      <c r="L4" s="31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="31" t="inlineStr">
+      <c r="N4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O4" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q4" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="N4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="O4" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="P4" s="31" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
-      <c r="Q4" s="31" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="R4" s="31" t="inlineStr"/>
+      <c r="R4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="S4" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T4" s="31" t="inlineStr"/>
-      <c r="U4" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="V4" s="31" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W4" s="31" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" s="31" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="Y4" s="31" t="inlineStr"/>
-      <c r="Z4" s="31" t="inlineStr"/>
-      <c r="AA4" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z4" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="AB4" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AC4" s="31" t="inlineStr"/>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="AD4" s="31" t="inlineStr"/>
-      <c r="AE4" s="31" t="inlineStr"/>
-      <c r="AF4" s="31" t="inlineStr"/>
-      <c r="AG4" s="31" t="inlineStr"/>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AH4" s="31" t="inlineStr"/>
-      <c r="AI4" s="31" t="inlineStr"/>
-      <c r="AJ4" s="31" t="inlineStr"/>
-      <c r="AK4" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AL4" s="31" t="inlineStr"/>
-      <c r="AM4" s="31" t="inlineStr"/>
-      <c r="AN4" s="31" t="inlineStr"/>
-      <c r="AO4" s="31" t="inlineStr"/>
-      <c r="AP4" s="31" t="inlineStr"/>
-      <c r="AQ4" s="31" t="inlineStr">
+      <c r="AI4" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001_4</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr"/>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J5" s="31" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="inlineStr"/>
+      <c r="L5" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O5" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z5" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA5" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB5" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD5" s="31" t="inlineStr"/>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH5" s="31" t="inlineStr"/>
+      <c r="AI5" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -4619,476 +3970,154 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>vd_osh_normal_00001_1</t>
+          <t>vd_kai_normal_00001_5</t>
         </is>
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr"/>
       <c r="E6" s="31" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F6" s="31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>__NULL__</t>
         </is>
       </c>
       <c r="G6" s="31" t="inlineStr">
         <is>
-          <t>osh_00001</t>
+          <t>ElapsedTime</t>
         </is>
       </c>
       <c r="H6" s="31" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="I6" s="31" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>SummonEnemy</t>
         </is>
       </c>
       <c r="J6" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K6" s="31" t="inlineStr">
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="K6" s="31" t="inlineStr"/>
+      <c r="L6" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M6" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" s="31" t="inlineStr">
+      <c r="N6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O6" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q6" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="N6" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="O6" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="P6" s="31" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="Q6" s="31" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="R6" s="31" t="inlineStr"/>
+      <c r="R6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="S6" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T6" s="31" t="inlineStr"/>
-      <c r="U6" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="V6" s="31" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" s="31" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X6" s="31" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="Y6" s="31" t="inlineStr"/>
-      <c r="Z6" s="31" t="inlineStr"/>
-      <c r="AA6" s="31" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z6" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA6" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="AB6" s="31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AC6" s="31" t="inlineStr"/>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC6" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="AD6" s="31" t="inlineStr"/>
-      <c r="AE6" s="31" t="inlineStr"/>
-      <c r="AF6" s="31" t="inlineStr"/>
-      <c r="AG6" s="31" t="inlineStr"/>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AH6" s="31" t="inlineStr"/>
-      <c r="AI6" s="31" t="inlineStr"/>
-      <c r="AJ6" s="31" t="inlineStr"/>
-      <c r="AK6" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AL6" s="31" t="inlineStr"/>
-      <c r="AM6" s="31" t="inlineStr"/>
-      <c r="AN6" s="31" t="inlineStr"/>
-      <c r="AO6" s="31" t="inlineStr"/>
-      <c r="AP6" s="31" t="inlineStr"/>
-      <c r="AQ6" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001_2</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="D7" s="31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="F7" s="31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G7" s="31" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="H7" s="31" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I7" s="31" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J7" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K7" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="N7" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="O7" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="P7" s="31" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="Q7" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="R7" s="31" t="inlineStr"/>
-      <c r="S7" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T7" s="31" t="inlineStr"/>
-      <c r="U7" s="31" t="inlineStr"/>
-      <c r="V7" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="W7" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="X7" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="Y7" s="31" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="Z7" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AA7" s="31" t="inlineStr"/>
-      <c r="AB7" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AC7" s="31" t="inlineStr"/>
-      <c r="AD7" s="31" t="inlineStr"/>
-      <c r="AE7" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AF7" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AG7" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AH7" s="31" t="inlineStr"/>
-      <c r="AI7" s="31" t="inlineStr"/>
-      <c r="AJ7" s="31" t="inlineStr"/>
-      <c r="AK7" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AL7" s="31" t="inlineStr"/>
-      <c r="AM7" s="31" t="inlineStr"/>
-      <c r="AN7" s="31" t="inlineStr"/>
-      <c r="AO7" s="31" t="inlineStr"/>
-      <c r="AP7" s="31" t="inlineStr"/>
-      <c r="AQ7" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001_3</t>
-        </is>
-      </c>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="D8" s="31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="F8" s="31" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G8" s="31" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="H8" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="I8" s="31" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J8" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K8" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="N8" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="O8" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="P8" s="31" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="Q8" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="R8" s="31" t="inlineStr"/>
-      <c r="S8" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T8" s="31" t="inlineStr"/>
-      <c r="U8" s="31" t="inlineStr"/>
-      <c r="V8" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="W8" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="X8" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="Y8" s="31" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="Z8" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AA8" s="31" t="inlineStr"/>
-      <c r="AB8" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AC8" s="31" t="inlineStr"/>
-      <c r="AD8" s="31" t="inlineStr"/>
-      <c r="AE8" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AF8" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AG8" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AH8" s="31" t="inlineStr">
-        <is>
-          <t>osh_00001</t>
-        </is>
-      </c>
-      <c r="AI8" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AJ8" s="31" t="inlineStr"/>
-      <c r="AK8" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AL8" s="31" t="inlineStr"/>
-      <c r="AM8" s="31" t="inlineStr"/>
-      <c r="AN8" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AO8" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AP8" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="AQ8" s="31" t="inlineStr">
+      <c r="AI6" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -5105,8 +4134,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI12"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="30" t="inlineStr">
@@ -5121,166 +4155,6 @@
       </c>
       <c r="C1" s="30" t="inlineStr">
         <is>
-          <t>sequence_set_id</t>
-        </is>
-      </c>
-      <c r="D1" s="30" t="inlineStr">
-        <is>
-          <t>sequence_group_id</t>
-        </is>
-      </c>
-      <c r="E1" s="30" t="inlineStr">
-        <is>
-          <t>sequence_element_id</t>
-        </is>
-      </c>
-      <c r="F1" s="30" t="inlineStr">
-        <is>
-          <t>priority_sequence_element_id</t>
-        </is>
-      </c>
-      <c r="G1" s="30" t="inlineStr">
-        <is>
-          <t>condition_type</t>
-        </is>
-      </c>
-      <c r="H1" s="30" t="inlineStr">
-        <is>
-          <t>condition_value</t>
-        </is>
-      </c>
-      <c r="I1" s="30" t="inlineStr">
-        <is>
-          <t>action_type</t>
-        </is>
-      </c>
-      <c r="J1" s="30" t="inlineStr">
-        <is>
-          <t>action_value</t>
-        </is>
-      </c>
-      <c r="K1" s="30" t="inlineStr">
-        <is>
-          <t>action_value2</t>
-        </is>
-      </c>
-      <c r="L1" s="30" t="inlineStr">
-        <is>
-          <t>summon_count</t>
-        </is>
-      </c>
-      <c r="M1" s="30" t="inlineStr">
-        <is>
-          <t>summon_interval</t>
-        </is>
-      </c>
-      <c r="N1" s="30" t="inlineStr">
-        <is>
-          <t>summon_animation_type</t>
-        </is>
-      </c>
-      <c r="O1" s="30" t="inlineStr">
-        <is>
-          <t>summon_position</t>
-        </is>
-      </c>
-      <c r="P1" s="30" t="inlineStr">
-        <is>
-          <t>move_start_condition_type</t>
-        </is>
-      </c>
-      <c r="Q1" s="30" t="inlineStr">
-        <is>
-          <t>move_start_condition_value</t>
-        </is>
-      </c>
-      <c r="R1" s="30" t="inlineStr">
-        <is>
-          <t>move_stop_condition_type</t>
-        </is>
-      </c>
-      <c r="S1" s="30" t="inlineStr">
-        <is>
-          <t>move_stop_condition_value</t>
-        </is>
-      </c>
-      <c r="T1" s="30" t="inlineStr">
-        <is>
-          <t>move_restart_condition_type</t>
-        </is>
-      </c>
-      <c r="U1" s="30" t="inlineStr">
-        <is>
-          <t>move_restart_condition_value</t>
-        </is>
-      </c>
-      <c r="V1" s="30" t="inlineStr">
-        <is>
-          <t>move_loop_count</t>
-        </is>
-      </c>
-      <c r="W1" s="30" t="inlineStr">
-        <is>
-          <t>is_summon_unit_outpost_damage_invalidation</t>
-        </is>
-      </c>
-      <c r="X1" s="30" t="inlineStr">
-        <is>
-          <t>last_boss_trigger</t>
-        </is>
-      </c>
-      <c r="Y1" s="30" t="inlineStr">
-        <is>
-          <t>aura_type</t>
-        </is>
-      </c>
-      <c r="Z1" s="30" t="inlineStr">
-        <is>
-          <t>death_type</t>
-        </is>
-      </c>
-      <c r="AA1" s="30" t="inlineStr">
-        <is>
-          <t>enemy_hp_coef</t>
-        </is>
-      </c>
-      <c r="AB1" s="30" t="inlineStr">
-        <is>
-          <t>enemy_attack_coef</t>
-        </is>
-      </c>
-      <c r="AC1" s="30" t="inlineStr">
-        <is>
-          <t>enemy_speed_coef</t>
-        </is>
-      </c>
-      <c r="AD1" s="30" t="inlineStr">
-        <is>
-          <t>override_drop_battle_point</t>
-        </is>
-      </c>
-      <c r="AE1" s="30" t="inlineStr">
-        <is>
-          <t>defeated_score</t>
-        </is>
-      </c>
-      <c r="AF1" s="30" t="inlineStr">
-        <is>
-          <t>action_delay</t>
-        </is>
-      </c>
-      <c r="AG1" s="30" t="inlineStr">
-        <is>
-          <t>deactivation_condition_type</t>
-        </is>
-      </c>
-      <c r="AH1" s="30" t="inlineStr">
-        <is>
-          <t>deactivation_condition_value</t>
-        </is>
-      </c>
-      <c r="AI1" s="30" t="inlineStr">
-        <is>
           <t>release_key</t>
         </is>
       </c>
@@ -5293,1583 +4167,10 @@
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001_1</t>
+          <t>vd_kai_normal_00001</t>
         </is>
       </c>
       <c r="C2" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="D2" s="31" t="inlineStr"/>
-      <c r="E2" s="31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F2" s="31" t="inlineStr">
-        <is>
-          <t>__NULL__</t>
-        </is>
-      </c>
-      <c r="G2" s="31" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="H2" s="31" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="I2" s="31" t="inlineStr">
-        <is>
-          <t>SummonEnemy</t>
-        </is>
-      </c>
-      <c r="J2" s="31" t="inlineStr">
-        <is>
-          <t>e_glo_00001_vd_Normal_Colorless</t>
-        </is>
-      </c>
-      <c r="K2" s="31" t="inlineStr"/>
-      <c r="L2" s="31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O2" s="31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P2" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="Z2" s="31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AB2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AC2" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD2" s="31" t="inlineStr"/>
-      <c r="AE2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF2" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AH2" s="31" t="inlineStr"/>
-      <c r="AI2" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B3" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001_2</t>
-        </is>
-      </c>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="D3" s="31" t="inlineStr"/>
-      <c r="E3" s="31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F3" s="31" t="inlineStr">
-        <is>
-          <t>__NULL__</t>
-        </is>
-      </c>
-      <c r="G3" s="31" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="H3" s="31" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="I3" s="31" t="inlineStr">
-        <is>
-          <t>SummonEnemy</t>
-        </is>
-      </c>
-      <c r="J3" s="31" t="inlineStr">
-        <is>
-          <t>e_kai_00101_vd_Normal_Yellow</t>
-        </is>
-      </c>
-      <c r="K3" s="31" t="inlineStr"/>
-      <c r="L3" s="31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O3" s="31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="Z3" s="31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA3" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AB3" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AC3" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD3" s="31" t="inlineStr"/>
-      <c r="AE3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AH3" s="31" t="inlineStr"/>
-      <c r="AI3" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001_3</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="inlineStr"/>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="31" t="inlineStr">
-        <is>
-          <t>__NULL__</t>
-        </is>
-      </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="H4" s="31" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="I4" s="31" t="inlineStr">
-        <is>
-          <t>SummonEnemy</t>
-        </is>
-      </c>
-      <c r="J4" s="31" t="inlineStr">
-        <is>
-          <t>e_glo_00001_vd_Normal_Colorless</t>
-        </is>
-      </c>
-      <c r="K4" s="31" t="inlineStr"/>
-      <c r="L4" s="31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O4" s="31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P4" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="Z4" s="31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA4" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AB4" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AC4" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD4" s="31" t="inlineStr"/>
-      <c r="AE4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF4" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AH4" s="31" t="inlineStr"/>
-      <c r="AI4" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001_4</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr"/>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="inlineStr">
-        <is>
-          <t>__NULL__</t>
-        </is>
-      </c>
-      <c r="G5" s="31" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="H5" s="31" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="I5" s="31" t="inlineStr">
-        <is>
-          <t>SummonEnemy</t>
-        </is>
-      </c>
-      <c r="J5" s="31" t="inlineStr">
-        <is>
-          <t>e_kai_00101_vd_Normal_Yellow</t>
-        </is>
-      </c>
-      <c r="K5" s="31" t="inlineStr"/>
-      <c r="L5" s="31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O5" s="31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P5" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="Z5" s="31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA5" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AB5" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AC5" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD5" s="31" t="inlineStr"/>
-      <c r="AE5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF5" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AH5" s="31" t="inlineStr"/>
-      <c r="AI5" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001_5</t>
-        </is>
-      </c>
-      <c r="C6" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr"/>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F6" s="31" t="inlineStr">
-        <is>
-          <t>__NULL__</t>
-        </is>
-      </c>
-      <c r="G6" s="31" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="H6" s="31" t="inlineStr">
-        <is>
-          <t>7000</t>
-        </is>
-      </c>
-      <c r="I6" s="31" t="inlineStr">
-        <is>
-          <t>SummonEnemy</t>
-        </is>
-      </c>
-      <c r="J6" s="31" t="inlineStr">
-        <is>
-          <t>e_kai_00101_vd_Normal_Yellow</t>
-        </is>
-      </c>
-      <c r="K6" s="31" t="inlineStr"/>
-      <c r="L6" s="31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M6" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N6" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O6" s="31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P6" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q6" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S6" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U6" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V6" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="Z6" s="31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA6" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AB6" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AC6" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD6" s="31" t="inlineStr"/>
-      <c r="AE6" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF6" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AH6" s="31" t="inlineStr"/>
-      <c r="AI6" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001_1</t>
-        </is>
-      </c>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="D8" s="31" t="inlineStr"/>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F8" s="31" t="inlineStr"/>
-      <c r="G8" s="31" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="H8" s="31" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="I8" s="31" t="inlineStr">
-        <is>
-          <t>SummonEnemy</t>
-        </is>
-      </c>
-      <c r="J8" s="31" t="inlineStr">
-        <is>
-          <t>e_glo_00001_vd_Normal_Colorless</t>
-        </is>
-      </c>
-      <c r="K8" s="31" t="inlineStr"/>
-      <c r="L8" s="31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M8" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N8" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O8" s="31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P8" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q8" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S8" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U8" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V8" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="Z8" s="31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA8" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AB8" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AC8" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD8" s="31" t="inlineStr"/>
-      <c r="AE8" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF8" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AH8" s="31" t="inlineStr"/>
-      <c r="AI8" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001_2</t>
-        </is>
-      </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="D9" s="31" t="inlineStr"/>
-      <c r="E9" s="31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F9" s="31" t="inlineStr"/>
-      <c r="G9" s="31" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="H9" s="31" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="I9" s="31" t="inlineStr">
-        <is>
-          <t>SummonEnemy</t>
-        </is>
-      </c>
-      <c r="J9" s="31" t="inlineStr">
-        <is>
-          <t>c_osh_00501_vd_Normal_Green</t>
-        </is>
-      </c>
-      <c r="K9" s="31" t="inlineStr"/>
-      <c r="L9" s="31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M9" s="31" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="N9" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O9" s="31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P9" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q9" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S9" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U9" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V9" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="Z9" s="31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA9" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AB9" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AC9" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD9" s="31" t="inlineStr"/>
-      <c r="AE9" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF9" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AH9" s="31" t="inlineStr"/>
-      <c r="AI9" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001_3</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr"/>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F10" s="31" t="inlineStr"/>
-      <c r="G10" s="31" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="H10" s="31" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="I10" s="31" t="inlineStr">
-        <is>
-          <t>SummonEnemy</t>
-        </is>
-      </c>
-      <c r="J10" s="31" t="inlineStr">
-        <is>
-          <t>c_osh_00201_vd_Normal_Green</t>
-        </is>
-      </c>
-      <c r="K10" s="31" t="inlineStr"/>
-      <c r="L10" s="31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M10" s="31" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="N10" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O10" s="31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P10" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q10" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S10" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U10" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V10" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="Z10" s="31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA10" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AB10" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AC10" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD10" s="31" t="inlineStr"/>
-      <c r="AE10" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF10" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AH10" s="31" t="inlineStr"/>
-      <c r="AI10" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001_4</t>
-        </is>
-      </c>
-      <c r="C11" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="D11" s="31" t="inlineStr"/>
-      <c r="E11" s="31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F11" s="31" t="inlineStr"/>
-      <c r="G11" s="31" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="H11" s="31" t="inlineStr">
-        <is>
-          <t>13000</t>
-        </is>
-      </c>
-      <c r="I11" s="31" t="inlineStr">
-        <is>
-          <t>SummonEnemy</t>
-        </is>
-      </c>
-      <c r="J11" s="31" t="inlineStr">
-        <is>
-          <t>c_osh_00401_vd_Normal_Green</t>
-        </is>
-      </c>
-      <c r="K11" s="31" t="inlineStr"/>
-      <c r="L11" s="31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M11" s="31" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="N11" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O11" s="31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P11" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q11" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S11" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U11" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V11" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y11" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="Z11" s="31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA11" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AB11" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AC11" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD11" s="31" t="inlineStr"/>
-      <c r="AE11" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF11" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG11" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AH11" s="31" t="inlineStr"/>
-      <c r="AI11" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001_5</t>
-        </is>
-      </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="D12" s="31" t="inlineStr"/>
-      <c r="E12" s="31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F12" s="31" t="inlineStr"/>
-      <c r="G12" s="31" t="inlineStr">
-        <is>
-          <t>ElapsedTime</t>
-        </is>
-      </c>
-      <c r="H12" s="31" t="inlineStr">
-        <is>
-          <t>18000</t>
-        </is>
-      </c>
-      <c r="I12" s="31" t="inlineStr">
-        <is>
-          <t>SummonEnemy</t>
-        </is>
-      </c>
-      <c r="J12" s="31" t="inlineStr">
-        <is>
-          <t>c_osh_00301_vd_Normal_Green</t>
-        </is>
-      </c>
-      <c r="K12" s="31" t="inlineStr"/>
-      <c r="L12" s="31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M12" s="31" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="N12" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O12" s="31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P12" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q12" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S12" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U12" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V12" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X12" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y12" s="31" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="Z12" s="31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AA12" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AB12" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AC12" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AD12" s="31" t="inlineStr"/>
-      <c r="AE12" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF12" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG12" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AH12" s="31" t="inlineStr"/>
-      <c r="AI12" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -6886,73 +4187,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="30" t="inlineStr">
-        <is>
-          <t>ENABLE</t>
-        </is>
-      </c>
-      <c r="B1" s="30" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" s="30" t="inlineStr">
-        <is>
-          <t>release_key</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B2" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="C2" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>vd_osh_normal_00001</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:S48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="29" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="30" t="inlineStr">

--- a/domain/tasks/20260311_202700_vd_masterdata_ingame_generation/vd_all/vd_all.xlsx
+++ b/domain/tasks/20260311_202700_vd_masterdata_ingame_generation/vd_all/vd_all.xlsx
@@ -6,17 +6,19 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="920" yWindow="660" windowWidth="29320" windowHeight="18980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ブロック基礎設計_vd_kai_normal_00001" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="MstInGame" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MstEnemyOutpost" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MstKomaLine" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="MstAutoPlayerSequence" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MstPage" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="MstEnemyStageParameter" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ブロック基礎設計_vd_kai_boss_00001" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ブロック基礎設計_vd_kai_normal_00001" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ブロック基礎設計_vd_osh_normal_00001" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MstInGame" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MstEnemyOutpost" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MstKomaLine" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MstAutoPlayerSequence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MstPage" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MstEnemyStageParameter" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -680,7 +682,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>ブロック基礎設計_vd_kai_normal_00001</t>
+          <t>ブロック基礎設計_vd_kai_boss_00001</t>
         </is>
       </c>
       <c r="C1" s="5" t="n"/>
@@ -730,9 +732,8 @@
       <c r="A4" s="6" t="n"/>
       <c r="B4" s="26" t="inlineStr">
         <is>
-          <t>ファントム（Colorless/Attack・HP5,000・ATK100・SPD34）が開幕250msと中間3,000msに各5体ずつ、怪獣 余獣（Yellow/Defense・HP25,000・ATK350・SPD45）が1,500ms・5,000ms・7,000msに各4体ずつ出現する5波構成、合計22体。ファントムが序盤のテンポを作りつつ、中盤以降は高HPでゆっくり前進する防御型の余獣が中心となり、Yellow属性対策を求める緊張感のある展開になる。
-コマは3行固定（各行独立抽選）。row1=4等分4コマ（0.25×4）・row2=右広い3コマ（0.50, 0.25, 0.25）・row3=2等分2コマ（0.50, 0.50）。幅の組み合わせに変化を持たせることで、コマ組みの選択肢を広げる。コマアセット: kai_00001（back_ground_offset: -1.0）。
-UR対抗キャラ「隠された英雄の姿 怪獣８号」（chara_kai_00002）対抗。Yellow/Defenseの余獣が主軸となるため、Yellow属性対策コマを活かしたプレイが有効になる設計。</t>
+          <t>UR対抗キャラ「隠された英雄の姿 怪獣８号」（`c_kai_00002_vd_Boss_Yellow`）がボスとして砦付近（position=1.7）に開幕即配置し、初ダメージを受けるまで待機状態を保つ。1500ms後にファントム2体が前衛を形成し、2000ms後に怪獣余獣2体が追加。累計3体撃破後は怪獣余獣3体と後方ファントム1体（pos=2.8）が同時展開する。さらに6体撃破後は怪獣余獣3体が追加。拠点に初ダメージが入ると独立したトリガーで怪獣余獣3体が援護を展開する。ボスを主役にした適度な雑魚量で、ボス撃破に集中できる設計。
+コマは1行・2等分（パターン6、幅0.5/0.5）のシンプル構成。コマアセットキーは `kai_00001`、`koma1_back_ground_offset = -1.0`。ボス本体が「隠された英雄の姿 怪獣８号」（chara_kai_00002）のVD敵バージョンであるため、同URキャラのコマ効果・スキルが戦闘上の対抗手段となる。</t>
         </is>
       </c>
       <c r="C4" s="27" t="n"/>
@@ -847,20 +848,20 @@
       <c r="A9" s="2" t="n"/>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
+          <t>vd_kai_boss_00001</t>
         </is>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D9" s="26" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>3行</t>
+          <t>1行</t>
         </is>
       </c>
       <c r="F9" s="26" t="inlineStr">
@@ -870,7 +871,7 @@
       </c>
       <c r="G9" s="26" t="inlineStr">
         <is>
-          <t>5行</t>
+          <t>7行</t>
         </is>
       </c>
       <c r="H9" s="26" t="n">
@@ -979,7 +980,7 @@
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>4コマ</t>
+          <t>2コマ</t>
         </is>
       </c>
       <c r="D14" s="26" t="inlineStr">
@@ -994,7 +995,7 @@
       </c>
       <c r="F14" s="26" t="inlineStr">
         <is>
-          <t>0.25 / 0.25 / 0.25 / 0.25</t>
+          <t>0.5 / 0.5</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -1007,31 +1008,11 @@
     </row>
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="2" t="n"/>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>行2</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>3コマ</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
-      <c r="E15" s="26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F15" s="26" t="inlineStr">
-        <is>
-          <t>0.5 / 0.25 / 0.25</t>
-        </is>
-      </c>
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="12" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
@@ -1042,31 +1023,11 @@
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="2" t="n"/>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>行3</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>2コマ</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F16" s="26" t="inlineStr">
-        <is>
-          <t>0.5 / 0.5</t>
-        </is>
-      </c>
+      <c r="B16" s="11" t="inlineStr"/>
+      <c r="C16" s="11" t="inlineStr"/>
+      <c r="D16" s="12" t="inlineStr"/>
+      <c r="E16" s="11" t="inlineStr"/>
+      <c r="F16" s="11" t="inlineStr"/>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
@@ -1262,12 +1223,12 @@
       <c r="A26" s="2" t="n"/>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>e_kai_00101_vd_Normal_Yellow</t>
+          <t>c_kai_00002_vd_Boss_Yellow</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>怪獣 余獣</t>
+          <t>隠された英雄の姿 怪獣８号</t>
         </is>
       </c>
       <c r="D26" s="26" t="inlineStr">
@@ -1277,21 +1238,21 @@
       </c>
       <c r="E26" s="26" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="F26" s="29" t="n">
-        <v>25000</v>
+        <v>700000</v>
       </c>
       <c r="G26" s="26" t="n">
-        <v>350</v>
+        <v>1700</v>
       </c>
       <c r="H26" s="26" t="n">
         <v>45</v>
       </c>
       <c r="I26" s="26" t="inlineStr">
         <is>
-          <t>雑魚（e_キャラ）</t>
+          <t>ボス（c_キャラ・VD UR対抗）</t>
         </is>
       </c>
       <c r="J26" s="2" t="n"/>
@@ -1303,32 +1264,32 @@
       <c r="A27" s="2" t="n"/>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>e_glo_00001_vd_Normal_Colorless</t>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>ファントム</t>
+          <t>怪獣 余獣</t>
         </is>
       </c>
       <c r="D27" s="26" t="inlineStr">
         <is>
-          <t>Colorless（無属性）</t>
+          <t>Yellow（黄属性）</t>
         </is>
       </c>
       <c r="E27" s="26" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="F27" s="29" t="n">
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="G27" s="26" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="H27" s="26" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
@@ -1342,14 +1303,40 @@
     </row>
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="2" t="n"/>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="11" t="n"/>
-      <c r="I28" s="9" t="n"/>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Colorless（無属性）</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="F28" s="29" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G28" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="I28" s="26" t="inlineStr">
+        <is>
+          <t>雑魚（グロー汎用）</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
@@ -1559,26 +1546,30 @@
       </c>
       <c r="C40" s="26" t="inlineStr">
         <is>
-          <t>ElapsedTime</t>
+          <t>InitialSummon</t>
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E40" s="26" t="inlineStr">
         <is>
-          <t>e_glo_00001_vd_Normal_Colorless</t>
+          <t>c_kai_00002_vd_Boss_Yellow</t>
         </is>
       </c>
       <c r="F40" s="26" t="inlineStr">
         <is>
-          <t>ファントム</t>
+          <t>隠された英雄の姿 怪獣８号</t>
         </is>
       </c>
       <c r="G40" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="H40" s="26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>1体 / pos=1.7</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
@@ -1596,22 +1587,26 @@
         </is>
       </c>
       <c r="D41" s="26" t="n">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="E41" s="26" t="inlineStr">
         <is>
-          <t>e_kai_00101_vd_Normal_Yellow</t>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
         </is>
       </c>
       <c r="F41" s="26" t="inlineStr">
         <is>
-          <t>怪獣 余獣</t>
+          <t>ファントム</t>
         </is>
       </c>
       <c r="G41" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="H41" s="26" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>3体 / デフォルト</t>
+        </is>
+      </c>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
@@ -1629,22 +1624,26 @@
         </is>
       </c>
       <c r="D42" s="29" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="E42" s="26" t="inlineStr">
         <is>
-          <t>e_glo_00001_vd_Normal_Colorless</t>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
         </is>
       </c>
       <c r="F42" s="26" t="inlineStr">
         <is>
-          <t>ファントム</t>
+          <t>怪獣 余獣</t>
         </is>
       </c>
       <c r="G42" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="H42" s="26" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H42" s="26" t="inlineStr">
+        <is>
+          <t>5体 / デフォルト</t>
+        </is>
+      </c>
       <c r="I42" s="2" t="n"/>
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
@@ -1658,11 +1657,11 @@
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>ElapsedTime</t>
+          <t>FriendUnitDead</t>
         </is>
       </c>
       <c r="D43" s="29" t="n">
-        <v>5000</v>
+        <v>3</v>
       </c>
       <c r="E43" s="26" t="inlineStr">
         <is>
@@ -1675,9 +1674,13 @@
         </is>
       </c>
       <c r="G43" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="H43" s="26" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H43" s="26" t="inlineStr">
+        <is>
+          <t>8体 / デフォルト</t>
+        </is>
+      </c>
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
@@ -1691,26 +1694,30 @@
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>ElapsedTime</t>
+          <t>FriendUnitDead</t>
         </is>
       </c>
       <c r="D44" s="29" t="n">
-        <v>7000</v>
+        <v>3</v>
       </c>
       <c r="E44" s="26" t="inlineStr">
         <is>
-          <t>e_kai_00101_vd_Normal_Yellow</t>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
         </is>
       </c>
       <c r="F44" s="26" t="inlineStr">
         <is>
-          <t>怪獣 余獣</t>
+          <t>ファントム</t>
         </is>
       </c>
       <c r="G44" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="H44" s="26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H44" s="26" t="inlineStr">
+        <is>
+          <t>9体 / pos=2.8（elem=4と同タイミング）</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="n"/>
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
@@ -1719,13 +1726,35 @@
     </row>
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="2" t="n"/>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="11" t="n"/>
+      <c r="B45" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" s="26" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="F45" s="26" t="inlineStr">
+        <is>
+          <t>怪獣 余獣</t>
+        </is>
+      </c>
+      <c r="G45" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" s="26" t="inlineStr">
+        <is>
+          <t>12体 / デフォルト</t>
+        </is>
+      </c>
       <c r="I45" s="2" t="n"/>
       <c r="J45" s="2" t="n"/>
       <c r="K45" s="2" t="n"/>
@@ -1734,13 +1763,35 @@
     </row>
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="2" t="n"/>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="11" t="n"/>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="12" t="n"/>
-      <c r="F46" s="11" t="n"/>
-      <c r="G46" s="11" t="n"/>
-      <c r="H46" s="11" t="n"/>
+      <c r="B46" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>OutpostHpPercentage</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="F46" s="26" t="inlineStr">
+        <is>
+          <t>怪獣 余獣</t>
+        </is>
+      </c>
+      <c r="G46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" s="26" t="inlineStr">
+        <is>
+          <t>15体 / デフォルト（独立トリガー）</t>
+        </is>
+      </c>
       <c r="I46" s="2" t="n"/>
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
@@ -2052,10 +2103,3015 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M64"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="3.1640625" customWidth="1" min="1" max="1"/>
+    <col width="19.1640625" customWidth="1" min="2" max="2"/>
+    <col width="18.83203125" customWidth="1" min="3" max="10"/>
+    <col width="3.1640625" customWidth="1" min="11" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>ブロック基礎設計_vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="A2" s="6" t="n"/>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="13" customHeight="1">
+      <c r="A3" s="6" t="n"/>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>■要件テキスト</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="186" customHeight="1">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>ファントム（Colorless/Attack・HP5,000・ATK100・SPD34）が開幕250msと中間3,000msに各5体ずつ、怪獣 余獣（Yellow/Defense・HP25,000・ATK350・SPD45）が1,500ms・5,000ms・7,000msに各4体ずつ出現する5波構成、合計22体。ファントムが序盤のテンポを作りつつ、中盤以降は高HPでゆっくり前進する防御型の余獣が中心となり、Yellow属性対策を求める緊張感のある展開になる。
+コマは3行固定（各行独立抽選）。row1=4等分4コマ（0.25×4）・row2=右広い3コマ（0.50, 0.25, 0.25）・row3=2等分2コマ（0.50, 0.50）。幅の組み合わせに変化を持たせることで、コマ組みの選択肢を広げる。コマアセット: kai_00001（back_ground_offset: -1.0）。
+UR対抗キャラ「隠された英雄の姿 怪獣８号」（chara_kai_00002）対抗。Yellow/Defenseの余獣が主軸となるため、Yellow属性対策コマを活かしたプレイが有効になる設計。</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
+      <c r="H4" s="27" t="n"/>
+      <c r="I4" s="27" t="n"/>
+      <c r="J4" s="28" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="13" customHeight="1">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="13" customHeight="1">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>■基本情報</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>⇩ボスブロックのみに記載する</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>インゲームID</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>ブロック種別</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>敵ゲートHP</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>コマ行数</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>グループ切り替え</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>シーケンス行数</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>リリースキー</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>3行</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>なし（デフォルトグループのみ）</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>5行</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>202604010</v>
+      </c>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>※ノーマルブロックは3フロア固定で、ボスブロックは1フロア固定</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>■コマ効果</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>行</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>コマ数</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>コマアセット</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>コマ効果</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>レイアウト幅</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>行1</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>4コマ</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>0.25 / 0.25 / 0.25 / 0.25</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>行2</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>3コマ</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>0.5 / 0.25 / 0.25</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>行3</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>2コマ</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>0.5 / 0.5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>コマ効果1</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>効果時間</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>効果数値</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>■登場敵パラメータ</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>敵ID</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>キャラ名</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>属性</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>ロール</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>攻撃</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>移動速度</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>役割</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>怪獣 余獣</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Yellow（黄属性）</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="F26" s="29" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>350</v>
+      </c>
+      <c r="H26" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>雑魚（e_キャラ）</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Colorless（無属性）</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="F27" s="29" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G27" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="H27" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>雑魚（e_キャラ）</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="13" customHeight="1">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="9" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="13" customHeight="1">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="13" customHeight="1">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="9" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="13" customHeight="1">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+    </row>
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>■シーケンス構成</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+    </row>
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>行番号</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>トリガー種別</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>条件値（ms）</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>敵ID</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>キャラ名</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>体数</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="F40" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" s="26" t="inlineStr"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E41" s="26" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="F41" s="26" t="inlineStr">
+        <is>
+          <t>怪獣 余獣</t>
+        </is>
+      </c>
+      <c r="G41" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H41" s="26" t="inlineStr"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="D42" s="29" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="F42" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="G42" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" s="26" t="inlineStr"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E43" s="26" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="F43" s="26" t="inlineStr">
+        <is>
+          <t>怪獣 余獣</t>
+        </is>
+      </c>
+      <c r="G43" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H43" s="26" t="inlineStr"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="D44" s="29" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="F44" s="26" t="inlineStr">
+        <is>
+          <t>怪獣 余獣</t>
+        </is>
+      </c>
+      <c r="G44" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" s="26" t="inlineStr"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+    </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="11" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
+    </row>
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="11" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
+    </row>
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="11" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="11" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n"/>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="11" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="11" t="n"/>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="11" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="11" t="n"/>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="15" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="11" t="n"/>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="11" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n"/>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="15" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="11" t="n"/>
+      <c r="G52" s="11" t="n"/>
+      <c r="H52" s="11" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n"/>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="11" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="11" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n"/>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="16" t="n"/>
+      <c r="B54" s="16" t="n"/>
+      <c r="C54" s="16" t="n"/>
+      <c r="D54" s="16" t="n"/>
+      <c r="E54" s="16" t="n"/>
+      <c r="F54" s="16" t="n"/>
+      <c r="G54" s="16" t="n"/>
+      <c r="H54" s="16" t="n"/>
+      <c r="I54" s="16" t="n"/>
+      <c r="J54" s="16" t="n"/>
+      <c r="K54" s="16" t="n"/>
+      <c r="L54" s="16" t="n"/>
+      <c r="M54" s="16" t="n"/>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="16" t="n"/>
+      <c r="B55" s="16" t="n"/>
+      <c r="C55" s="16" t="n"/>
+      <c r="D55" s="16" t="n"/>
+      <c r="E55" s="16" t="n"/>
+      <c r="F55" s="16" t="n"/>
+      <c r="G55" s="16" t="n"/>
+      <c r="H55" s="16" t="n"/>
+      <c r="I55" s="16" t="n"/>
+      <c r="J55" s="16" t="n"/>
+      <c r="K55" s="16" t="n"/>
+      <c r="L55" s="16" t="n"/>
+      <c r="M55" s="16" t="n"/>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="16" t="n"/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>■ステージ説明文</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="16" t="n"/>
+      <c r="F56" s="16" t="n"/>
+      <c r="G56" s="16" t="n"/>
+      <c r="H56" s="16" t="n"/>
+      <c r="I56" s="16" t="n"/>
+      <c r="J56" s="16" t="n"/>
+      <c r="K56" s="16" t="n"/>
+      <c r="L56" s="16" t="n"/>
+      <c r="M56" s="16" t="n"/>
+    </row>
+    <row r="57" ht="13" customHeight="1">
+      <c r="A57" s="16" t="n"/>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D57" s="27" t="n"/>
+      <c r="E57" s="27" t="n"/>
+      <c r="F57" s="27" t="n"/>
+      <c r="G57" s="28" t="n"/>
+      <c r="H57" s="16" t="n"/>
+      <c r="I57" s="16" t="n"/>
+      <c r="J57" s="16" t="n"/>
+      <c r="K57" s="16" t="n"/>
+      <c r="L57" s="16" t="n"/>
+      <c r="M57" s="16" t="n"/>
+    </row>
+    <row r="58" ht="13" customHeight="1">
+      <c r="A58" s="16" t="n"/>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>バトルヒント</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr"/>
+      <c r="D58" s="27" t="n"/>
+      <c r="E58" s="27" t="n"/>
+      <c r="F58" s="27" t="n"/>
+      <c r="G58" s="28" t="n"/>
+      <c r="H58" s="16" t="n"/>
+      <c r="I58" s="16" t="n"/>
+      <c r="J58" s="16" t="n"/>
+      <c r="K58" s="16" t="n"/>
+      <c r="L58" s="16" t="n"/>
+      <c r="M58" s="16" t="n"/>
+    </row>
+    <row r="59" ht="13" customHeight="1">
+      <c r="A59" s="16" t="n"/>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>ステージ説明文</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr"/>
+      <c r="D59" s="27" t="n"/>
+      <c r="E59" s="27" t="n"/>
+      <c r="F59" s="27" t="n"/>
+      <c r="G59" s="28" t="n"/>
+      <c r="H59" s="16" t="n"/>
+      <c r="I59" s="16" t="n"/>
+      <c r="J59" s="16" t="n"/>
+      <c r="K59" s="16" t="n"/>
+      <c r="L59" s="16" t="n"/>
+      <c r="M59" s="16" t="n"/>
+    </row>
+    <row r="60" ht="13" customHeight="1">
+      <c r="A60" s="16" t="n"/>
+      <c r="B60" s="16" t="n"/>
+      <c r="C60" s="16" t="n"/>
+      <c r="D60" s="16" t="n"/>
+      <c r="E60" s="16" t="n"/>
+      <c r="F60" s="16" t="n"/>
+      <c r="G60" s="16" t="n"/>
+      <c r="H60" s="16" t="n"/>
+      <c r="I60" s="16" t="n"/>
+      <c r="J60" s="16" t="n"/>
+      <c r="K60" s="16" t="n"/>
+      <c r="L60" s="16" t="n"/>
+      <c r="M60" s="16" t="n"/>
+    </row>
+    <row r="61" ht="13" customHeight="1">
+      <c r="A61" s="19" t="n"/>
+      <c r="B61" s="19" t="n"/>
+      <c r="C61" s="19" t="n"/>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="19" t="n"/>
+      <c r="G61" s="19" t="n"/>
+      <c r="H61" s="19" t="n"/>
+      <c r="I61" s="19" t="n"/>
+      <c r="J61" s="19" t="n"/>
+      <c r="K61" s="19" t="n"/>
+      <c r="L61" s="19" t="n"/>
+      <c r="M61" s="19" t="n"/>
+    </row>
+    <row r="62" ht="13" customHeight="1">
+      <c r="A62" s="19" t="n"/>
+      <c r="B62" s="19" t="n"/>
+      <c r="C62" s="19" t="n"/>
+      <c r="D62" s="19" t="n"/>
+      <c r="E62" s="19" t="n"/>
+      <c r="F62" s="19" t="n"/>
+      <c r="G62" s="19" t="n"/>
+      <c r="H62" s="19" t="n"/>
+      <c r="I62" s="19" t="n"/>
+      <c r="J62" s="19" t="n"/>
+      <c r="K62" s="19" t="n"/>
+      <c r="L62" s="19" t="n"/>
+      <c r="M62" s="19" t="n"/>
+    </row>
+    <row r="63" ht="13" customHeight="1">
+      <c r="A63" s="19" t="n"/>
+      <c r="B63" s="19" t="n"/>
+      <c r="C63" s="19" t="n"/>
+      <c r="D63" s="19" t="n"/>
+      <c r="E63" s="19" t="n"/>
+      <c r="F63" s="19" t="n"/>
+      <c r="G63" s="19" t="n"/>
+      <c r="H63" s="19" t="n"/>
+      <c r="I63" s="19" t="n"/>
+      <c r="J63" s="19" t="n"/>
+      <c r="K63" s="19" t="n"/>
+      <c r="L63" s="19" t="n"/>
+      <c r="M63" s="19" t="n"/>
+    </row>
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="19" t="n"/>
+      <c r="B64" s="19" t="n"/>
+      <c r="C64" s="19" t="n"/>
+      <c r="D64" s="19" t="n"/>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="19" t="n"/>
+      <c r="G64" s="19" t="n"/>
+      <c r="H64" s="19" t="n"/>
+      <c r="I64" s="19" t="n"/>
+      <c r="J64" s="19" t="n"/>
+      <c r="K64" s="19" t="n"/>
+      <c r="L64" s="19" t="n"/>
+      <c r="M64" s="19" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="B4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M64"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="3.1640625" customWidth="1" min="1" max="1"/>
+    <col width="19.1640625" customWidth="1" min="2" max="2"/>
+    <col width="18.83203125" customWidth="1" min="3" max="10"/>
+    <col width="3.1640625" customWidth="1" min="11" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>ブロック基礎設計_vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="A2" s="6" t="n"/>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="13" customHeight="1">
+      <c r="A3" s="6" t="n"/>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>■要件テキスト</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="186" customHeight="1">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>開幕 ElapsedTime=250ms でファントムが3体出現し、コマ0・コマ1・コマ2 到達ごとにファントムが伏兵として2〜3体追加される。ElapsedTime=2500ms で黒川あかね（`c_osh_00501`・HP低め）が最初のc_キャラとして登場し、以降は6体・10体・15体倒すたびに星野ルビー→MEMちょ→有馬かなが1体ずつ Bossオーラ付きで順番に登場する。16体全員倒した後はファントムが無限補充に切り替わってステージが継続する。
+ElapsedTime / EnterTargetKomaIndex / FriendUnitDead の3種のトリガーを組み合わせることで、時間・コマ進行・倒した数の3軸からプレッシャーを与える構成。コマを進めるほど伏兵が増え、倒すほど強いキャラが次々と登場するスパイラル構造。
+コマは3行構成。row1 はパターン6（2コマ均等 0.5/0.5）、row2 はパターン9（3コマ 中央広め 0.25/0.5/0.25）、row3 はパターン12（4コマ均等 0.25×4）で、コマ数が行ごとに増える段階的なレイアウト。コマアセットキーは `osh_00001`（back_ground_offset = -1.0）。
+UR対抗キャラ「B小町不動のセンター アイ（`chara_osh_00001`）」のGreen属性コマ効果・オーラを最大限に活かして、コマ伏兵を素早く処理しながらB小町メンバーを撃破する立ち回りを要求する設計。</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
+      <c r="H4" s="27" t="n"/>
+      <c r="I4" s="27" t="n"/>
+      <c r="J4" s="28" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="13" customHeight="1">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="13" customHeight="1">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>■基本情報</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>⇩ボスブロックのみに記載する</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>インゲームID</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>ブロック種別</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>敵ゲートHP</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>コマ行数</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>グループ切り替え</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>シーケンス行数</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>リリースキー</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>3行</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>なし（デフォルトグループのみ）</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>11行</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>202604010</v>
+      </c>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>※ノーマルブロックは3フロア固定で、ボスブロックは1フロア固定</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>■コマ効果</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>行</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>コマ数</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>コマアセット</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>コマ効果</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>レイアウト幅</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>行1</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>2コマ</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>0.5 / 0.5</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>行2</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>3コマ</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>0.25 / 0.5 / 0.25</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>行3</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>4コマ</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>0.25 / 0.25 / 0.25 / 0.25</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>コマ効果1</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>効果時間</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>効果数値</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>■登場敵パラメータ</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>敵ID</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>キャラ名</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>属性</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>ロール</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>攻撃</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>移動速度</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>役割</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Colorless（無属性）</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="F26" s="29" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="H26" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>雑魚（e_キャラ）</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00501_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>黒川 あかね</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Green（緑属性）</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="F27" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G27" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="H27" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>c_キャラ（Bossオーラ）1体目</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="13" customHeight="1">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00201_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>星野 ルビー</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Green（緑属性）</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="F28" s="29" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G28" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="H28" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="26" t="inlineStr">
+        <is>
+          <t>c_キャラ（Bossオーラ）2体目</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="13" customHeight="1">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00301_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>MEMちょ</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Green（緑属性）</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F29" s="29" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G29" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="H29" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="26" t="inlineStr">
+        <is>
+          <t>c_キャラ（Bossオーラ）3体目</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="13" customHeight="1">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00401_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>有馬 かな</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>Green（緑属性）</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="F30" s="29" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G30" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="H30" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="I30" s="26" t="inlineStr">
+        <is>
+          <t>c_キャラ（Bossオーラ）4体目</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="13" customHeight="1">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+    </row>
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>■シーケンス構成</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+    </row>
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>行番号</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>トリガー種別</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>条件値（ms）</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>敵ID</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>キャラ名</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>体数</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="F40" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>開幕ウェーブ</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>EnterTargetKomaIndex</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="F41" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="G41" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>コマ0伏兵</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="D42" s="29" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00501_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="F42" s="26" t="inlineStr">
+        <is>
+          <t>黒川 あかね</t>
+        </is>
+      </c>
+      <c r="G42" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="26" t="inlineStr">
+        <is>
+          <t>黒川あかね（1体目c_）</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>EnterTargetKomaIndex</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="F43" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="G43" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" s="26" t="inlineStr">
+        <is>
+          <t>コマ1伏兵</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="D44" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00201_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="F44" s="26" t="inlineStr">
+        <is>
+          <t>星野 ルビー</t>
+        </is>
+      </c>
+      <c r="G44" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="26" t="inlineStr">
+        <is>
+          <t>星野ルビー（2体目c_）elem1+2+3全滅後</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+    </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="F45" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="G45" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="26" t="inlineStr">
+        <is>
+          <t>補充（elem5と同タイミング）</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>EnterTargetKomaIndex</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="F46" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="G46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" s="26" t="inlineStr">
+        <is>
+          <t>コマ2伏兵</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
+    </row>
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00301_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="F47" s="26" t="inlineStr">
+        <is>
+          <t>MEMちょ</t>
+        </is>
+      </c>
+      <c r="G47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="26" t="inlineStr">
+        <is>
+          <t>MEMちょ（3体目c_）</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
+    </row>
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="F48" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" s="26" t="inlineStr">
+        <is>
+          <t>補充（elem8と同タイミング）</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n"/>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="E49" s="26" t="inlineStr">
+        <is>
+          <t>c_osh_00401_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="F49" s="26" t="inlineStr">
+        <is>
+          <t>有馬 かな</t>
+        </is>
+      </c>
+      <c r="G49" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="26" t="inlineStr">
+        <is>
+          <t>有馬かな（4体目c_）</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="F50" s="26" t="inlineStr">
+        <is>
+          <t>ファントム</t>
+        </is>
+      </c>
+      <c r="G50" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="H50" s="26" t="inlineStr">
+        <is>
+          <t>終盤無限補充（elem10と同タイミング）</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="11" t="n"/>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="15" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="11" t="n"/>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="11" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n"/>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="15" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="11" t="n"/>
+      <c r="G52" s="11" t="n"/>
+      <c r="H52" s="11" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n"/>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="11" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="11" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n"/>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="16" t="n"/>
+      <c r="B54" s="16" t="n"/>
+      <c r="C54" s="16" t="n"/>
+      <c r="D54" s="16" t="n"/>
+      <c r="E54" s="16" t="n"/>
+      <c r="F54" s="16" t="n"/>
+      <c r="G54" s="16" t="n"/>
+      <c r="H54" s="16" t="n"/>
+      <c r="I54" s="16" t="n"/>
+      <c r="J54" s="16" t="n"/>
+      <c r="K54" s="16" t="n"/>
+      <c r="L54" s="16" t="n"/>
+      <c r="M54" s="16" t="n"/>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="16" t="n"/>
+      <c r="B55" s="16" t="n"/>
+      <c r="C55" s="16" t="n"/>
+      <c r="D55" s="16" t="n"/>
+      <c r="E55" s="16" t="n"/>
+      <c r="F55" s="16" t="n"/>
+      <c r="G55" s="16" t="n"/>
+      <c r="H55" s="16" t="n"/>
+      <c r="I55" s="16" t="n"/>
+      <c r="J55" s="16" t="n"/>
+      <c r="K55" s="16" t="n"/>
+      <c r="L55" s="16" t="n"/>
+      <c r="M55" s="16" t="n"/>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="16" t="n"/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>■ステージ説明文</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="16" t="n"/>
+      <c r="F56" s="16" t="n"/>
+      <c r="G56" s="16" t="n"/>
+      <c r="H56" s="16" t="n"/>
+      <c r="I56" s="16" t="n"/>
+      <c r="J56" s="16" t="n"/>
+      <c r="K56" s="16" t="n"/>
+      <c r="L56" s="16" t="n"/>
+      <c r="M56" s="16" t="n"/>
+    </row>
+    <row r="57" ht="13" customHeight="1">
+      <c r="A57" s="16" t="n"/>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D57" s="27" t="n"/>
+      <c r="E57" s="27" t="n"/>
+      <c r="F57" s="27" t="n"/>
+      <c r="G57" s="28" t="n"/>
+      <c r="H57" s="16" t="n"/>
+      <c r="I57" s="16" t="n"/>
+      <c r="J57" s="16" t="n"/>
+      <c r="K57" s="16" t="n"/>
+      <c r="L57" s="16" t="n"/>
+      <c r="M57" s="16" t="n"/>
+    </row>
+    <row r="58" ht="13" customHeight="1">
+      <c r="A58" s="16" t="n"/>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>バトルヒント</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr"/>
+      <c r="D58" s="27" t="n"/>
+      <c r="E58" s="27" t="n"/>
+      <c r="F58" s="27" t="n"/>
+      <c r="G58" s="28" t="n"/>
+      <c r="H58" s="16" t="n"/>
+      <c r="I58" s="16" t="n"/>
+      <c r="J58" s="16" t="n"/>
+      <c r="K58" s="16" t="n"/>
+      <c r="L58" s="16" t="n"/>
+      <c r="M58" s="16" t="n"/>
+    </row>
+    <row r="59" ht="13" customHeight="1">
+      <c r="A59" s="16" t="n"/>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>ステージ説明文</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr"/>
+      <c r="D59" s="27" t="n"/>
+      <c r="E59" s="27" t="n"/>
+      <c r="F59" s="27" t="n"/>
+      <c r="G59" s="28" t="n"/>
+      <c r="H59" s="16" t="n"/>
+      <c r="I59" s="16" t="n"/>
+      <c r="J59" s="16" t="n"/>
+      <c r="K59" s="16" t="n"/>
+      <c r="L59" s="16" t="n"/>
+      <c r="M59" s="16" t="n"/>
+    </row>
+    <row r="60" ht="13" customHeight="1">
+      <c r="A60" s="16" t="n"/>
+      <c r="B60" s="16" t="n"/>
+      <c r="C60" s="16" t="n"/>
+      <c r="D60" s="16" t="n"/>
+      <c r="E60" s="16" t="n"/>
+      <c r="F60" s="16" t="n"/>
+      <c r="G60" s="16" t="n"/>
+      <c r="H60" s="16" t="n"/>
+      <c r="I60" s="16" t="n"/>
+      <c r="J60" s="16" t="n"/>
+      <c r="K60" s="16" t="n"/>
+      <c r="L60" s="16" t="n"/>
+      <c r="M60" s="16" t="n"/>
+    </row>
+    <row r="61" ht="13" customHeight="1">
+      <c r="A61" s="19" t="n"/>
+      <c r="B61" s="19" t="n"/>
+      <c r="C61" s="19" t="n"/>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="19" t="n"/>
+      <c r="G61" s="19" t="n"/>
+      <c r="H61" s="19" t="n"/>
+      <c r="I61" s="19" t="n"/>
+      <c r="J61" s="19" t="n"/>
+      <c r="K61" s="19" t="n"/>
+      <c r="L61" s="19" t="n"/>
+      <c r="M61" s="19" t="n"/>
+    </row>
+    <row r="62" ht="13" customHeight="1">
+      <c r="A62" s="19" t="n"/>
+      <c r="B62" s="19" t="n"/>
+      <c r="C62" s="19" t="n"/>
+      <c r="D62" s="19" t="n"/>
+      <c r="E62" s="19" t="n"/>
+      <c r="F62" s="19" t="n"/>
+      <c r="G62" s="19" t="n"/>
+      <c r="H62" s="19" t="n"/>
+      <c r="I62" s="19" t="n"/>
+      <c r="J62" s="19" t="n"/>
+      <c r="K62" s="19" t="n"/>
+      <c r="L62" s="19" t="n"/>
+      <c r="M62" s="19" t="n"/>
+    </row>
+    <row r="63" ht="13" customHeight="1">
+      <c r="A63" s="19" t="n"/>
+      <c r="B63" s="19" t="n"/>
+      <c r="C63" s="19" t="n"/>
+      <c r="D63" s="19" t="n"/>
+      <c r="E63" s="19" t="n"/>
+      <c r="F63" s="19" t="n"/>
+      <c r="G63" s="19" t="n"/>
+      <c r="H63" s="19" t="n"/>
+      <c r="I63" s="19" t="n"/>
+      <c r="J63" s="19" t="n"/>
+      <c r="K63" s="19" t="n"/>
+      <c r="L63" s="19" t="n"/>
+      <c r="M63" s="19" t="n"/>
+    </row>
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="19" t="n"/>
+      <c r="B64" s="19" t="n"/>
+      <c r="C64" s="19" t="n"/>
+      <c r="D64" s="19" t="n"/>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="19" t="n"/>
+      <c r="G64" s="19" t="n"/>
+      <c r="H64" s="19" t="n"/>
+      <c r="I64" s="19" t="n"/>
+      <c r="J64" s="19" t="n"/>
+      <c r="K64" s="19" t="n"/>
+      <c r="L64" s="19" t="n"/>
+      <c r="M64" s="19" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="B4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2202,31 +5258,39 @@
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="C2" s="31" t="inlineStr"/>
+          <t>vd_kai_boss_00001</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_boss_00001</t>
+        </is>
+      </c>
       <c r="D2" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
+          <t>vd_kai_boss_00001</t>
         </is>
       </c>
       <c r="E2" s="31" t="inlineStr">
         <is>
-          <t>SSE_SBG_003_010</t>
+          <t>SSE_SBG_003_004</t>
         </is>
       </c>
       <c r="F2" s="31" t="inlineStr"/>
-      <c r="G2" s="31" t="inlineStr"/>
+      <c r="G2" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
       <c r="H2" s="31" t="inlineStr"/>
       <c r="I2" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
+          <t>vd_kai_boss_00001</t>
         </is>
       </c>
       <c r="J2" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
+          <t>vd_kai_boss_00001</t>
         </is>
       </c>
       <c r="K2" s="31" t="inlineStr">
@@ -2234,7 +5298,11 @@
           <t>__NULL__</t>
         </is>
       </c>
-      <c r="L2" s="31" t="inlineStr"/>
+      <c r="L2" s="31" t="inlineStr">
+        <is>
+          <t>c_kai_00002_vd_Boss_Yellow</t>
+        </is>
+      </c>
       <c r="M2" s="31" t="inlineStr">
         <is>
           <t>__NULL__</t>
@@ -2277,19 +5345,189 @@
       </c>
       <c r="U2" s="31" t="inlineStr"/>
       <c r="V2" s="31" t="inlineStr"/>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr"/>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>SSE_SBG_003_010</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr"/>
+      <c r="G4" s="31" t="inlineStr"/>
+      <c r="H4" s="31" t="inlineStr"/>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="J4" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="K4" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="L4" s="31" t="inlineStr"/>
+      <c r="M4" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="N4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="S4" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="T4" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+      <c r="U4" s="31" t="inlineStr"/>
+      <c r="V4" s="31" t="inlineStr"/>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr"/>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>SSE_SBG_003_010</t>
+        </is>
+      </c>
+      <c r="F6" s="31" t="inlineStr"/>
+      <c r="G6" s="31" t="inlineStr"/>
+      <c r="H6" s="31" t="inlineStr"/>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="J6" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="K6" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="L6" s="31" t="inlineStr"/>
+      <c r="M6" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="N6" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="O6" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P6" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q6" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R6" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="S6" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="T6" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+      <c r="U6" s="31" t="inlineStr"/>
+      <c r="V6" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2346,12 +5584,12 @@
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
+          <t>vd_kai_boss_00001</t>
         </is>
       </c>
       <c r="C2" s="31" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D2" s="31" t="inlineStr">
@@ -2362,6 +5600,66 @@
       <c r="E2" s="31" t="inlineStr"/>
       <c r="F2" s="31" t="inlineStr"/>
       <c r="G2" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr"/>
+      <c r="F4" s="31" t="inlineStr"/>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr"/>
+      <c r="F6" s="31" t="inlineStr"/>
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -2372,13 +5670,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2651,12 +5949,12 @@
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001_1</t>
+          <t>vd_kai_boss_00001_1</t>
         </is>
       </c>
       <c r="C2" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
+          <t>vd_kai_boss_00001</t>
         </is>
       </c>
       <c r="D2" s="31" t="inlineStr">
@@ -2666,12 +5964,12 @@
       </c>
       <c r="E2" s="31" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F2" s="31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G2" s="31" t="inlineStr">
@@ -2681,7 +5979,7 @@
       </c>
       <c r="H2" s="31" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I2" s="31" t="inlineStr">
@@ -2726,7 +6024,7 @@
       </c>
       <c r="Q2" s="31" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="R2" s="31" t="inlineStr"/>
@@ -2752,16 +6050,8 @@
           <t>All</t>
         </is>
       </c>
-      <c r="Y2" s="31" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
-      <c r="Z2" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
+      <c r="Y2" s="31" t="inlineStr"/>
+      <c r="Z2" s="31" t="inlineStr"/>
       <c r="AA2" s="31" t="inlineStr"/>
       <c r="AB2" s="31" t="inlineStr">
         <is>
@@ -2773,16 +6063,8 @@
       <c r="AE2" s="31" t="inlineStr"/>
       <c r="AF2" s="31" t="inlineStr"/>
       <c r="AG2" s="31" t="inlineStr"/>
-      <c r="AH2" s="31" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
-      <c r="AI2" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
+      <c r="AH2" s="31" t="inlineStr"/>
+      <c r="AI2" s="31" t="inlineStr"/>
       <c r="AJ2" s="31" t="inlineStr"/>
       <c r="AK2" s="31" t="inlineStr">
         <is>
@@ -2800,155 +6082,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B3" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001_2</t>
-        </is>
-      </c>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t>vd_kai_normal_00001</t>
-        </is>
-      </c>
-      <c r="D3" s="31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E3" s="31" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="F3" s="31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G3" s="31" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
-      <c r="H3" s="31" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I3" s="31" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" s="31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="N3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="O3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="P3" s="31" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
-      <c r="Q3" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="R3" s="31" t="inlineStr"/>
-      <c r="S3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T3" s="31" t="inlineStr"/>
-      <c r="U3" s="31" t="inlineStr"/>
-      <c r="V3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="W3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="X3" s="31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="Y3" s="31" t="inlineStr">
-        <is>
-          <t>kai_00001</t>
-        </is>
-      </c>
-      <c r="Z3" s="31" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AA3" s="31" t="inlineStr"/>
-      <c r="AB3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AC3" s="31" t="inlineStr"/>
-      <c r="AD3" s="31" t="inlineStr"/>
-      <c r="AE3" s="31" t="inlineStr"/>
-      <c r="AF3" s="31" t="inlineStr"/>
-      <c r="AG3" s="31" t="inlineStr"/>
-      <c r="AH3" s="31" t="inlineStr"/>
-      <c r="AI3" s="31" t="inlineStr"/>
-      <c r="AJ3" s="31" t="inlineStr"/>
-      <c r="AK3" s="31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AL3" s="31" t="inlineStr"/>
-      <c r="AM3" s="31" t="inlineStr"/>
-      <c r="AN3" s="31" t="inlineStr"/>
-      <c r="AO3" s="31" t="inlineStr"/>
-      <c r="AP3" s="31" t="inlineStr"/>
-      <c r="AQ3" s="31" t="inlineStr">
-        <is>
-          <t>202604010</t>
-        </is>
-      </c>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -2957,7 +6091,7 @@
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001_3</t>
+          <t>vd_kai_normal_00001_1</t>
         </is>
       </c>
       <c r="C4" s="31" t="inlineStr">
@@ -2967,17 +6101,17 @@
       </c>
       <c r="D4" s="31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="31" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F4" s="31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G4" s="31" t="inlineStr">
@@ -2987,7 +6121,7 @@
       </c>
       <c r="H4" s="31" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I4" s="31" t="inlineStr">
@@ -3032,7 +6166,7 @@
       </c>
       <c r="Q4" s="31" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="R4" s="31" t="inlineStr"/>
@@ -3058,8 +6192,16 @@
           <t>All</t>
         </is>
       </c>
-      <c r="Y4" s="31" t="inlineStr"/>
-      <c r="Z4" s="31" t="inlineStr"/>
+      <c r="Y4" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="Z4" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
       <c r="AA4" s="31" t="inlineStr"/>
       <c r="AB4" s="31" t="inlineStr">
         <is>
@@ -3071,8 +6213,16 @@
       <c r="AE4" s="31" t="inlineStr"/>
       <c r="AF4" s="31" t="inlineStr"/>
       <c r="AG4" s="31" t="inlineStr"/>
-      <c r="AH4" s="31" t="inlineStr"/>
-      <c r="AI4" s="31" t="inlineStr"/>
+      <c r="AH4" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="AI4" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
       <c r="AJ4" s="31" t="inlineStr"/>
       <c r="AK4" s="31" t="inlineStr">
         <is>
@@ -3090,27 +6240,765 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001_2</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="N5" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O5" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="P5" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="Q5" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="R5" s="31" t="inlineStr"/>
+      <c r="S5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T5" s="31" t="inlineStr"/>
+      <c r="U5" s="31" t="inlineStr"/>
+      <c r="V5" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W5" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X5" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Y5" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="Z5" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA5" s="31" t="inlineStr"/>
+      <c r="AB5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC5" s="31" t="inlineStr"/>
+      <c r="AD5" s="31" t="inlineStr"/>
+      <c r="AE5" s="31" t="inlineStr"/>
+      <c r="AF5" s="31" t="inlineStr"/>
+      <c r="AG5" s="31" t="inlineStr"/>
+      <c r="AH5" s="31" t="inlineStr"/>
+      <c r="AI5" s="31" t="inlineStr"/>
+      <c r="AJ5" s="31" t="inlineStr"/>
+      <c r="AK5" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL5" s="31" t="inlineStr"/>
+      <c r="AM5" s="31" t="inlineStr"/>
+      <c r="AN5" s="31" t="inlineStr"/>
+      <c r="AO5" s="31" t="inlineStr"/>
+      <c r="AP5" s="31" t="inlineStr"/>
+      <c r="AQ5" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001_3</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="H6" s="31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="N6" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O6" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="P6" s="31" t="inlineStr">
+        <is>
+          <t>kai_00001</t>
+        </is>
+      </c>
+      <c r="Q6" s="31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="R6" s="31" t="inlineStr"/>
+      <c r="S6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T6" s="31" t="inlineStr"/>
+      <c r="U6" s="31" t="inlineStr"/>
+      <c r="V6" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W6" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X6" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Y6" s="31" t="inlineStr"/>
+      <c r="Z6" s="31" t="inlineStr"/>
+      <c r="AA6" s="31" t="inlineStr"/>
+      <c r="AB6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC6" s="31" t="inlineStr"/>
+      <c r="AD6" s="31" t="inlineStr"/>
+      <c r="AE6" s="31" t="inlineStr"/>
+      <c r="AF6" s="31" t="inlineStr"/>
+      <c r="AG6" s="31" t="inlineStr"/>
+      <c r="AH6" s="31" t="inlineStr"/>
+      <c r="AI6" s="31" t="inlineStr"/>
+      <c r="AJ6" s="31" t="inlineStr"/>
+      <c r="AK6" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL6" s="31" t="inlineStr"/>
+      <c r="AM6" s="31" t="inlineStr"/>
+      <c r="AN6" s="31" t="inlineStr"/>
+      <c r="AO6" s="31" t="inlineStr"/>
+      <c r="AP6" s="31" t="inlineStr"/>
+      <c r="AQ6" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_1</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G8" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="H8" s="31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="N8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="P8" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="Q8" s="31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="R8" s="31" t="inlineStr"/>
+      <c r="S8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T8" s="31" t="inlineStr"/>
+      <c r="U8" s="31" t="inlineStr"/>
+      <c r="V8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X8" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Y8" s="31" t="inlineStr"/>
+      <c r="Z8" s="31" t="inlineStr"/>
+      <c r="AA8" s="31" t="inlineStr"/>
+      <c r="AB8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC8" s="31" t="inlineStr"/>
+      <c r="AD8" s="31" t="inlineStr"/>
+      <c r="AE8" s="31" t="inlineStr"/>
+      <c r="AF8" s="31" t="inlineStr"/>
+      <c r="AG8" s="31" t="inlineStr"/>
+      <c r="AH8" s="31" t="inlineStr"/>
+      <c r="AI8" s="31" t="inlineStr"/>
+      <c r="AJ8" s="31" t="inlineStr"/>
+      <c r="AK8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL8" s="31" t="inlineStr"/>
+      <c r="AM8" s="31" t="inlineStr"/>
+      <c r="AN8" s="31" t="inlineStr"/>
+      <c r="AO8" s="31" t="inlineStr"/>
+      <c r="AP8" s="31" t="inlineStr"/>
+      <c r="AQ8" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_2</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G9" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="H9" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="I9" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K9" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="N9" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O9" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="P9" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="Q9" s="31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="R9" s="31" t="inlineStr"/>
+      <c r="S9" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T9" s="31" t="inlineStr"/>
+      <c r="U9" s="31" t="inlineStr"/>
+      <c r="V9" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W9" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X9" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Y9" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="Z9" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA9" s="31" t="inlineStr"/>
+      <c r="AB9" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC9" s="31" t="inlineStr"/>
+      <c r="AD9" s="31" t="inlineStr"/>
+      <c r="AE9" s="31" t="inlineStr"/>
+      <c r="AF9" s="31" t="inlineStr"/>
+      <c r="AG9" s="31" t="inlineStr"/>
+      <c r="AH9" s="31" t="inlineStr"/>
+      <c r="AI9" s="31" t="inlineStr"/>
+      <c r="AJ9" s="31" t="inlineStr"/>
+      <c r="AK9" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL9" s="31" t="inlineStr"/>
+      <c r="AM9" s="31" t="inlineStr"/>
+      <c r="AN9" s="31" t="inlineStr"/>
+      <c r="AO9" s="31" t="inlineStr"/>
+      <c r="AP9" s="31" t="inlineStr"/>
+      <c r="AQ9" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_3</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="N10" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O10" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="P10" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="Q10" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="R10" s="31" t="inlineStr"/>
+      <c r="S10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T10" s="31" t="inlineStr"/>
+      <c r="U10" s="31" t="inlineStr"/>
+      <c r="V10" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W10" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="X10" s="31" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="Y10" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="Z10" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA10" s="31" t="inlineStr"/>
+      <c r="AB10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AC10" s="31" t="inlineStr"/>
+      <c r="AD10" s="31" t="inlineStr"/>
+      <c r="AE10" s="31" t="inlineStr"/>
+      <c r="AF10" s="31" t="inlineStr"/>
+      <c r="AG10" s="31" t="inlineStr"/>
+      <c r="AH10" s="31" t="inlineStr">
+        <is>
+          <t>osh_00001</t>
+        </is>
+      </c>
+      <c r="AI10" s="31" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AJ10" s="31" t="inlineStr"/>
+      <c r="AK10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AL10" s="31" t="inlineStr"/>
+      <c r="AM10" s="31" t="inlineStr"/>
+      <c r="AN10" s="31" t="inlineStr"/>
+      <c r="AO10" s="31" t="inlineStr"/>
+      <c r="AP10" s="31" t="inlineStr"/>
+      <c r="AQ10" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="33" customWidth="1" min="10" max="10"/>
@@ -3326,18 +7214,18 @@
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001_1</t>
+          <t>vd_kai_boss_00001_1</t>
         </is>
       </c>
       <c r="C2" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
+          <t>vd_kai_boss_00001</t>
         </is>
       </c>
       <c r="D2" s="31" t="inlineStr"/>
       <c r="E2" s="31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>vd_kai_boss_00001_1</t>
         </is>
       </c>
       <c r="F2" s="31" t="inlineStr">
@@ -3347,12 +7235,12 @@
       </c>
       <c r="G2" s="31" t="inlineStr">
         <is>
-          <t>ElapsedTime</t>
+          <t>InitialSummon</t>
         </is>
       </c>
       <c r="H2" s="31" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="31" t="inlineStr">
@@ -3362,13 +7250,13 @@
       </c>
       <c r="J2" s="31" t="inlineStr">
         <is>
-          <t>e_glo_00001_vd_Normal_Colorless</t>
+          <t>c_kai_00002_vd_Boss_Yellow</t>
         </is>
       </c>
       <c r="K2" s="31" t="inlineStr"/>
       <c r="L2" s="31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" s="31" t="inlineStr">
@@ -3383,17 +7271,17 @@
       </c>
       <c r="O2" s="31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="P2" s="31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="Q2" s="31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R2" s="31" t="inlineStr">
@@ -3433,7 +7321,7 @@
       </c>
       <c r="Y2" s="31" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="Z2" s="31" t="inlineStr">
@@ -3456,7 +7344,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="AD2" s="31" t="inlineStr"/>
+      <c r="AD2" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
           <t>0</t>
@@ -3487,18 +7379,18 @@
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001_2</t>
+          <t>vd_kai_boss_00001_2</t>
         </is>
       </c>
       <c r="C3" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
+          <t>vd_kai_boss_00001</t>
         </is>
       </c>
       <c r="D3" s="31" t="inlineStr"/>
       <c r="E3" s="31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>vd_kai_boss_00001_2</t>
         </is>
       </c>
       <c r="F3" s="31" t="inlineStr">
@@ -3513,7 +7405,7 @@
       </c>
       <c r="H3" s="31" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I3" s="31" t="inlineStr">
@@ -3523,18 +7415,18 @@
       </c>
       <c r="J3" s="31" t="inlineStr">
         <is>
-          <t>e_kai_00101_vd_Normal_Yellow</t>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
         </is>
       </c>
       <c r="K3" s="31" t="inlineStr"/>
       <c r="L3" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" s="31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N3" s="31" t="inlineStr">
@@ -3617,7 +7509,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="AD3" s="31" t="inlineStr"/>
+      <c r="AD3" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
           <t>0</t>
@@ -3648,18 +7544,18 @@
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001_3</t>
+          <t>vd_kai_boss_00001_3</t>
         </is>
       </c>
       <c r="C4" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
+          <t>vd_kai_boss_00001</t>
         </is>
       </c>
       <c r="D4" s="31" t="inlineStr"/>
       <c r="E4" s="31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>vd_kai_boss_00001_3</t>
         </is>
       </c>
       <c r="F4" s="31" t="inlineStr">
@@ -3674,7 +7570,7 @@
       </c>
       <c r="H4" s="31" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I4" s="31" t="inlineStr">
@@ -3684,18 +7580,18 @@
       </c>
       <c r="J4" s="31" t="inlineStr">
         <is>
-          <t>e_glo_00001_vd_Normal_Colorless</t>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
         </is>
       </c>
       <c r="K4" s="31" t="inlineStr"/>
       <c r="L4" s="31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" s="31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="N4" s="31" t="inlineStr">
@@ -3778,7 +7674,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="AD4" s="31" t="inlineStr"/>
+      <c r="AD4" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
           <t>0</t>
@@ -3809,18 +7709,18 @@
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001_4</t>
+          <t>vd_kai_boss_00001_4</t>
         </is>
       </c>
       <c r="C5" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
+          <t>vd_kai_boss_00001</t>
         </is>
       </c>
       <c r="D5" s="31" t="inlineStr"/>
       <c r="E5" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>vd_kai_boss_00001_4</t>
         </is>
       </c>
       <c r="F5" s="31" t="inlineStr">
@@ -3830,12 +7730,12 @@
       </c>
       <c r="G5" s="31" t="inlineStr">
         <is>
-          <t>ElapsedTime</t>
+          <t>FriendUnitDead</t>
         </is>
       </c>
       <c r="H5" s="31" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" s="31" t="inlineStr">
@@ -3851,12 +7751,12 @@
       <c r="K5" s="31" t="inlineStr"/>
       <c r="L5" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M5" s="31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N5" s="31" t="inlineStr">
@@ -3939,7 +7839,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="AD5" s="31" t="inlineStr"/>
+      <c r="AD5" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
           <t>0</t>
@@ -3970,18 +7874,18 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001_5</t>
+          <t>vd_kai_boss_00001_5</t>
         </is>
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>vd_kai_normal_00001</t>
+          <t>vd_kai_boss_00001</t>
         </is>
       </c>
       <c r="D6" s="31" t="inlineStr"/>
       <c r="E6" s="31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>vd_kai_boss_00001_5</t>
         </is>
       </c>
       <c r="F6" s="31" t="inlineStr">
@@ -3991,12 +7895,12 @@
       </c>
       <c r="G6" s="31" t="inlineStr">
         <is>
-          <t>ElapsedTime</t>
+          <t>FriendUnitDead</t>
         </is>
       </c>
       <c r="H6" s="31" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" s="31" t="inlineStr">
@@ -4006,13 +7910,13 @@
       </c>
       <c r="J6" s="31" t="inlineStr">
         <is>
-          <t>e_kai_00101_vd_Normal_Yellow</t>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
         </is>
       </c>
       <c r="K6" s="31" t="inlineStr"/>
       <c r="L6" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" s="31" t="inlineStr">
@@ -4027,7 +7931,7 @@
       </c>
       <c r="O6" s="31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="P6" s="31" t="inlineStr">
@@ -4100,7 +8004,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="AD6" s="31" t="inlineStr"/>
+      <c r="AD6" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
           <t>0</t>
@@ -4118,6 +8026,2958 @@
       </c>
       <c r="AH6" s="31" t="inlineStr"/>
       <c r="AI6" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_boss_00001_6</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_boss_00001</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr"/>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_boss_00001_6</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G7" s="31" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="H7" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="K7" s="31" t="inlineStr"/>
+      <c r="L7" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="31" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="N7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O7" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z7" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA7" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB7" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC7" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD7" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH7" s="31" t="inlineStr"/>
+      <c r="AI7" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_boss_00001_7</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_boss_00001</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr"/>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_boss_00001_7</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G8" s="31" t="inlineStr">
+        <is>
+          <t>OutpostHpPercentage</t>
+        </is>
+      </c>
+      <c r="H8" s="31" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J8" s="31" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="K8" s="31" t="inlineStr"/>
+      <c r="L8" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M8" s="31" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="N8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O8" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z8" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA8" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB8" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC8" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD8" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH8" s="31" t="inlineStr"/>
+      <c r="AI8" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001_1</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr"/>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J10" s="31" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K10" s="31" t="inlineStr"/>
+      <c r="L10" s="31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O10" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z10" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA10" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB10" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD10" s="31" t="inlineStr"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH10" s="31" t="inlineStr"/>
+      <c r="AI10" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001_2</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr"/>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G11" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H11" s="31" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="I11" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="K11" s="31" t="inlineStr"/>
+      <c r="L11" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O11" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P11" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R11" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z11" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA11" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB11" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD11" s="31" t="inlineStr"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG11" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH11" s="31" t="inlineStr"/>
+      <c r="AI11" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001_3</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr"/>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H12" s="31" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I12" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J12" s="31" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K12" s="31" t="inlineStr"/>
+      <c r="L12" s="31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N12" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O12" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P12" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R12" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y12" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z12" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA12" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB12" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD12" s="31" t="inlineStr"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG12" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH12" s="31" t="inlineStr"/>
+      <c r="AI12" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001_4</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr"/>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H13" s="31" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="I13" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="K13" s="31" t="inlineStr"/>
+      <c r="L13" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O13" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P13" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q13" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R13" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S13" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U13" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V13" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W13" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z13" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA13" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB13" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD13" s="31" t="inlineStr"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG13" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH13" s="31" t="inlineStr"/>
+      <c r="AI13" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001_5</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>vd_kai_normal_00001</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr"/>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H14" s="31" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="I14" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J14" s="31" t="inlineStr">
+        <is>
+          <t>e_kai_00101_vd_Normal_Yellow</t>
+        </is>
+      </c>
+      <c r="K14" s="31" t="inlineStr"/>
+      <c r="L14" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M14" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O14" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P14" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q14" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R14" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S14" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U14" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V14" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y14" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z14" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA14" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB14" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD14" s="31" t="inlineStr"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG14" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH14" s="31" t="inlineStr"/>
+      <c r="AI14" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_1</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr"/>
+      <c r="E16" s="31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H16" s="31" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I16" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J16" s="31" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K16" s="31" t="inlineStr"/>
+      <c r="L16" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M16" s="31" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="N16" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O16" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P16" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R16" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y16" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z16" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA16" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB16" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD16" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG16" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH16" s="31" t="inlineStr"/>
+      <c r="AI16" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_2</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr"/>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="inlineStr">
+        <is>
+          <t>EnterTargetKomaIndex</t>
+        </is>
+      </c>
+      <c r="H17" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J17" s="31" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K17" s="31" t="inlineStr"/>
+      <c r="L17" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" s="31" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N17" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O17" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P17" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q17" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R17" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S17" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U17" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V17" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X17" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y17" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z17" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA17" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB17" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD17" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG17" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH17" s="31" t="inlineStr"/>
+      <c r="AI17" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_3</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr"/>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="inlineStr">
+        <is>
+          <t>ElapsedTime</t>
+        </is>
+      </c>
+      <c r="H18" s="31" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="I18" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J18" s="31" t="inlineStr">
+        <is>
+          <t>c_osh_00501_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="K18" s="31" t="inlineStr"/>
+      <c r="L18" s="31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N18" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O18" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P18" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R18" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y18" s="31" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="Z18" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA18" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB18" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD18" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG18" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH18" s="31" t="inlineStr"/>
+      <c r="AI18" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_4</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr"/>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="inlineStr">
+        <is>
+          <t>EnterTargetKomaIndex</t>
+        </is>
+      </c>
+      <c r="H19" s="31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J19" s="31" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K19" s="31" t="inlineStr"/>
+      <c r="L19" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M19" s="31" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="N19" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O19" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P19" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q19" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S19" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U19" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z19" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA19" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB19" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD19" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG19" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH19" s="31" t="inlineStr"/>
+      <c r="AI19" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_5</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr"/>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G20" s="31" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="H20" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I20" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J20" s="31" t="inlineStr">
+        <is>
+          <t>c_osh_00201_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="K20" s="31" t="inlineStr"/>
+      <c r="L20" s="31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O20" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P20" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q20" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R20" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S20" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U20" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V20" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X20" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y20" s="31" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="Z20" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA20" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB20" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD20" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG20" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH20" s="31" t="inlineStr"/>
+      <c r="AI20" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_6</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr"/>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="H21" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I21" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J21" s="31" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K21" s="31" t="inlineStr"/>
+      <c r="L21" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" s="31" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N21" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O21" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P21" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q21" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R21" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S21" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U21" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V21" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X21" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y21" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z21" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA21" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB21" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD21" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG21" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH21" s="31" t="inlineStr"/>
+      <c r="AI21" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_7</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr"/>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="inlineStr">
+        <is>
+          <t>EnterTargetKomaIndex</t>
+        </is>
+      </c>
+      <c r="H22" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J22" s="31" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K22" s="31" t="inlineStr"/>
+      <c r="L22" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M22" s="31" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="N22" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O22" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P22" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q22" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R22" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S22" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U22" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V22" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X22" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y22" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z22" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA22" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB22" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD22" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG22" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH22" s="31" t="inlineStr"/>
+      <c r="AI22" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_8</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr"/>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="H23" s="31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I23" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J23" s="31" t="inlineStr">
+        <is>
+          <t>c_osh_00301_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="K23" s="31" t="inlineStr"/>
+      <c r="L23" s="31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O23" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P23" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q23" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R23" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S23" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U23" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V23" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X23" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y23" s="31" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="Z23" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA23" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB23" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD23" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG23" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH23" s="31" t="inlineStr"/>
+      <c r="AI23" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_9</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr"/>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G24" s="31" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="H24" s="31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I24" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J24" s="31" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K24" s="31" t="inlineStr"/>
+      <c r="L24" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M24" s="31" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="N24" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O24" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P24" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q24" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R24" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S24" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T24" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U24" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V24" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W24" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X24" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y24" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z24" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA24" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB24" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD24" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG24" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH24" s="31" t="inlineStr"/>
+      <c r="AI24" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_10</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr"/>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G25" s="31" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="H25" s="31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I25" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J25" s="31" t="inlineStr">
+        <is>
+          <t>c_osh_00401_vd_Normal_Green</t>
+        </is>
+      </c>
+      <c r="K25" s="31" t="inlineStr"/>
+      <c r="L25" s="31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N25" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O25" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P25" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q25" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R25" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S25" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U25" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V25" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W25" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X25" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y25" s="31" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="Z25" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA25" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB25" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD25" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG25" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH25" s="31" t="inlineStr"/>
+      <c r="AI25" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001_11</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr"/>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="G26" s="31" t="inlineStr">
+        <is>
+          <t>FriendUnitDead</t>
+        </is>
+      </c>
+      <c r="H26" s="31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I26" s="31" t="inlineStr">
+        <is>
+          <t>SummonEnemy</t>
+        </is>
+      </c>
+      <c r="J26" s="31" t="inlineStr">
+        <is>
+          <t>e_glo_00001_vd_Normal_Colorless</t>
+        </is>
+      </c>
+      <c r="K26" s="31" t="inlineStr"/>
+      <c r="L26" s="31" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="M26" s="31" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="N26" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O26" s="31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P26" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q26" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R26" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S26" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U26" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V26" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W26" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X26" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y26" s="31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="Z26" s="31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AA26" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB26" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AD26" s="31" t="inlineStr">
+        <is>
+          <t>__NULL__</t>
+        </is>
+      </c>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG26" s="31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AH26" s="31" t="inlineStr"/>
+      <c r="AI26" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -4128,13 +10988,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4167,10 +11027,46 @@
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
+          <t>vd_kai_boss_00001</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
           <t>vd_kai_normal_00001</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>202604010</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>vd_osh_normal_00001</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>202604010</t>
         </is>
@@ -4181,7 +11077,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
